--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1320">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -5887,6 +5887,159 @@
   </si>
   <si>
     <t xml:space="preserve">r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1:s ⊻ O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1:s ∧ O2:s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1:s - O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1:s - O2:s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧[W]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨[W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻[W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] + [W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] + [W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - [W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - [W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨[W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻[W] → [V]; A-1 → A; V+a → V; W+a → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧R; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] + R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] + R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - R; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - R; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V]; R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻R → [V]; A-1 → A; V+r → V; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1016 = HInterrupt1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1015 = HInterrupt2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 = Add unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 = Add signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 = Subtract unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 = Subtract signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 = Compare unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 = Compare signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 = Add unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 = Add signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 = Subtract unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 = Subtract signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 = Compare unsigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 = Compare signed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B, S, V, W, X or Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy into B the value in address X+W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brac z, -8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pul (A, V, W), S</t>
   </si>
 </sst>
 </file>
@@ -8855,7 +9008,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD25"/>
+  <dimension ref="A1:XFD24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.85"/>
@@ -8948,13 +9101,13 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="253"/>
+      <c r="A6" s="212"/>
       <c r="B6" s="102" t="n">
         <f aca="false">B5+D5</f>
         <v>2</v>
       </c>
       <c r="C6" s="127" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D6" s="102" t="n">
         <v>2</v>
@@ -8963,23 +9116,23 @@
         <v>607</v>
       </c>
       <c r="F6" s="102" t="s">
-        <v>1084</v>
+        <v>1089</v>
       </c>
       <c r="G6" s="102" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="102" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="212"/>
+      <c r="A7" s="254"/>
       <c r="B7" s="102" t="n">
         <f aca="false">B6+D6</f>
         <v>4</v>
       </c>
-      <c r="C7" s="127" t="s">
-        <v>1088</v>
+      <c r="C7" s="255" t="s">
+        <v>1091</v>
       </c>
       <c r="D7" s="102" t="n">
         <v>2</v>
@@ -8988,55 +9141,55 @@
         <v>607</v>
       </c>
       <c r="F7" s="102" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G7" s="102" t="n">
-        <v>2</v>
+        <v>1083</v>
+      </c>
+      <c r="G7" s="102" t="s">
+        <v>1092</v>
       </c>
       <c r="H7" s="102" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="254"/>
-      <c r="B8" s="102" t="n">
+      <c r="A8" s="212" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C8" s="127"/>
+      <c r="H8" s="0"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="212"/>
+      <c r="B9" s="102" t="n">
         <f aca="false">B7+D7</f>
         <v>6</v>
       </c>
-      <c r="C8" s="255" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D8" s="102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="102" t="s">
+      <c r="C9" s="127" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D9" s="102" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E9" s="102" t="s">
         <v>607</v>
       </c>
-      <c r="F8" s="102" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G8" s="102" t="s">
-        <v>1092</v>
-      </c>
-      <c r="H8" s="102" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="212" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C9" s="127"/>
-      <c r="H9" s="0"/>
+      <c r="F9" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="G9" s="102" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H9" s="102" t="s">
+        <v>1316</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="212"/>
       <c r="B10" s="102" t="n">
-        <f aca="false">B8+D8</f>
+        <f aca="false">B9+D9</f>
         <v>8</v>
       </c>
       <c r="C10" s="127" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="D10" s="102" t="s">
         <v>1096</v>
@@ -9051,7 +9204,7 @@
         <v>1097</v>
       </c>
       <c r="H10" s="102" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9061,7 +9214,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="127" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D11" s="102" t="s">
         <v>1096</v>
@@ -9070,13 +9223,13 @@
         <v>607</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>960</v>
-      </c>
-      <c r="G11" s="102" t="s">
-        <v>1097</v>
+        <v>1089</v>
+      </c>
+      <c r="G11" s="102" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="102" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9086,113 +9239,110 @@
         <v>12</v>
       </c>
       <c r="C12" s="127" t="s">
-        <v>1101</v>
+        <v>1317</v>
       </c>
       <c r="D12" s="102" t="s">
         <v>1096</v>
       </c>
-      <c r="E12" s="102" t="s">
-        <v>607</v>
-      </c>
-      <c r="F12" s="0" t="s">
-        <v>1089</v>
+      <c r="E12" s="0" t="s">
+        <v>756</v>
+      </c>
+      <c r="F12" s="102" t="s">
+        <v>1104</v>
       </c>
       <c r="G12" s="102" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="102" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="212"/>
-      <c r="B13" s="102" t="n">
+      <c r="A13" s="189" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B13" s="256" t="n">
         <f aca="false">B12+D12</f>
         <v>14</v>
       </c>
-      <c r="C13" s="127" t="s">
-        <v>1103</v>
-      </c>
-      <c r="D13" s="102" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>756</v>
-      </c>
-      <c r="F13" s="102" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G13" s="102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="102" t="s">
-        <v>1105</v>
-      </c>
+      <c r="C13" s="191"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="189" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B14" s="256" t="n">
-        <f aca="false">B13+D13</f>
-        <v>16</v>
-      </c>
-      <c r="C14" s="191"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="119" t="s">
+      <c r="A14" s="119" t="s">
         <v>1107</v>
       </c>
-      <c r="B15" s="119"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="102" t="s">
+        <v>1108</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H17" s="102" t="s">
-        <v>1108</v>
-      </c>
+      <c r="A17" s="250" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B17" s="251"/>
+      <c r="C17" s="252"/>
+      <c r="D17" s="0"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="250" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B18" s="251"/>
-      <c r="C18" s="252"/>
-      <c r="D18" s="0"/>
+      <c r="A18" s="253"/>
+      <c r="B18" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="127" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D18" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="102" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F18" s="102" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G18" s="102" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="253"/>
       <c r="B19" s="102" t="n">
-        <v>0</v>
+        <f aca="false">B18+D18</f>
+        <v>2</v>
       </c>
       <c r="C19" s="127" t="s">
-        <v>1082</v>
+        <v>1109</v>
       </c>
       <c r="D19" s="102" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="102" t="s">
-        <v>1083</v>
+        <v>607</v>
       </c>
       <c r="F19" s="102" t="s">
-        <v>1084</v>
+        <v>1318</v>
       </c>
       <c r="G19" s="102" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="253"/>
+      <c r="A20" s="254"/>
       <c r="B20" s="102" t="n">
         <f aca="false">B19+D19</f>
-        <v>2</v>
-      </c>
-      <c r="C20" s="127" t="s">
-        <v>1109</v>
+        <v>4</v>
+      </c>
+      <c r="C20" s="255" t="s">
+        <v>1319</v>
       </c>
       <c r="D20" s="102" t="n">
         <v>2</v>
@@ -9201,88 +9351,66 @@
         <v>607</v>
       </c>
       <c r="F20" s="102" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G20" s="102" t="n">
+        <v>1083</v>
+      </c>
+      <c r="G20" s="102" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="212" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C21" s="127"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="212"/>
+      <c r="B22" s="102" t="n">
+        <f aca="false">B20+D20</f>
+        <v>6</v>
+      </c>
+      <c r="C22" s="127" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D22" s="102" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="254"/>
-      <c r="B21" s="102" t="n">
-        <f aca="false">B20+D20</f>
-        <v>4</v>
-      </c>
-      <c r="C21" s="255" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D21" s="102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="102" t="s">
-        <v>607</v>
-      </c>
-      <c r="F21" s="102" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G21" s="102" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="212" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C22" s="127"/>
+      <c r="E22" s="102" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G22" s="102" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H22" s="102" t="s">
+        <v>1114</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="212"/>
-      <c r="B23" s="102" t="n">
-        <f aca="false">B21+D21</f>
-        <v>6</v>
-      </c>
-      <c r="C23" s="127" t="s">
-        <v>1112</v>
-      </c>
-      <c r="D23" s="102" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="102" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G23" s="102" t="s">
-        <v>1097</v>
-      </c>
-      <c r="H23" s="102" t="s">
-        <v>1114</v>
-      </c>
+      <c r="A23" s="189" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B23" s="256" t="n">
+        <f aca="false">B22+D22</f>
+        <v>8</v>
+      </c>
+      <c r="C23" s="191"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="189" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B24" s="256" t="n">
-        <f aca="false">B23+D23</f>
-        <v>8</v>
-      </c>
-      <c r="C24" s="191"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="119" t="s">
+      <c r="A24" s="119" t="s">
         <v>1115</v>
       </c>
-      <c r="B25" s="119"/>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="119"/>
-      <c r="H25" s="119"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A24:H24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15183,7 +15311,7 @@
       <c r="H18" s="57"/>
       <c r="I18" s="115"/>
       <c r="J18" s="114" t="s">
-        <v>273</v>
+        <v>1270</v>
       </c>
       <c r="K18" s="114" t="s">
         <v>254</v>
@@ -15239,7 +15367,7 @@
       <c r="H20" s="57"/>
       <c r="I20" s="115"/>
       <c r="J20" s="114" t="s">
-        <v>279</v>
+        <v>1271</v>
       </c>
       <c r="K20" s="114" t="s">
         <v>254</v>
@@ -15353,7 +15481,7 @@
       <c r="H24" s="57"/>
       <c r="I24" s="115"/>
       <c r="J24" s="114" t="s">
-        <v>293</v>
+        <v>1272</v>
       </c>
       <c r="K24" s="114" t="s">
         <v>285</v>
@@ -15409,7 +15537,7 @@
       <c r="H26" s="57"/>
       <c r="I26" s="115"/>
       <c r="J26" s="114" t="s">
-        <v>300</v>
+        <v>1273</v>
       </c>
       <c r="K26" s="114" t="s">
         <v>298</v>
@@ -16006,7 +16134,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" s="57" t="s">
         <v>313</v>
@@ -16035,7 +16163,7 @@
       <c r="E48" s="111"/>
       <c r="F48" s="111"/>
       <c r="G48" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" s="57"/>
       <c r="I48" s="115" t="s">
@@ -16662,7 +16790,7 @@
       </c>
       <c r="I69" s="115"/>
       <c r="J69" s="114" t="s">
-        <v>466</v>
+        <v>1283</v>
       </c>
       <c r="K69" s="114" t="s">
         <v>184</v>
@@ -16692,7 +16820,7 @@
       <c r="H70" s="125"/>
       <c r="I70" s="115"/>
       <c r="J70" s="114" t="s">
-        <v>470</v>
+        <v>1284</v>
       </c>
       <c r="K70" s="114" t="s">
         <v>471</v>
@@ -16722,7 +16850,7 @@
       <c r="H71" s="125"/>
       <c r="I71" s="115"/>
       <c r="J71" s="114" t="s">
-        <v>475</v>
+        <v>1285</v>
       </c>
       <c r="K71" s="114" t="s">
         <v>471</v>
@@ -16752,7 +16880,7 @@
       <c r="H72" s="125"/>
       <c r="I72" s="115"/>
       <c r="J72" s="114" t="s">
-        <v>479</v>
+        <v>1286</v>
       </c>
       <c r="K72" s="114" t="s">
         <v>471</v>
@@ -16779,7 +16907,7 @@
       <c r="H73" s="125"/>
       <c r="I73" s="115"/>
       <c r="J73" s="114" t="s">
-        <v>482</v>
+        <v>1287</v>
       </c>
       <c r="K73" s="114" t="s">
         <v>471</v>
@@ -16808,7 +16936,7 @@
       </c>
       <c r="I74" s="115"/>
       <c r="J74" s="114" t="s">
-        <v>485</v>
+        <v>1288</v>
       </c>
       <c r="K74" s="114" t="s">
         <v>471</v>
@@ -16835,7 +16963,7 @@
       <c r="H75" s="125"/>
       <c r="I75" s="115"/>
       <c r="J75" s="114" t="s">
-        <v>485</v>
+        <v>1289</v>
       </c>
       <c r="K75" s="114" t="s">
         <v>471</v>
@@ -16862,7 +16990,7 @@
       <c r="H76" s="125"/>
       <c r="I76" s="115"/>
       <c r="J76" s="114" t="s">
-        <v>490</v>
+        <v>1290</v>
       </c>
       <c r="K76" s="114" t="s">
         <v>471</v>
@@ -16889,7 +17017,7 @@
       <c r="H77" s="125"/>
       <c r="I77" s="115"/>
       <c r="J77" s="114" t="s">
-        <v>490</v>
+        <v>1291</v>
       </c>
       <c r="K77" s="114" t="s">
         <v>471</v>
@@ -16919,7 +17047,7 @@
       <c r="H78" s="125"/>
       <c r="I78" s="115"/>
       <c r="J78" s="114" t="s">
-        <v>496</v>
+        <v>1292</v>
       </c>
       <c r="K78" s="114" t="s">
         <v>471</v>
@@ -16949,7 +17077,7 @@
       <c r="H79" s="125"/>
       <c r="I79" s="115"/>
       <c r="J79" s="114" t="s">
-        <v>496</v>
+        <v>1293</v>
       </c>
       <c r="K79" s="114" t="s">
         <v>471</v>
@@ -16959,8 +17087,8 @@
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="103"/>
       <c r="B80" s="0" t="n">
-        <f aca="false">B75+1</f>
-        <v>65</v>
+        <f aca="false">B79+1</f>
+        <v>69</v>
       </c>
       <c r="C80" s="30" t="s">
         <v>500</v>
@@ -16978,7 +17106,7 @@
       </c>
       <c r="I80" s="115"/>
       <c r="J80" s="114" t="s">
-        <v>502</v>
+        <v>1294</v>
       </c>
       <c r="K80" s="114" t="s">
         <v>471</v>
@@ -16992,7 +17120,7 @@
       <c r="A81" s="103"/>
       <c r="B81" s="0" t="n">
         <f aca="false">B80+1</f>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C81" s="30" t="s">
         <v>504</v>
@@ -17008,7 +17136,7 @@
       <c r="H81" s="125"/>
       <c r="I81" s="115"/>
       <c r="J81" s="114" t="s">
-        <v>470</v>
+        <v>1295</v>
       </c>
       <c r="K81" s="114" t="s">
         <v>471</v>
@@ -17022,7 +17150,7 @@
       <c r="A82" s="103"/>
       <c r="B82" s="0" t="n">
         <f aca="false">B81+1</f>
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C82" s="30" t="s">
         <v>507</v>
@@ -17038,7 +17166,7 @@
       <c r="H82" s="125"/>
       <c r="I82" s="115"/>
       <c r="J82" s="114" t="s">
-        <v>479</v>
+        <v>1296</v>
       </c>
       <c r="K82" s="114" t="s">
         <v>471</v>
@@ -17049,7 +17177,7 @@
       <c r="A83" s="103"/>
       <c r="B83" s="0" t="n">
         <f aca="false">B82+1</f>
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C83" s="30" t="s">
         <v>509</v>
@@ -17065,7 +17193,7 @@
       <c r="H83" s="125"/>
       <c r="I83" s="115"/>
       <c r="J83" s="114" t="s">
-        <v>482</v>
+        <v>1297</v>
       </c>
       <c r="K83" s="114" t="s">
         <v>471</v>
@@ -17076,7 +17204,7 @@
       <c r="A84" s="103"/>
       <c r="B84" s="0" t="n">
         <f aca="false">B83+1</f>
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C84" s="30" t="s">
         <v>511</v>
@@ -17110,7 +17238,7 @@
       <c r="A85" s="103"/>
       <c r="B85" s="0" t="n">
         <f aca="false">B84+1</f>
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C85" s="30" t="s">
         <v>515</v>
@@ -17140,7 +17268,7 @@
       <c r="A86" s="103"/>
       <c r="B86" s="0" t="n">
         <f aca="false">B85+1</f>
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C86" s="30" t="s">
         <v>519</v>
@@ -17170,7 +17298,7 @@
       <c r="A87" s="103"/>
       <c r="B87" s="0" t="n">
         <f aca="false">B86+1</f>
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C87" s="30" t="s">
         <v>523</v>
@@ -17186,7 +17314,7 @@
       <c r="H87" s="125"/>
       <c r="I87" s="115"/>
       <c r="J87" s="114" t="s">
-        <v>525</v>
+        <v>1274</v>
       </c>
       <c r="K87" s="114" t="s">
         <v>471</v>
@@ -17197,7 +17325,7 @@
       <c r="A88" s="103"/>
       <c r="B88" s="0" t="n">
         <f aca="false">B87+1</f>
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C88" s="30" t="s">
         <v>526</v>
@@ -17213,7 +17341,7 @@
       <c r="H88" s="125"/>
       <c r="I88" s="115"/>
       <c r="J88" s="114" t="s">
-        <v>528</v>
+        <v>1275</v>
       </c>
       <c r="K88" s="114" t="s">
         <v>471</v>
@@ -17224,7 +17352,7 @@
       <c r="A89" s="103"/>
       <c r="B89" s="0" t="n">
         <f aca="false">B88+1</f>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C89" s="30" t="s">
         <v>529</v>
@@ -17240,7 +17368,7 @@
       <c r="H89" s="125"/>
       <c r="I89" s="115"/>
       <c r="J89" s="114" t="s">
-        <v>528</v>
+        <v>1276</v>
       </c>
       <c r="K89" s="114" t="s">
         <v>471</v>
@@ -17251,7 +17379,7 @@
       <c r="A90" s="103"/>
       <c r="B90" s="0" t="n">
         <f aca="false">B89+1</f>
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C90" s="30" t="s">
         <v>531</v>
@@ -17269,7 +17397,7 @@
       </c>
       <c r="I90" s="115"/>
       <c r="J90" s="114" t="s">
-        <v>533</v>
+        <v>1277</v>
       </c>
       <c r="K90" s="114" t="s">
         <v>471</v>
@@ -17280,7 +17408,7 @@
       <c r="A91" s="103"/>
       <c r="B91" s="0" t="n">
         <f aca="false">B90+1</f>
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C91" s="30" t="s">
         <v>534</v>
@@ -17296,7 +17424,7 @@
       <c r="H91" s="125"/>
       <c r="I91" s="115"/>
       <c r="J91" s="114" t="s">
-        <v>533</v>
+        <v>1278</v>
       </c>
       <c r="K91" s="114" t="s">
         <v>471</v>
@@ -17307,7 +17435,7 @@
       <c r="A92" s="103"/>
       <c r="B92" s="0" t="n">
         <f aca="false">B91+1</f>
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C92" s="30" t="s">
         <v>536</v>
@@ -17323,7 +17451,7 @@
       <c r="H92" s="125"/>
       <c r="I92" s="115"/>
       <c r="J92" s="114" t="s">
-        <v>538</v>
+        <v>1279</v>
       </c>
       <c r="K92" s="114" t="s">
         <v>471</v>
@@ -17334,7 +17462,7 @@
       <c r="A93" s="103"/>
       <c r="B93" s="0" t="n">
         <f aca="false">B92+1</f>
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C93" s="30" t="s">
         <v>539</v>
@@ -17350,7 +17478,7 @@
       <c r="H93" s="125"/>
       <c r="I93" s="115"/>
       <c r="J93" s="114" t="s">
-        <v>538</v>
+        <v>1280</v>
       </c>
       <c r="K93" s="114" t="s">
         <v>471</v>
@@ -17361,7 +17489,7 @@
       <c r="A94" s="103"/>
       <c r="B94" s="0" t="n">
         <f aca="false">B93+1</f>
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C94" s="30" t="s">
         <v>541</v>
@@ -17388,7 +17516,7 @@
       <c r="A95" s="103"/>
       <c r="B95" s="0" t="n">
         <f aca="false">B94+1</f>
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C95" s="30" t="s">
         <v>543</v>
@@ -17415,7 +17543,7 @@
       <c r="A96" s="103"/>
       <c r="B96" s="0" t="n">
         <f aca="false">B95+1</f>
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C96" s="30" t="s">
         <v>545</v>
@@ -17447,7 +17575,7 @@
       <c r="A97" s="103"/>
       <c r="B97" s="0" t="n">
         <f aca="false">B96+1</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C97" s="30" t="s">
         <v>547</v>
@@ -17474,7 +17602,7 @@
       <c r="A98" s="103"/>
       <c r="B98" s="0" t="n">
         <f aca="false">B97+1</f>
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C98" s="30" t="s">
         <v>549</v>
@@ -17490,7 +17618,7 @@
       <c r="H98" s="125"/>
       <c r="I98" s="115"/>
       <c r="J98" s="114" t="s">
-        <v>528</v>
+        <v>1281</v>
       </c>
       <c r="K98" s="114" t="s">
         <v>471</v>
@@ -17501,7 +17629,7 @@
       <c r="A99" s="103"/>
       <c r="B99" s="0" t="n">
         <f aca="false">B98+1</f>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C99" s="30" t="s">
         <v>551</v>
@@ -17517,7 +17645,7 @@
       <c r="H99" s="125"/>
       <c r="I99" s="115"/>
       <c r="J99" s="114" t="s">
-        <v>528</v>
+        <v>1282</v>
       </c>
       <c r="K99" s="114" t="s">
         <v>471</v>
@@ -17528,13 +17656,13 @@
       <c r="A100" s="103"/>
       <c r="B100" s="0" t="n">
         <f aca="false">B99+1</f>
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C100" s="30" t="s">
         <v>553</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>532</v>
+        <v>1269</v>
       </c>
       <c r="E100" s="111" t="n">
         <v>15</v>
@@ -17557,7 +17685,7 @@
       <c r="A101" s="103"/>
       <c r="B101" s="0" t="n">
         <f aca="false">B100+1</f>
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C101" s="30" t="s">
         <v>556</v>
@@ -17582,7 +17710,7 @@
       <c r="A102" s="103"/>
       <c r="B102" s="0" t="n">
         <f aca="false">B101+1</f>
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C102" s="30" t="s">
         <v>559</v>
@@ -17607,7 +17735,7 @@
       <c r="A103" s="103"/>
       <c r="B103" s="0" t="n">
         <f aca="false">B102+1</f>
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C103" s="30" t="s">
         <v>562</v>
@@ -17632,7 +17760,7 @@
       <c r="A104" s="103"/>
       <c r="B104" s="0" t="n">
         <f aca="false">B103+1</f>
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C104" s="30" t="s">
         <v>565</v>
@@ -17661,7 +17789,7 @@
       <c r="A105" s="103"/>
       <c r="B105" s="0" t="n">
         <f aca="false">B104+1</f>
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C105" s="30" t="s">
         <v>569</v>
@@ -17686,7 +17814,7 @@
       <c r="A106" s="103"/>
       <c r="B106" s="0" t="n">
         <f aca="false">B105+1</f>
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C106" s="30" t="s">
         <v>572</v>
@@ -25394,7 +25522,7 @@
       <c r="A140" s="103"/>
       <c r="C140" s="103"/>
       <c r="D140" s="170" t="s">
-        <v>791</v>
+        <v>1298</v>
       </c>
       <c r="E140" s="170"/>
       <c r="F140" s="170"/>
@@ -25434,7 +25562,7 @@
       <c r="A141" s="103"/>
       <c r="C141" s="103"/>
       <c r="D141" s="170" t="s">
-        <v>792</v>
+        <v>1299</v>
       </c>
       <c r="E141" s="170"/>
       <c r="F141" s="170"/>
@@ -29116,10 +29244,10 @@
       <c r="E224" s="57"/>
       <c r="F224" s="57"/>
       <c r="G224" s="80" t="s">
-        <v>847</v>
+        <v>1300</v>
       </c>
       <c r="H224" s="80" t="s">
-        <v>846</v>
+        <v>1301</v>
       </c>
       <c r="I224" s="80" t="s">
         <v>848</v>
@@ -32736,7 +32864,7 @@
       </c>
       <c r="G308" s="224"/>
       <c r="H308" s="57" t="s">
-        <v>668</v>
+        <v>1314</v>
       </c>
       <c r="I308" s="57"/>
       <c r="J308" s="57"/>
@@ -33011,7 +33139,7 @@
       <c r="I314" s="57"/>
       <c r="J314" s="57"/>
       <c r="K314" s="228" t="s">
-        <v>925</v>
+        <v>1302</v>
       </c>
       <c r="L314" s="228"/>
       <c r="M314" s="228"/>
@@ -33051,7 +33179,7 @@
       <c r="I315" s="57"/>
       <c r="J315" s="57"/>
       <c r="K315" s="228" t="s">
-        <v>926</v>
+        <v>1303</v>
       </c>
       <c r="L315" s="228"/>
       <c r="M315" s="228"/>
@@ -33091,7 +33219,7 @@
       <c r="I316" s="57"/>
       <c r="J316" s="57"/>
       <c r="K316" s="228" t="s">
-        <v>927</v>
+        <v>1304</v>
       </c>
       <c r="L316" s="228"/>
       <c r="M316" s="228"/>
@@ -33131,7 +33259,7 @@
       <c r="I317" s="57"/>
       <c r="J317" s="57"/>
       <c r="K317" s="228" t="s">
-        <v>928</v>
+        <v>1305</v>
       </c>
       <c r="L317" s="228"/>
       <c r="M317" s="228"/>
@@ -33171,7 +33299,7 @@
       <c r="I318" s="57"/>
       <c r="J318" s="57"/>
       <c r="K318" s="228" t="s">
-        <v>929</v>
+        <v>1306</v>
       </c>
       <c r="L318" s="228"/>
       <c r="M318" s="228"/>
@@ -33211,7 +33339,7 @@
       <c r="I319" s="57"/>
       <c r="J319" s="57"/>
       <c r="K319" s="228" t="s">
-        <v>930</v>
+        <v>1307</v>
       </c>
       <c r="L319" s="228"/>
       <c r="M319" s="228"/>
@@ -33729,7 +33857,7 @@
       <c r="I332" s="95"/>
       <c r="J332" s="95"/>
       <c r="K332" s="228" t="s">
-        <v>925</v>
+        <v>1308</v>
       </c>
       <c r="L332" s="228"/>
       <c r="M332" s="228"/>
@@ -33771,7 +33899,7 @@
       <c r="I333" s="95"/>
       <c r="J333" s="95"/>
       <c r="K333" s="228" t="s">
-        <v>926</v>
+        <v>1309</v>
       </c>
       <c r="L333" s="228"/>
       <c r="M333" s="228"/>
@@ -33810,7 +33938,7 @@
       <c r="I334" s="95"/>
       <c r="J334" s="95"/>
       <c r="K334" s="228" t="s">
-        <v>927</v>
+        <v>1310</v>
       </c>
       <c r="L334" s="228"/>
       <c r="M334" s="228"/>
@@ -33849,7 +33977,7 @@
       <c r="I335" s="95"/>
       <c r="J335" s="95"/>
       <c r="K335" s="228" t="s">
-        <v>928</v>
+        <v>1311</v>
       </c>
       <c r="L335" s="228"/>
       <c r="M335" s="228"/>
@@ -33888,7 +34016,7 @@
       <c r="I336" s="95"/>
       <c r="J336" s="95"/>
       <c r="K336" s="228" t="s">
-        <v>929</v>
+        <v>1312</v>
       </c>
       <c r="L336" s="228"/>
       <c r="M336" s="228"/>
@@ -33927,7 +34055,7 @@
       <c r="I337" s="95"/>
       <c r="J337" s="95"/>
       <c r="K337" s="228" t="s">
-        <v>930</v>
+        <v>1313</v>
       </c>
       <c r="L337" s="228"/>
       <c r="M337" s="228"/>
@@ -35415,7 +35543,7 @@
         <v>965</v>
       </c>
       <c r="B18" s="242" t="s">
-        <v>1003</v>
+        <v>1315</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>1004</v>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1344">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -6040,6 +6040,78 @@
   </si>
   <si>
     <t xml:space="preserve">pul (A, V, W), S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">badd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block subtract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bsub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Block compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bcmp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vadd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector subtract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vsub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vcmp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 = Add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 = Subtract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 = Compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 = Add</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8 = Subtract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 = Compare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 = Unused</t>
   </si>
 </sst>
 </file>
@@ -14947,7 +15019,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:M123"/>
+  <dimension ref="A2:M117"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.64"/>
@@ -16921,10 +16993,10 @@
         <v>63</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>483</v>
+        <v>1320</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>484</v>
+        <v>1321</v>
       </c>
       <c r="E74" s="111"/>
       <c r="F74" s="111"/>
@@ -16950,23 +17022,26 @@
         <v>64</v>
       </c>
       <c r="C75" s="30" t="s">
-        <v>486</v>
+        <v>1322</v>
       </c>
       <c r="D75" s="30" t="s">
-        <v>487</v>
+        <v>1323</v>
       </c>
       <c r="E75" s="111"/>
       <c r="F75" s="111"/>
       <c r="G75" s="30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H75" s="125"/>
       <c r="I75" s="115"/>
       <c r="J75" s="114" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="K75" s="114" t="s">
         <v>471</v>
+      </c>
+      <c r="L75" s="0" t="s">
+        <v>493</v>
       </c>
       <c r="M75" s="103"/>
     </row>
@@ -16977,53 +17052,58 @@
         <v>65</v>
       </c>
       <c r="C76" s="30" t="s">
-        <v>488</v>
+        <v>1324</v>
       </c>
       <c r="D76" s="30" t="s">
-        <v>489</v>
+        <v>1325</v>
       </c>
       <c r="E76" s="111"/>
       <c r="F76" s="111"/>
       <c r="G76" s="30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H76" s="125"/>
       <c r="I76" s="115"/>
       <c r="J76" s="114" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="K76" s="114" t="s">
         <v>471</v>
       </c>
+      <c r="L76" s="0" t="s">
+        <v>497</v>
+      </c>
       <c r="M76" s="103"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="103"/>
       <c r="B77" s="0" t="n">
         <f aca="false">B76+1</f>
         <v>66</v>
       </c>
       <c r="C77" s="30" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D77" s="30" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E77" s="111"/>
       <c r="F77" s="111"/>
       <c r="G77" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="H77" s="125"/>
+        <v>12</v>
+      </c>
+      <c r="H77" s="125" t="s">
+        <v>465</v>
+      </c>
       <c r="I77" s="115"/>
       <c r="J77" s="114" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="K77" s="114" t="s">
         <v>471</v>
       </c>
       <c r="L77" s="0" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="M77" s="103"/>
     </row>
@@ -17034,26 +17114,26 @@
         <v>67</v>
       </c>
       <c r="C78" s="30" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="D78" s="30" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="E78" s="111"/>
       <c r="F78" s="111"/>
       <c r="G78" s="30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H78" s="125"/>
       <c r="I78" s="115"/>
       <c r="J78" s="114" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="K78" s="114" t="s">
         <v>471</v>
       </c>
       <c r="L78" s="0" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="M78" s="103"/>
     </row>
@@ -17064,85 +17144,84 @@
         <v>68</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="E79" s="111"/>
       <c r="F79" s="111"/>
       <c r="G79" s="30" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H79" s="125"/>
       <c r="I79" s="115"/>
       <c r="J79" s="114" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="K79" s="114" t="s">
         <v>471</v>
       </c>
       <c r="M79" s="103"/>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="103"/>
       <c r="B80" s="0" t="n">
         <f aca="false">B79+1</f>
         <v>69</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="E80" s="111"/>
       <c r="F80" s="111"/>
       <c r="G80" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H80" s="125" t="s">
-        <v>465</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H80" s="125"/>
       <c r="I80" s="115"/>
       <c r="J80" s="114" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="K80" s="114" t="s">
         <v>471</v>
       </c>
-      <c r="L80" s="0" t="s">
-        <v>503</v>
-      </c>
       <c r="M80" s="103"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="103"/>
       <c r="B81" s="0" t="n">
         <f aca="false">B80+1</f>
         <v>70</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="E81" s="111"/>
-      <c r="F81" s="111"/>
+      <c r="F81" s="111" t="n">
+        <v>3</v>
+      </c>
       <c r="G81" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="H81" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="H81" s="125" t="s">
+        <v>465</v>
+      </c>
       <c r="I81" s="115"/>
       <c r="J81" s="114" t="s">
-        <v>1295</v>
+        <v>513</v>
       </c>
       <c r="K81" s="114" t="s">
         <v>471</v>
       </c>
       <c r="L81" s="0" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="M81" s="103"/>
     </row>
@@ -17153,23 +17232,26 @@
         <v>71</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="D82" s="30" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="E82" s="111"/>
       <c r="F82" s="111"/>
       <c r="G82" s="30" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H82" s="125"/>
-      <c r="I82" s="115"/>
+      <c r="I82" s="127"/>
       <c r="J82" s="114" t="s">
-        <v>1296</v>
+        <v>517</v>
       </c>
       <c r="K82" s="114" t="s">
         <v>471</v>
+      </c>
+      <c r="L82" s="0" t="s">
+        <v>518</v>
       </c>
       <c r="M82" s="103"/>
     </row>
@@ -17180,57 +17262,53 @@
         <v>72</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="E83" s="111"/>
       <c r="F83" s="111"/>
       <c r="G83" s="30" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H83" s="125"/>
       <c r="I83" s="115"/>
       <c r="J83" s="114" t="s">
-        <v>1297</v>
+        <v>521</v>
       </c>
       <c r="K83" s="114" t="s">
         <v>471</v>
       </c>
+      <c r="L83" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="M83" s="103"/>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="103"/>
       <c r="B84" s="0" t="n">
         <f aca="false">B83+1</f>
         <v>73</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="E84" s="111"/>
-      <c r="F84" s="111" t="n">
+      <c r="F84" s="111"/>
+      <c r="G84" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="G84" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="125" t="s">
-        <v>465</v>
-      </c>
+      <c r="H84" s="125"/>
       <c r="I84" s="115"/>
       <c r="J84" s="114" t="s">
-        <v>513</v>
+        <v>1274</v>
       </c>
       <c r="K84" s="114" t="s">
         <v>471</v>
-      </c>
-      <c r="L84" s="0" t="s">
-        <v>514</v>
       </c>
       <c r="M84" s="103"/>
     </row>
@@ -17241,26 +17319,23 @@
         <v>74</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D85" s="30" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E85" s="111"/>
       <c r="F85" s="111"/>
       <c r="G85" s="30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H85" s="125"/>
-      <c r="I85" s="127"/>
+      <c r="I85" s="115"/>
       <c r="J85" s="114" t="s">
-        <v>517</v>
+        <v>1275</v>
       </c>
       <c r="K85" s="114" t="s">
         <v>471</v>
-      </c>
-      <c r="L85" s="0" t="s">
-        <v>518</v>
       </c>
       <c r="M85" s="103"/>
     </row>
@@ -17271,50 +17346,49 @@
         <v>75</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="E86" s="111"/>
       <c r="F86" s="111"/>
       <c r="G86" s="30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H86" s="125"/>
       <c r="I86" s="115"/>
       <c r="J86" s="114" t="s">
-        <v>521</v>
+        <v>1276</v>
       </c>
       <c r="K86" s="114" t="s">
         <v>471</v>
       </c>
-      <c r="L86" s="0" t="s">
-        <v>522</v>
-      </c>
       <c r="M86" s="103"/>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="103"/>
       <c r="B87" s="0" t="n">
         <f aca="false">B86+1</f>
         <v>76</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>523</v>
+        <v>1326</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>524</v>
+        <v>1327</v>
       </c>
       <c r="E87" s="111"/>
       <c r="F87" s="111"/>
       <c r="G87" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="H87" s="125"/>
+        <v>6</v>
+      </c>
+      <c r="H87" s="125" t="s">
+        <v>422</v>
+      </c>
       <c r="I87" s="115"/>
       <c r="J87" s="114" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="K87" s="114" t="s">
         <v>471</v>
@@ -17328,20 +17402,20 @@
         <v>77</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>526</v>
+        <v>1328</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>527</v>
+        <v>1329</v>
       </c>
       <c r="E88" s="111"/>
       <c r="F88" s="111"/>
       <c r="G88" s="30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H88" s="125"/>
       <c r="I88" s="115"/>
       <c r="J88" s="114" t="s">
-        <v>1275</v>
+        <v>1279</v>
       </c>
       <c r="K88" s="114" t="s">
         <v>471</v>
@@ -17355,20 +17429,20 @@
         <v>78</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>529</v>
+        <v>1330</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>530</v>
+        <v>1331</v>
       </c>
       <c r="E89" s="111"/>
       <c r="F89" s="111"/>
       <c r="G89" s="30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H89" s="125"/>
       <c r="I89" s="115"/>
       <c r="J89" s="114" t="s">
-        <v>1276</v>
+        <v>538</v>
       </c>
       <c r="K89" s="114" t="s">
         <v>471</v>
@@ -17382,25 +17456,28 @@
         <v>79</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="E90" s="111"/>
       <c r="F90" s="111"/>
       <c r="G90" s="30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H90" s="125" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="I90" s="115"/>
       <c r="J90" s="114" t="s">
-        <v>1277</v>
+        <v>513</v>
       </c>
       <c r="K90" s="114" t="s">
         <v>471</v>
+      </c>
+      <c r="L90" s="0" t="s">
+        <v>514</v>
       </c>
       <c r="M90" s="103"/>
     </row>
@@ -17411,20 +17488,20 @@
         <v>80</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="E91" s="111"/>
       <c r="F91" s="111"/>
       <c r="G91" s="30" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H91" s="125"/>
       <c r="I91" s="115"/>
       <c r="J91" s="114" t="s">
-        <v>1278</v>
+        <v>521</v>
       </c>
       <c r="K91" s="114" t="s">
         <v>471</v>
@@ -17438,20 +17515,20 @@
         <v>81</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="E92" s="111"/>
       <c r="F92" s="111"/>
       <c r="G92" s="30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H92" s="125"/>
       <c r="I92" s="115"/>
       <c r="J92" s="114" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="K92" s="114" t="s">
         <v>471</v>
@@ -17465,20 +17542,20 @@
         <v>82</v>
       </c>
       <c r="C93" s="30" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="E93" s="111"/>
       <c r="F93" s="111"/>
       <c r="G93" s="30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H93" s="125"/>
       <c r="I93" s="115"/>
       <c r="J93" s="114" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="K93" s="114" t="s">
         <v>471</v>
@@ -17492,24 +17569,26 @@
         <v>83</v>
       </c>
       <c r="C94" s="30" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>542</v>
-      </c>
-      <c r="E94" s="111"/>
-      <c r="F94" s="111"/>
-      <c r="G94" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="H94" s="125"/>
+        <v>1269</v>
+      </c>
+      <c r="E94" s="111" t="n">
+        <v>15</v>
+      </c>
+      <c r="F94" s="121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="128"/>
+      <c r="H94" s="57" t="s">
+        <v>554</v>
+      </c>
       <c r="I94" s="115"/>
       <c r="J94" s="114" t="s">
-        <v>538</v>
-      </c>
-      <c r="K94" s="114" t="s">
-        <v>471</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="K94" s="114"/>
       <c r="M94" s="103"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17519,56 +17598,47 @@
         <v>84</v>
       </c>
       <c r="C95" s="30" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="E95" s="111"/>
-      <c r="F95" s="111"/>
-      <c r="G95" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="H95" s="125"/>
+      <c r="F95" s="121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="124"/>
+      <c r="H95" s="57"/>
       <c r="I95" s="115"/>
       <c r="J95" s="114" t="s">
-        <v>538</v>
-      </c>
-      <c r="K95" s="114" t="s">
-        <v>471</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="K95" s="114"/>
       <c r="M95" s="103"/>
     </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="103"/>
       <c r="B96" s="0" t="n">
         <f aca="false">B95+1</f>
         <v>85</v>
       </c>
       <c r="C96" s="30" t="s">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="E96" s="111"/>
-      <c r="F96" s="111"/>
-      <c r="G96" s="30" t="n">
-        <v>12</v>
-      </c>
-      <c r="H96" s="125" t="s">
-        <v>465</v>
-      </c>
+      <c r="F96" s="121" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="124"/>
+      <c r="H96" s="57"/>
       <c r="I96" s="115"/>
       <c r="J96" s="114" t="s">
-        <v>513</v>
-      </c>
-      <c r="K96" s="114" t="s">
-        <v>471</v>
-      </c>
-      <c r="L96" s="0" t="s">
-        <v>514</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="K96" s="114"/>
       <c r="M96" s="103"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17578,24 +17648,22 @@
         <v>86</v>
       </c>
       <c r="C97" s="30" t="s">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="D97" s="30" t="s">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="E97" s="111"/>
-      <c r="F97" s="111"/>
-      <c r="G97" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="H97" s="125"/>
+      <c r="F97" s="121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G97" s="124"/>
+      <c r="H97" s="57"/>
       <c r="I97" s="115"/>
       <c r="J97" s="114" t="s">
-        <v>521</v>
-      </c>
-      <c r="K97" s="114" t="s">
-        <v>471</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="K97" s="114"/>
       <c r="M97" s="103"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17605,23 +17673,25 @@
         <v>87</v>
       </c>
       <c r="C98" s="30" t="s">
-        <v>549</v>
+        <v>565</v>
       </c>
       <c r="D98" s="30" t="s">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="E98" s="111"/>
-      <c r="F98" s="111"/>
-      <c r="G98" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="H98" s="125"/>
+      <c r="F98" s="121" t="n">
+        <v>4</v>
+      </c>
+      <c r="G98" s="124"/>
+      <c r="H98" s="57" t="s">
+        <v>328</v>
+      </c>
       <c r="I98" s="115"/>
       <c r="J98" s="114" t="s">
-        <v>1281</v>
+        <v>567</v>
       </c>
       <c r="K98" s="114" t="s">
-        <v>471</v>
+        <v>568</v>
       </c>
       <c r="M98" s="103"/>
     </row>
@@ -17632,24 +17702,22 @@
         <v>88</v>
       </c>
       <c r="C99" s="30" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="E99" s="111"/>
-      <c r="F99" s="111"/>
-      <c r="G99" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="H99" s="125"/>
+      <c r="F99" s="121" t="n">
+        <v>5</v>
+      </c>
+      <c r="G99" s="124"/>
+      <c r="H99" s="57"/>
       <c r="I99" s="115"/>
       <c r="J99" s="114" t="s">
-        <v>1282</v>
-      </c>
-      <c r="K99" s="114" t="s">
-        <v>471</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="K99" s="114"/>
       <c r="M99" s="103"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17659,380 +17727,222 @@
         <v>89</v>
       </c>
       <c r="C100" s="30" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="D100" s="30" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E100" s="111" t="n">
-        <v>15</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="E100" s="111"/>
       <c r="F100" s="121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="128"/>
-      <c r="H100" s="57" t="s">
-        <v>554</v>
-      </c>
-      <c r="I100" s="115"/>
+        <v>7</v>
+      </c>
+      <c r="G100" s="126"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="129"/>
       <c r="J100" s="114" t="s">
-        <v>555</v>
-      </c>
-      <c r="K100" s="114"/>
+        <v>574</v>
+      </c>
+      <c r="K100" s="114" t="s">
+        <v>568</v>
+      </c>
       <c r="M100" s="103"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="103"/>
-      <c r="B101" s="0" t="n">
-        <f aca="false">B100+1</f>
-        <v>90</v>
-      </c>
-      <c r="C101" s="30" t="s">
-        <v>556</v>
-      </c>
-      <c r="D101" s="30" t="s">
-        <v>557</v>
-      </c>
-      <c r="E101" s="111"/>
-      <c r="F101" s="121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="124"/>
-      <c r="H101" s="57"/>
-      <c r="I101" s="115"/>
-      <c r="J101" s="114" t="s">
-        <v>558</v>
-      </c>
-      <c r="K101" s="114"/>
       <c r="M101" s="103"/>
     </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="103"/>
-      <c r="B102" s="0" t="n">
-        <f aca="false">B101+1</f>
-        <v>91</v>
-      </c>
-      <c r="C102" s="30" t="s">
-        <v>559</v>
-      </c>
-      <c r="D102" s="30" t="s">
-        <v>560</v>
-      </c>
-      <c r="E102" s="111"/>
-      <c r="F102" s="121" t="n">
-        <v>2</v>
-      </c>
-      <c r="G102" s="124"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="115"/>
-      <c r="J102" s="114" t="s">
-        <v>561</v>
-      </c>
-      <c r="K102" s="114"/>
+      <c r="C102" s="130" t="s">
+        <v>575</v>
+      </c>
+      <c r="D102" s="130"/>
+      <c r="E102" s="130"/>
+      <c r="F102" s="130"/>
+      <c r="G102" s="130"/>
       <c r="M102" s="103"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="103"/>
-      <c r="B103" s="0" t="n">
-        <f aca="false">B102+1</f>
-        <v>92</v>
-      </c>
-      <c r="C103" s="30" t="s">
-        <v>562</v>
-      </c>
-      <c r="D103" s="30" t="s">
-        <v>563</v>
-      </c>
-      <c r="E103" s="111"/>
-      <c r="F103" s="121" t="n">
-        <v>3</v>
-      </c>
-      <c r="G103" s="124"/>
-      <c r="H103" s="57"/>
-      <c r="I103" s="115"/>
-      <c r="J103" s="114" t="s">
-        <v>564</v>
-      </c>
-      <c r="K103" s="114"/>
       <c r="M103" s="103"/>
     </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="103"/>
-      <c r="B104" s="0" t="n">
-        <f aca="false">B103+1</f>
-        <v>93</v>
-      </c>
-      <c r="C104" s="30" t="s">
-        <v>565</v>
-      </c>
-      <c r="D104" s="30" t="s">
-        <v>566</v>
-      </c>
-      <c r="E104" s="111"/>
-      <c r="F104" s="121" t="n">
-        <v>4</v>
-      </c>
-      <c r="G104" s="124"/>
-      <c r="H104" s="57" t="s">
-        <v>328</v>
-      </c>
-      <c r="I104" s="115"/>
-      <c r="J104" s="114" t="s">
-        <v>567</v>
-      </c>
-      <c r="K104" s="114" t="s">
-        <v>568</v>
-      </c>
+      <c r="C104" s="130" t="s">
+        <v>576</v>
+      </c>
+      <c r="D104" s="130"/>
+      <c r="E104" s="130"/>
+      <c r="F104" s="130"/>
+      <c r="G104" s="130"/>
       <c r="M104" s="103"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="103"/>
-      <c r="B105" s="0" t="n">
-        <f aca="false">B104+1</f>
-        <v>94</v>
-      </c>
-      <c r="C105" s="30" t="s">
-        <v>569</v>
-      </c>
-      <c r="D105" s="30" t="s">
-        <v>570</v>
-      </c>
-      <c r="E105" s="111"/>
-      <c r="F105" s="121" t="n">
-        <v>5</v>
-      </c>
-      <c r="G105" s="124"/>
-      <c r="H105" s="57"/>
-      <c r="I105" s="115"/>
-      <c r="J105" s="114" t="s">
-        <v>571</v>
-      </c>
-      <c r="K105" s="114"/>
       <c r="M105" s="103"/>
     </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="103"/>
-      <c r="B106" s="0" t="n">
-        <f aca="false">B105+1</f>
-        <v>95</v>
-      </c>
-      <c r="C106" s="30" t="s">
-        <v>572</v>
-      </c>
-      <c r="D106" s="30" t="s">
-        <v>573</v>
-      </c>
-      <c r="E106" s="111"/>
-      <c r="F106" s="121" t="n">
-        <v>7</v>
-      </c>
-      <c r="G106" s="126"/>
-      <c r="H106" s="57"/>
-      <c r="I106" s="129"/>
-      <c r="J106" s="114" t="s">
-        <v>574</v>
-      </c>
-      <c r="K106" s="114" t="s">
-        <v>568</v>
-      </c>
+      <c r="C106" s="131" t="s">
+        <v>577</v>
+      </c>
+      <c r="D106" s="131"/>
+      <c r="E106" s="131"/>
+      <c r="F106" s="131"/>
+      <c r="G106" s="131"/>
+      <c r="H106" s="131"/>
       <c r="M106" s="103"/>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="103"/>
+      <c r="C107" s="110" t="s">
+        <v>578</v>
+      </c>
+      <c r="D107" s="132" t="s">
+        <v>579</v>
+      </c>
+      <c r="E107" s="132"/>
+      <c r="F107" s="132"/>
+      <c r="G107" s="132"/>
+      <c r="H107" s="132" t="s">
+        <v>580</v>
+      </c>
+      <c r="I107" s="132"/>
+      <c r="J107" s="132"/>
+      <c r="K107" s="132"/>
       <c r="M107" s="103"/>
     </row>
-    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="103"/>
-      <c r="C108" s="130" t="s">
-        <v>575</v>
-      </c>
-      <c r="D108" s="130"/>
-      <c r="E108" s="130"/>
-      <c r="F108" s="130"/>
-      <c r="G108" s="130"/>
+      <c r="C108" s="110" t="s">
+        <v>581</v>
+      </c>
+      <c r="D108" s="132" t="s">
+        <v>582</v>
+      </c>
+      <c r="E108" s="132"/>
+      <c r="F108" s="132"/>
+      <c r="G108" s="132"/>
+      <c r="H108" s="133" t="s">
+        <v>583</v>
+      </c>
+      <c r="I108" s="133"/>
+      <c r="J108" s="133"/>
+      <c r="K108" s="133"/>
       <c r="M108" s="103"/>
     </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="103"/>
+      <c r="C109" s="110" t="s">
+        <v>584</v>
+      </c>
+      <c r="D109" s="132" t="s">
+        <v>585</v>
+      </c>
+      <c r="E109" s="132"/>
+      <c r="F109" s="132"/>
+      <c r="G109" s="132"/>
+      <c r="H109" s="132" t="s">
+        <v>586</v>
+      </c>
+      <c r="I109" s="132"/>
+      <c r="J109" s="132"/>
+      <c r="K109" s="132"/>
       <c r="M109" s="103"/>
     </row>
-    <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="103"/>
-      <c r="C110" s="130" t="s">
-        <v>576</v>
-      </c>
-      <c r="D110" s="130"/>
-      <c r="E110" s="130"/>
-      <c r="F110" s="130"/>
-      <c r="G110" s="130"/>
+      <c r="C110" s="110" t="s">
+        <v>587</v>
+      </c>
+      <c r="D110" s="132" t="s">
+        <v>588</v>
+      </c>
+      <c r="E110" s="132"/>
+      <c r="F110" s="132"/>
+      <c r="G110" s="132"/>
+      <c r="H110" s="132" t="s">
+        <v>589</v>
+      </c>
+      <c r="I110" s="132"/>
+      <c r="J110" s="132"/>
+      <c r="K110" s="132"/>
       <c r="M110" s="103"/>
     </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="103"/>
+      <c r="C111" s="110" t="s">
+        <v>590</v>
+      </c>
+      <c r="D111" s="132" t="s">
+        <v>591</v>
+      </c>
+      <c r="E111" s="132"/>
+      <c r="F111" s="132"/>
+      <c r="G111" s="132"/>
+      <c r="H111" s="132" t="s">
+        <v>592</v>
+      </c>
+      <c r="I111" s="132"/>
+      <c r="J111" s="132"/>
+      <c r="K111" s="132"/>
       <c r="M111" s="103"/>
     </row>
-    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="103"/>
-      <c r="C112" s="131" t="s">
-        <v>577</v>
-      </c>
-      <c r="D112" s="131"/>
-      <c r="E112" s="131"/>
-      <c r="F112" s="131"/>
-      <c r="G112" s="131"/>
-      <c r="H112" s="131"/>
+      <c r="C112" s="134" t="s">
+        <v>593</v>
+      </c>
+      <c r="D112" s="134"/>
+      <c r="E112" s="134"/>
+      <c r="F112" s="134"/>
       <c r="M112" s="103"/>
     </row>
-    <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="103"/>
-      <c r="C113" s="110" t="s">
-        <v>578</v>
-      </c>
-      <c r="D113" s="132" t="s">
-        <v>579</v>
-      </c>
-      <c r="E113" s="132"/>
-      <c r="F113" s="132"/>
-      <c r="G113" s="132"/>
-      <c r="H113" s="132" t="s">
-        <v>580</v>
-      </c>
-      <c r="I113" s="132"/>
-      <c r="J113" s="132"/>
-      <c r="K113" s="132"/>
+      <c r="C113" s="0" t="s">
+        <v>594</v>
+      </c>
       <c r="M113" s="103"/>
     </row>
-    <row r="114" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="103"/>
-      <c r="C114" s="110" t="s">
-        <v>581</v>
-      </c>
-      <c r="D114" s="132" t="s">
-        <v>582</v>
-      </c>
-      <c r="E114" s="132"/>
-      <c r="F114" s="132"/>
-      <c r="G114" s="132"/>
-      <c r="H114" s="133" t="s">
-        <v>583</v>
-      </c>
-      <c r="I114" s="133"/>
-      <c r="J114" s="133"/>
-      <c r="K114" s="133"/>
+      <c r="C114" s="0" t="s">
+        <v>595</v>
+      </c>
       <c r="M114" s="103"/>
     </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="103"/>
-      <c r="C115" s="110" t="s">
-        <v>584</v>
-      </c>
-      <c r="D115" s="132" t="s">
-        <v>585</v>
-      </c>
-      <c r="E115" s="132"/>
-      <c r="F115" s="132"/>
-      <c r="G115" s="132"/>
-      <c r="H115" s="132" t="s">
-        <v>586</v>
-      </c>
-      <c r="I115" s="132"/>
-      <c r="J115" s="132"/>
-      <c r="K115" s="132"/>
+      <c r="C115" s="134" t="s">
+        <v>596</v>
+      </c>
+      <c r="D115" s="134"/>
+      <c r="E115" s="134"/>
+      <c r="F115" s="134"/>
       <c r="M115" s="103"/>
     </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="103"/>
-      <c r="C116" s="110" t="s">
-        <v>587</v>
-      </c>
-      <c r="D116" s="132" t="s">
-        <v>588</v>
-      </c>
-      <c r="E116" s="132"/>
-      <c r="F116" s="132"/>
-      <c r="G116" s="132"/>
-      <c r="H116" s="132" t="s">
-        <v>589</v>
-      </c>
-      <c r="I116" s="132"/>
-      <c r="J116" s="132"/>
-      <c r="K116" s="132"/>
+      <c r="C116" s="0" t="s">
+        <v>597</v>
+      </c>
       <c r="M116" s="103"/>
     </row>
-    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="103"/>
-      <c r="C117" s="110" t="s">
-        <v>590</v>
-      </c>
-      <c r="D117" s="132" t="s">
-        <v>591</v>
-      </c>
-      <c r="E117" s="132"/>
-      <c r="F117" s="132"/>
-      <c r="G117" s="132"/>
-      <c r="H117" s="132" t="s">
-        <v>592</v>
-      </c>
-      <c r="I117" s="132"/>
-      <c r="J117" s="132"/>
-      <c r="K117" s="132"/>
+      <c r="B117" s="103"/>
+      <c r="C117" s="103"/>
+      <c r="D117" s="103"/>
+      <c r="E117" s="103"/>
+      <c r="F117" s="103"/>
+      <c r="G117" s="103"/>
+      <c r="H117" s="103"/>
+      <c r="I117" s="103"/>
+      <c r="J117" s="103"/>
+      <c r="K117" s="103"/>
+      <c r="L117" s="103"/>
       <c r="M117" s="103"/>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="103"/>
-      <c r="C118" s="134" t="s">
-        <v>593</v>
-      </c>
-      <c r="D118" s="134"/>
-      <c r="E118" s="134"/>
-      <c r="F118" s="134"/>
-      <c r="M118" s="103"/>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="103"/>
-      <c r="C119" s="0" t="s">
-        <v>594</v>
-      </c>
-      <c r="M119" s="103"/>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="103"/>
-      <c r="C120" s="0" t="s">
-        <v>595</v>
-      </c>
-      <c r="M120" s="103"/>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="103"/>
-      <c r="C121" s="134" t="s">
-        <v>596</v>
-      </c>
-      <c r="D121" s="134"/>
-      <c r="E121" s="134"/>
-      <c r="F121" s="134"/>
-      <c r="M121" s="103"/>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="103"/>
-      <c r="C122" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="M122" s="103"/>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="103"/>
-      <c r="B123" s="103"/>
-      <c r="C123" s="103"/>
-      <c r="D123" s="103"/>
-      <c r="E123" s="103"/>
-      <c r="F123" s="103"/>
-      <c r="G123" s="103"/>
-      <c r="H123" s="103"/>
-      <c r="I123" s="103"/>
-      <c r="J123" s="103"/>
-      <c r="K123" s="103"/>
-      <c r="L123" s="103"/>
-      <c r="M123" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="91">
@@ -18100,33 +18010,33 @@
     <mergeCell ref="H63:H68"/>
     <mergeCell ref="G65:G66"/>
     <mergeCell ref="G67:G68"/>
-    <mergeCell ref="E69:E99"/>
-    <mergeCell ref="F69:F83"/>
+    <mergeCell ref="E69:E93"/>
+    <mergeCell ref="F69:F80"/>
     <mergeCell ref="H69:H73"/>
-    <mergeCell ref="H74:H79"/>
-    <mergeCell ref="H80:H83"/>
-    <mergeCell ref="F84:F99"/>
-    <mergeCell ref="H84:H89"/>
-    <mergeCell ref="H90:H95"/>
-    <mergeCell ref="H96:H99"/>
-    <mergeCell ref="E100:E106"/>
-    <mergeCell ref="H100:H103"/>
-    <mergeCell ref="H104:H106"/>
-    <mergeCell ref="C108:G108"/>
-    <mergeCell ref="C110:G110"/>
-    <mergeCell ref="C112:H112"/>
-    <mergeCell ref="D113:G113"/>
-    <mergeCell ref="H113:K113"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="H114:K114"/>
-    <mergeCell ref="D115:G115"/>
-    <mergeCell ref="H115:K115"/>
-    <mergeCell ref="D116:G116"/>
-    <mergeCell ref="H116:K116"/>
-    <mergeCell ref="D117:G117"/>
-    <mergeCell ref="H117:K117"/>
-    <mergeCell ref="C118:F118"/>
-    <mergeCell ref="C121:F121"/>
+    <mergeCell ref="H74:H76"/>
+    <mergeCell ref="H77:H80"/>
+    <mergeCell ref="F81:F93"/>
+    <mergeCell ref="H81:H86"/>
+    <mergeCell ref="H87:H89"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="E94:E100"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="H98:H100"/>
+    <mergeCell ref="C102:G102"/>
+    <mergeCell ref="C104:G104"/>
+    <mergeCell ref="C106:H106"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="H107:K107"/>
+    <mergeCell ref="D108:G108"/>
+    <mergeCell ref="H108:K108"/>
+    <mergeCell ref="D109:G109"/>
+    <mergeCell ref="H109:K109"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="H110:K110"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="H111:K111"/>
+    <mergeCell ref="C112:F112"/>
+    <mergeCell ref="C115:F115"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
@@ -33139,7 +33049,7 @@
       <c r="I314" s="57"/>
       <c r="J314" s="57"/>
       <c r="K314" s="228" t="s">
-        <v>1302</v>
+        <v>1332</v>
       </c>
       <c r="L314" s="228"/>
       <c r="M314" s="228"/>
@@ -33179,7 +33089,7 @@
       <c r="I315" s="57"/>
       <c r="J315" s="57"/>
       <c r="K315" s="228" t="s">
-        <v>1303</v>
+        <v>1333</v>
       </c>
       <c r="L315" s="228"/>
       <c r="M315" s="228"/>
@@ -33219,7 +33129,7 @@
       <c r="I316" s="57"/>
       <c r="J316" s="57"/>
       <c r="K316" s="228" t="s">
-        <v>1304</v>
+        <v>1334</v>
       </c>
       <c r="L316" s="228"/>
       <c r="M316" s="228"/>
@@ -33259,7 +33169,7 @@
       <c r="I317" s="57"/>
       <c r="J317" s="57"/>
       <c r="K317" s="228" t="s">
-        <v>1305</v>
+        <v>1335</v>
       </c>
       <c r="L317" s="228"/>
       <c r="M317" s="228"/>
@@ -33299,7 +33209,7 @@
       <c r="I318" s="57"/>
       <c r="J318" s="57"/>
       <c r="K318" s="228" t="s">
-        <v>1306</v>
+        <v>1336</v>
       </c>
       <c r="L318" s="228"/>
       <c r="M318" s="228"/>
@@ -33339,7 +33249,7 @@
       <c r="I319" s="57"/>
       <c r="J319" s="57"/>
       <c r="K319" s="228" t="s">
-        <v>1307</v>
+        <v>1337</v>
       </c>
       <c r="L319" s="228"/>
       <c r="M319" s="228"/>
@@ -33857,7 +33767,7 @@
       <c r="I332" s="95"/>
       <c r="J332" s="95"/>
       <c r="K332" s="228" t="s">
-        <v>1308</v>
+        <v>1338</v>
       </c>
       <c r="L332" s="228"/>
       <c r="M332" s="228"/>
@@ -33899,7 +33809,7 @@
       <c r="I333" s="95"/>
       <c r="J333" s="95"/>
       <c r="K333" s="228" t="s">
-        <v>1309</v>
+        <v>1339</v>
       </c>
       <c r="L333" s="228"/>
       <c r="M333" s="228"/>
@@ -33938,7 +33848,7 @@
       <c r="I334" s="95"/>
       <c r="J334" s="95"/>
       <c r="K334" s="228" t="s">
-        <v>1310</v>
+        <v>1340</v>
       </c>
       <c r="L334" s="228"/>
       <c r="M334" s="228"/>
@@ -33977,7 +33887,7 @@
       <c r="I335" s="95"/>
       <c r="J335" s="95"/>
       <c r="K335" s="228" t="s">
-        <v>1311</v>
+        <v>1341</v>
       </c>
       <c r="L335" s="228"/>
       <c r="M335" s="228"/>
@@ -34016,7 +33926,7 @@
       <c r="I336" s="95"/>
       <c r="J336" s="95"/>
       <c r="K336" s="228" t="s">
-        <v>1312</v>
+        <v>1342</v>
       </c>
       <c r="L336" s="228"/>
       <c r="M336" s="228"/>
@@ -34055,7 +33965,7 @@
       <c r="I337" s="95"/>
       <c r="J337" s="95"/>
       <c r="K337" s="228" t="s">
-        <v>1313</v>
+        <v>1343</v>
       </c>
       <c r="L337" s="228"/>
       <c r="M337" s="228"/>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1376">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -6112,6 +6112,102 @@
   </si>
   <si>
     <t xml:space="preserve">11 = Unused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">![W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧[W]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] + [W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - [W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] - [W]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load [W] into DI.  Load [V] into DJ.  z set indicates DJ was 0.  n indicates DJ was negative.  Store DI into [V].   Increment V, Increment W, decrement A.  v set indicates A is negative after decrement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∧[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ∨[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V] ⊻[W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[V]; [W] → [V]; A-1 → A; V+o → V; W+o → W; {C+i → C}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V is the source address; A is the destination address; W is the number of bytes to copy (a multiple of 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The loop copies from offset W down to offset 8 (z is set when W reaches 0), so V and A start 8 below the source and destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wth A, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set A width to 4 bytes (A holds the destination address)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pul (A, V, W), S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull using stack S into registers in order W, V, A.  1 + 2 words each (S aligned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpy B, V+W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy into B the 64 bit value in address V+W.  1 + 4 words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpy A+W, B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy B into address A+W.  1 + 4 words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copies 8 bytes in 12 cycles (5 + 5 + 1 + 1, aligned, 16 bit data bus): 1.50 cycles per byte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W is the source address; V is the destination address; A + 1 is the number of 64 bit values to copy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull using stack S into registers in order W, V, A.  1 + 2 words each (S aligned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy the 64 bit value in address W into address V.  Increment W by 8.  Increment V by 8.  Decrement A by 1.  v is set when A is negative; vcpy repeats until then.  1 + 4 reads + 4 writes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copies 8 bytes in 9 cycles (aligned, 16 bit data bus): 1.13 cycles per byte</t>
   </si>
 </sst>
 </file>
@@ -9125,7 +9221,7 @@
       <c r="F2" s="107"/>
       <c r="G2" s="107"/>
       <c r="H2" s="102" t="s">
-        <v>1079</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9136,7 +9232,7 @@
       <c r="F3" s="107"/>
       <c r="G3" s="107"/>
       <c r="H3" s="102" t="s">
-        <v>1080</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9154,22 +9250,22 @@
         <v>0</v>
       </c>
       <c r="C5" s="127" t="s">
-        <v>1082</v>
+        <v>1361</v>
       </c>
       <c r="D5" s="102" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="102" t="s">
-        <v>1083</v>
+        <v>1362</v>
       </c>
       <c r="F5" s="102" t="s">
-        <v>1084</v>
+        <v>1363</v>
       </c>
       <c r="G5" s="102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="102" t="s">
-        <v>1085</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9191,7 +9287,7 @@
         <v>1089</v>
       </c>
       <c r="G6" s="102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" s="102" t="s">
         <v>1090</v>
@@ -9204,7 +9300,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="255" t="s">
-        <v>1091</v>
+        <v>1365</v>
       </c>
       <c r="D7" s="102" t="n">
         <v>2</v>
@@ -9215,11 +9311,11 @@
       <c r="F7" s="102" t="s">
         <v>1083</v>
       </c>
-      <c r="G7" s="102" t="s">
-        <v>1092</v>
+      <c r="G7" s="102" t="n">
+        <v>7</v>
       </c>
       <c r="H7" s="102" t="s">
-        <v>1093</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9236,7 +9332,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="127" t="s">
-        <v>1095</v>
+        <v>1367</v>
       </c>
       <c r="D9" s="102" t="s">
         <v>1096</v>
@@ -9247,11 +9343,11 @@
       <c r="F9" s="0" t="s">
         <v>960</v>
       </c>
-      <c r="G9" s="102" t="s">
-        <v>1097</v>
+      <c r="G9" s="102" t="n">
+        <v>5</v>
       </c>
       <c r="H9" s="102" t="s">
-        <v>1316</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9261,7 +9357,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="127" t="s">
-        <v>1099</v>
+        <v>1369</v>
       </c>
       <c r="D10" s="102" t="s">
         <v>1096</v>
@@ -9272,11 +9368,11 @@
       <c r="F10" s="0" t="s">
         <v>960</v>
       </c>
-      <c r="G10" s="102" t="s">
-        <v>1097</v>
+      <c r="G10" s="102" t="n">
+        <v>5</v>
       </c>
       <c r="H10" s="102" t="s">
-        <v>1100</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9341,7 +9437,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="119" t="s">
-        <v>1107</v>
+        <v>1371</v>
       </c>
       <c r="B14" s="119"/>
       <c r="C14" s="119"/>
@@ -9353,7 +9449,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H16" s="102" t="s">
-        <v>1108</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9382,7 +9478,7 @@
         <v>1084</v>
       </c>
       <c r="G18" s="102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9404,7 +9500,7 @@
         <v>1318</v>
       </c>
       <c r="G19" s="102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9425,8 +9521,11 @@
       <c r="F20" s="102" t="s">
         <v>1083</v>
       </c>
-      <c r="G20" s="102" t="s">
-        <v>1111</v>
+      <c r="G20" s="102" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="102" t="s">
+        <v>1373</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9450,11 +9549,11 @@
       <c r="E22" s="102" t="s">
         <v>1113</v>
       </c>
-      <c r="G22" s="102" t="s">
-        <v>1097</v>
+      <c r="G22" s="102" t="n">
+        <v>9</v>
       </c>
       <c r="H22" s="102" t="s">
-        <v>1114</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9469,7 +9568,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="119" t="s">
-        <v>1115</v>
+        <v>1375</v>
       </c>
       <c r="B24" s="119"/>
       <c r="C24" s="119"/>
@@ -17215,7 +17314,7 @@
       </c>
       <c r="I81" s="115"/>
       <c r="J81" s="114" t="s">
-        <v>513</v>
+        <v>1344</v>
       </c>
       <c r="K81" s="114" t="s">
         <v>471</v>
@@ -17245,7 +17344,7 @@
       <c r="H82" s="125"/>
       <c r="I82" s="127"/>
       <c r="J82" s="114" t="s">
-        <v>517</v>
+        <v>1345</v>
       </c>
       <c r="K82" s="114" t="s">
         <v>471</v>
@@ -17275,7 +17374,7 @@
       <c r="H83" s="125"/>
       <c r="I83" s="115"/>
       <c r="J83" s="114" t="s">
-        <v>521</v>
+        <v>1346</v>
       </c>
       <c r="K83" s="114" t="s">
         <v>471</v>
@@ -17305,7 +17404,7 @@
       <c r="H84" s="125"/>
       <c r="I84" s="115"/>
       <c r="J84" s="114" t="s">
-        <v>1274</v>
+        <v>1347</v>
       </c>
       <c r="K84" s="114" t="s">
         <v>471</v>
@@ -17332,7 +17431,7 @@
       <c r="H85" s="125"/>
       <c r="I85" s="115"/>
       <c r="J85" s="114" t="s">
-        <v>1275</v>
+        <v>1348</v>
       </c>
       <c r="K85" s="114" t="s">
         <v>471</v>
@@ -17359,7 +17458,7 @@
       <c r="H86" s="125"/>
       <c r="I86" s="115"/>
       <c r="J86" s="114" t="s">
-        <v>1276</v>
+        <v>1349</v>
       </c>
       <c r="K86" s="114" t="s">
         <v>471</v>
@@ -17388,7 +17487,7 @@
       </c>
       <c r="I87" s="115"/>
       <c r="J87" s="114" t="s">
-        <v>1277</v>
+        <v>1350</v>
       </c>
       <c r="K87" s="114" t="s">
         <v>471</v>
@@ -17415,7 +17514,7 @@
       <c r="H88" s="125"/>
       <c r="I88" s="115"/>
       <c r="J88" s="114" t="s">
-        <v>1279</v>
+        <v>1351</v>
       </c>
       <c r="K88" s="114" t="s">
         <v>471</v>
@@ -17442,7 +17541,7 @@
       <c r="H89" s="125"/>
       <c r="I89" s="115"/>
       <c r="J89" s="114" t="s">
-        <v>538</v>
+        <v>1352</v>
       </c>
       <c r="K89" s="114" t="s">
         <v>471</v>
@@ -17471,13 +17570,13 @@
       </c>
       <c r="I90" s="115"/>
       <c r="J90" s="114" t="s">
-        <v>513</v>
+        <v>1358</v>
       </c>
       <c r="K90" s="114" t="s">
         <v>471</v>
       </c>
       <c r="L90" s="0" t="s">
-        <v>514</v>
+        <v>1354</v>
       </c>
       <c r="M90" s="103"/>
     </row>
@@ -17501,7 +17600,7 @@
       <c r="H91" s="125"/>
       <c r="I91" s="115"/>
       <c r="J91" s="114" t="s">
-        <v>521</v>
+        <v>1355</v>
       </c>
       <c r="K91" s="114" t="s">
         <v>471</v>
@@ -17528,7 +17627,7 @@
       <c r="H92" s="125"/>
       <c r="I92" s="115"/>
       <c r="J92" s="114" t="s">
-        <v>1281</v>
+        <v>1356</v>
       </c>
       <c r="K92" s="114" t="s">
         <v>471</v>
@@ -17555,7 +17654,7 @@
       <c r="H93" s="125"/>
       <c r="I93" s="115"/>
       <c r="J93" s="114" t="s">
-        <v>1282</v>
+        <v>1357</v>
       </c>
       <c r="K93" s="114" t="s">
         <v>471</v>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="1376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2618" uniqueCount="1413">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -2881,7 +2881,7 @@
     <t xml:space="preserve">v, z, c</t>
   </si>
   <si>
-    <t xml:space="preserve">W must be assigned 0 initially.  A is the divisor, B is the quotient.  Y contains the dividend and W the remainder when v is set.   Repeat partial divide whilst v is not set.  z set indicates Y is zero.  c clear indicates W is zero.</t>
+    <t xml:space="preserve">W must be assigned 0 initially.  A is the divisor and Y the dividend.  B is the top half of the dividend: usually 0, but any value below A divides B and Y together, (B &lt;&lt; Y’s width) + Y.  Y contains the quotient and B the remainder when v is set.   Repeat partial divide whilst v is not set.  z set indicates Y is zero.  c clear indicates B is zero.</t>
   </si>
   <si>
     <t xml:space="preserve">Negate</t>
@@ -6209,6 +6209,117 @@
   <si>
     <t xml:space="preserve">Copies 8 bytes in 9 cycles (aligned, 16 bit data bus): 1.13 cycles per byte</t>
   </si>
+  <si>
+    <t xml:space="preserve">Sign or zero extension only applies to the second operand, when it is narrower than the operation (the width of the register operand, or 32 bits without one).  The first operand is never extended.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 ∧ O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 ∨ O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 ⊻ O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 ∧ O2:s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 + O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 - O2:s → O1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n, v, z, c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v is set as by subtract (and c is not borrow), so a signed comparison can branch on n ≠ v (braso (n, v)).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O1 - O2:s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n, v, z, c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copies bytes from the index in the first register to the second register for count bytes, index incrementing.  Subcopy ignores the set width of a register.    Source bytes past 63 read as 0 and destination bytes past 63 are dropped.  n and z are set from the second register at its width.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copies bits from index in first register to second register for count bits, index incrementing.  Subcopy ignores the set width of a register.    Source bits past 63 read as 0 and destination bits past 63 are dropped.  n and z are set from the second register at its width.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{P → [S]; S-2 → S}; O2 → C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+i → C; {P → [S]; S-2 → S}; C + O2 → C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtracts 1 from the interrupt depth.  e and l come back with P.  The stack can be S, V, W or Y.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C+i → C; C → [S]; S-4 → S; P → [S]; S-2 → S; [vector] → C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vector n (0 to 1023) is at FFFF:F000 + 4n.  Adds 1 to the interrupt depth.  Unlike an interrupt, brk leaves e and l as they are.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Without wake bits the processor stops until reset.  With wake bits (l, e0 to e3) it waits for one of those interrupts, even a disabled one: an enabled interrupt is taken (with C after stp), a disabled one continues after stp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8r → R; {8r - 1 → R}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The width in bits, or one less with gwth R, (Q, -1) (see the ror example).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c is set to O1:b[o1] after shifting.  v is set to O1:b[o1+1] after shifting.  A shift of 0 clears c and v.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c is set to O1:b[-1] after shifting.  v is set to O1:b[-2] after shifting.  n is set to O1:b[o1-1] before shifting.  A shift of 0 clears c and v.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pushed in the order A, B, S, V, W, X, Y, each at its width, with the values from before the stack register moves.  n and z are set from the last register pushed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pulled in the order Y, X, W, V, S, B, A (the reverse), each at its width.  n and z are set from the last register pulled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An immediate is pushed at its own width; the value at an address is pushed as 32 bits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always pulls 32 bits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W must be assigned 0 initially.  A and B are multiplicands.  Y contains the result when v is set.   Repeat partial multiply whilst v is not set. z set indicates Y is zero.  W counts B’s nybbles, two a step, so there is a step for each byte of B.  The first step clears Y, and the product is truncated to Y’s width.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W must be assigned 0 initially.  A is the divisor and Y the dividend.  B is the top half of the dividend: usually 0, but any value below A divides B and Y together, (B &lt;&lt; Y’s width) + Y.  Y contains the quotient and B the remainder when v is set.   Repeat partial divide whilst v is not set.  z set indicates Y is zero.  c clear indicates B is zero.  W counts Y’s nybbles, one a step.  The remainder is truncated to B’s width every step.  Dividing by 0 gives quotient nybbles of 15.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - R2:s → R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abs(R2:s) → R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scan first register from bit indexed by count register in direction until bit in first is high.  Pre-increment count if c set.  v set indicates no more bits.  c is always set.  When nothing is found the count is one past the end: the width in units going up, all ones going down.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Store R into [V].   Increment V, decrement A.  v set indicates A is negative after decrement.  It never stops early (its stop bits are ignored).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load [V] into D.  And D with R.  Store D into [V].  Increment V, decrement A.  v set indicates A is negative after decrement.  z set indicates D was 0.  n indicates D was negative.  Every block and vector operation but bcpy repeats (C stays on the opcode) until v is set or, if stopping is allowed, its stop condition (z set, z clear, n set or n clear) holds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Load [W] into D.  Store D into [V].   Increment V, Increment W, decrement A.  v set indicates A is negative after decrement.  z set indicates D was 0.  n indicates D was negative.  Like the block operations, it repeats until v is set or an allowed stop condition holds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p → R:b[N]; {p → R:b[N±1] … R:b[N±(count-1)]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With a repeat the flag is written to count bits (a register, or 0 to 63) from bit N up or down.  Bits outside 0 to 63 are dropped and the register’s width is ignored; 32 or more bits take a cycle more.</t>
+  </si>
 </sst>
 </file>
 
@@ -6221,7 +6332,7 @@
     <numFmt numFmtId="167" formatCode="#,###.0"/>
     <numFmt numFmtId="168" formatCode="#,###"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -6330,6 +6441,12 @@
       <color rgb="FFCCCCCC"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="24">
@@ -6689,7 +6806,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="272">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7766,6 +7883,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15319,6 +15448,9 @@
       <c r="K12" s="114" t="s">
         <v>254</v>
       </c>
+      <c r="L12" s="269" t="s">
+        <v>1376</v>
+      </c>
       <c r="M12" s="103"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15369,8 +15501,8 @@
       </c>
       <c r="H14" s="57"/>
       <c r="I14" s="115"/>
-      <c r="J14" s="114" t="s">
-        <v>261</v>
+      <c r="J14" s="270" t="s">
+        <v>1377</v>
       </c>
       <c r="K14" s="114" t="s">
         <v>254</v>
@@ -15425,8 +15557,8 @@
       </c>
       <c r="H16" s="57"/>
       <c r="I16" s="115"/>
-      <c r="J16" s="114" t="s">
-        <v>267</v>
+      <c r="J16" s="270" t="s">
+        <v>1378</v>
       </c>
       <c r="K16" s="114" t="s">
         <v>254</v>
@@ -15481,8 +15613,8 @@
       </c>
       <c r="H18" s="57"/>
       <c r="I18" s="115"/>
-      <c r="J18" s="114" t="s">
-        <v>1270</v>
+      <c r="J18" s="270" t="s">
+        <v>1379</v>
       </c>
       <c r="K18" s="114" t="s">
         <v>254</v>
@@ -15537,8 +15669,8 @@
       </c>
       <c r="H20" s="57"/>
       <c r="I20" s="115"/>
-      <c r="J20" s="114" t="s">
-        <v>1271</v>
+      <c r="J20" s="270" t="s">
+        <v>1380</v>
       </c>
       <c r="K20" s="114" t="s">
         <v>254</v>
@@ -15595,8 +15727,8 @@
       </c>
       <c r="H22" s="57"/>
       <c r="I22" s="115"/>
-      <c r="J22" s="114" t="s">
-        <v>287</v>
+      <c r="J22" s="270" t="s">
+        <v>1381</v>
       </c>
       <c r="K22" s="114" t="s">
         <v>285</v>
@@ -15651,8 +15783,8 @@
       </c>
       <c r="H24" s="57"/>
       <c r="I24" s="115"/>
-      <c r="J24" s="114" t="s">
-        <v>1272</v>
+      <c r="J24" s="270" t="s">
+        <v>1382</v>
       </c>
       <c r="K24" s="114" t="s">
         <v>285</v>
@@ -15685,8 +15817,11 @@
       <c r="J25" s="114" t="s">
         <v>297</v>
       </c>
-      <c r="K25" s="114" t="s">
-        <v>298</v>
+      <c r="K25" s="270" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L25" s="269" t="s">
+        <v>1384</v>
       </c>
       <c r="M25" s="103"/>
     </row>
@@ -15707,11 +15842,11 @@
       </c>
       <c r="H26" s="57"/>
       <c r="I26" s="115"/>
-      <c r="J26" s="114" t="s">
-        <v>1273</v>
-      </c>
-      <c r="K26" s="114" t="s">
-        <v>298</v>
+      <c r="J26" s="270" t="s">
+        <v>1385</v>
+      </c>
+      <c r="K26" s="270" t="s">
+        <v>1386</v>
       </c>
       <c r="M26" s="103"/>
     </row>
@@ -15746,8 +15881,8 @@
       <c r="K27" s="118" t="s">
         <v>254</v>
       </c>
-      <c r="L27" s="119" t="s">
-        <v>305</v>
+      <c r="L27" s="271" t="s">
+        <v>1387</v>
       </c>
       <c r="M27" s="103"/>
     </row>
@@ -15798,8 +15933,8 @@
       <c r="K29" s="114" t="s">
         <v>254</v>
       </c>
-      <c r="L29" s="0" t="s">
-        <v>310</v>
+      <c r="L29" s="269" t="s">
+        <v>1388</v>
       </c>
       <c r="M29" s="103"/>
     </row>
@@ -15828,8 +15963,8 @@
       <c r="I30" s="115" t="s">
         <v>312</v>
       </c>
-      <c r="J30" s="114" t="s">
-        <v>314</v>
+      <c r="J30" s="270" t="s">
+        <v>1389</v>
       </c>
       <c r="K30" s="114"/>
       <c r="M30" s="103"/>
@@ -15881,8 +16016,8 @@
       </c>
       <c r="H32" s="57"/>
       <c r="I32" s="115"/>
-      <c r="J32" s="114" t="s">
-        <v>321</v>
+      <c r="J32" s="270" t="s">
+        <v>1390</v>
       </c>
       <c r="K32" s="114"/>
       <c r="L32" s="0" t="s">
@@ -16056,6 +16191,9 @@
       <c r="K38" s="114" t="s">
         <v>337</v>
       </c>
+      <c r="L38" s="269" t="s">
+        <v>1391</v>
+      </c>
       <c r="M38" s="103"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16199,10 +16337,13 @@
       <c r="I43" s="115" t="s">
         <v>364</v>
       </c>
-      <c r="J43" s="114" t="s">
-        <v>365</v>
+      <c r="J43" s="270" t="s">
+        <v>1392</v>
       </c>
       <c r="K43" s="114"/>
+      <c r="L43" s="269" t="s">
+        <v>1393</v>
+      </c>
       <c r="M43" s="103"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16232,6 +16373,9 @@
         <v>369</v>
       </c>
       <c r="K44" s="114"/>
+      <c r="L44" s="269" t="s">
+        <v>1394</v>
+      </c>
       <c r="M44" s="103"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16255,10 +16399,13 @@
         <v>328</v>
       </c>
       <c r="I45" s="115"/>
-      <c r="J45" s="114" t="s">
-        <v>372</v>
+      <c r="J45" s="270" t="s">
+        <v>1395</v>
       </c>
       <c r="K45" s="114"/>
+      <c r="L45" s="269" t="s">
+        <v>1396</v>
+      </c>
       <c r="M45" s="103"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16479,8 +16626,8 @@
       <c r="K53" s="114" t="s">
         <v>400</v>
       </c>
-      <c r="L53" s="0" t="s">
-        <v>401</v>
+      <c r="L53" s="269" t="s">
+        <v>1397</v>
       </c>
       <c r="M53" s="103"/>
     </row>
@@ -16511,8 +16658,8 @@
       <c r="K54" s="114" t="s">
         <v>406</v>
       </c>
-      <c r="L54" s="0" t="s">
-        <v>407</v>
+      <c r="L54" s="269" t="s">
+        <v>1398</v>
       </c>
       <c r="M54" s="103"/>
     </row>
@@ -16547,6 +16694,9 @@
       <c r="K55" s="114" t="s">
         <v>254</v>
       </c>
+      <c r="L55" s="269" t="s">
+        <v>1399</v>
+      </c>
       <c r="M55" s="103"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16576,6 +16726,9 @@
       <c r="K56" s="114" t="s">
         <v>254</v>
       </c>
+      <c r="L56" s="269" t="s">
+        <v>1400</v>
+      </c>
       <c r="M56" s="103"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16605,6 +16758,9 @@
         <v>417</v>
       </c>
       <c r="K57" s="114"/>
+      <c r="L57" s="269" t="s">
+        <v>1401</v>
+      </c>
       <c r="M57" s="103"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16630,6 +16786,9 @@
         <v>419</v>
       </c>
       <c r="K58" s="114"/>
+      <c r="L58" s="269" t="s">
+        <v>1402</v>
+      </c>
       <c r="M58" s="103"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16663,8 +16822,8 @@
       <c r="K59" s="114" t="s">
         <v>424</v>
       </c>
-      <c r="L59" s="0" t="s">
-        <v>425</v>
+      <c r="L59" s="269" t="s">
+        <v>1403</v>
       </c>
       <c r="M59" s="103"/>
     </row>
@@ -16693,8 +16852,8 @@
       <c r="K60" s="114" t="s">
         <v>429</v>
       </c>
-      <c r="L60" s="0" t="s">
-        <v>430</v>
+      <c r="L60" s="269" t="s">
+        <v>1404</v>
       </c>
       <c r="M60" s="103"/>
     </row>
@@ -16719,8 +16878,8 @@
         <v>282</v>
       </c>
       <c r="I61" s="115"/>
-      <c r="J61" s="114" t="s">
-        <v>433</v>
+      <c r="J61" s="270" t="s">
+        <v>1405</v>
       </c>
       <c r="K61" s="114" t="s">
         <v>254</v>
@@ -16746,8 +16905,8 @@
       </c>
       <c r="H62" s="57"/>
       <c r="I62" s="115"/>
-      <c r="J62" s="114" t="s">
-        <v>436</v>
+      <c r="J62" s="270" t="s">
+        <v>1406</v>
       </c>
       <c r="K62" s="114" t="s">
         <v>254</v>
@@ -16786,8 +16945,8 @@
       <c r="K63" s="114" t="s">
         <v>441</v>
       </c>
-      <c r="L63" s="0" t="s">
-        <v>442</v>
+      <c r="L63" s="269" t="s">
+        <v>1407</v>
       </c>
       <c r="M63" s="103"/>
     </row>
@@ -16966,8 +17125,8 @@
       <c r="K69" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="L69" s="0" t="s">
-        <v>467</v>
+      <c r="L69" s="269" t="s">
+        <v>1408</v>
       </c>
       <c r="M69" s="103"/>
     </row>
@@ -16996,8 +17155,8 @@
       <c r="K70" s="114" t="s">
         <v>471</v>
       </c>
-      <c r="L70" s="0" t="s">
-        <v>472</v>
+      <c r="L70" s="269" t="s">
+        <v>1409</v>
       </c>
       <c r="M70" s="103"/>
     </row>
@@ -17319,8 +17478,8 @@
       <c r="K81" s="114" t="s">
         <v>471</v>
       </c>
-      <c r="L81" s="0" t="s">
-        <v>514</v>
+      <c r="L81" s="269" t="s">
+        <v>1410</v>
       </c>
       <c r="M81" s="103"/>
     </row>
@@ -17813,10 +17972,13 @@
       <c r="G99" s="124"/>
       <c r="H99" s="57"/>
       <c r="I99" s="115"/>
-      <c r="J99" s="114" t="s">
-        <v>571</v>
+      <c r="J99" s="270" t="s">
+        <v>1411</v>
       </c>
       <c r="K99" s="114"/>
+      <c r="L99" s="269" t="s">
+        <v>1412</v>
+      </c>
       <c r="M99" s="103"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -5274,7 +5274,7 @@
     <t xml:space="preserve">Setup:</t>
   </si>
   <si>
-    <t xml:space="preserve">wtth (X, Y), 4</t>
+    <t xml:space="preserve">wtth (X, Y), 32</t>
   </si>
   <si>
     <t xml:space="preserve">Multi Register</t>
@@ -5289,16 +5289,16 @@
     <t xml:space="preserve">wth W, 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Set B width to 4 bytes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wth B, 8</t>
+    <t xml:space="preserve">Set B width to 32 bits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wth B, 64</t>
   </si>
   <si>
     <t xml:space="preserve">Embedded 8</t>
   </si>
   <si>
-    <t xml:space="preserve">Set B width to 8 bytes</t>
+    <t xml:space="preserve">Set B width to 64 bits</t>
   </si>
   <si>
     <t xml:space="preserve">pul (W, X, Y), S</t>
@@ -5355,7 +5355,7 @@
     <t xml:space="preserve">W is the source address; V is the destination address; A is the number of iterations.</t>
   </si>
   <si>
-    <t xml:space="preserve">wth A, 4</t>
+    <t xml:space="preserve">wth A, 32</t>
   </si>
   <si>
     <t xml:space="preserve">pul (A, X, Y), S</t>
@@ -6165,7 +6165,7 @@
     <t xml:space="preserve">The loop copies from offset W down to offset 8 (z is set when W reaches 0), so V and A start 8 below the source and destination</t>
   </si>
   <si>
-    <t xml:space="preserve">wth A, 4</t>
+    <t xml:space="preserve">wth A, 32</t>
   </si>
   <si>
     <t xml:space="preserve">Register</t>
@@ -6174,7 +6174,7 @@
     <t xml:space="preserve">Embedded 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Set A width to 4 bytes (A holds the destination address)</t>
+    <t xml:space="preserve">Set A width to 32 bits (A holds the destination address)</t>
   </si>
   <si>
     <t xml:space="preserve">pul (A, V, W), S</t>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2632" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1297">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -3038,7 +3038,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">cpx</t>
+    <t xml:space="preserve">cpyx</t>
   </si>
   <si>
     <t xml:space="preserve">O2:o → R</t>
@@ -6035,6 +6035,30 @@
   </si>
   <si>
     <t xml:space="preserve">r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8, -4, 4, 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy a value of a given width in memory into a register zero extended.  With swap the register's low o bits (zero extended when o is wider than the register) are written to memory.  A value wider than the register is truncated.  n and z are set from the value copied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy Extend (sign extend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8, 16, 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 = Copy Extend (sign extend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware, State, Copy Extend (sign extend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O2:o:s → R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy a value of a given width in memory into a register sign extended.  A value wider than the register is truncated.  n and z are set from the value copied.  The zero extending copy (and the copy into memory) is code 12 extend 3; there is no room for this one there.</t>
   </si>
 </sst>
 </file>
@@ -15021,7 +15045,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:M120"/>
+  <dimension ref="A2:M121"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="2.64"/>
@@ -16447,9 +16471,11 @@
       <c r="J55" s="115" t="s">
         <v>414</v>
       </c>
-      <c r="K55" s="115"/>
+      <c r="K55" s="115" t="s">
+        <v>257</v>
+      </c>
       <c r="L55" s="54" t="s">
-        <v>415</v>
+        <v>1290</v>
       </c>
       <c r="M55" s="104"/>
     </row>
@@ -17844,142 +17870,157 @@
         <v>92</v>
       </c>
       <c r="C103" s="30" t="s">
-        <v>590</v>
+        <v>1291</v>
       </c>
       <c r="D103" s="30" t="s">
-        <v>591</v>
+        <v>413</v>
       </c>
       <c r="E103" s="112"/>
       <c r="F103" s="123" t="n">
-        <v>7</v>
-      </c>
-      <c r="G103" s="130"/>
-      <c r="H103" s="58"/>
-      <c r="I103" s="134"/>
+        <v>6</v>
+      </c>
+      <c r="G103" s="128"/>
+      <c r="H103" s="58" t="s">
+        <v>254</v>
+      </c>
+      <c r="I103" s="126"/>
       <c r="J103" s="115" t="s">
-        <v>592</v>
+        <v>1295</v>
       </c>
       <c r="K103" s="115" t="s">
-        <v>585</v>
+        <v>257</v>
+      </c>
+      <c r="L103" s="117" t="s">
+        <v>1296</v>
       </c>
       <c r="M103" s="104"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="104"/>
+      <c r="B104" s="54" t="n">
+        <f aca="false">B103+1</f>
+        <v>93</v>
+      </c>
+      <c r="C104" s="30" t="s">
+        <v>590</v>
+      </c>
+      <c r="D104" s="30" t="s">
+        <v>591</v>
+      </c>
+      <c r="E104" s="112"/>
+      <c r="F104" s="123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G104" s="130"/>
+      <c r="H104" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="I104" s="134"/>
+      <c r="J104" s="115" t="s">
+        <v>592</v>
+      </c>
+      <c r="K104" s="115" t="s">
+        <v>585</v>
+      </c>
       <c r="M104" s="104"/>
     </row>
-    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="104"/>
-      <c r="C105" s="135" t="s">
+      <c r="M105" s="104"/>
+    </row>
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="104"/>
+      <c r="C106" s="135" t="s">
         <v>593</v>
       </c>
-      <c r="D105" s="135"/>
-      <c r="E105" s="135"/>
-      <c r="F105" s="135"/>
-      <c r="G105" s="135"/>
-      <c r="M105" s="104"/>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="104"/>
+      <c r="D106" s="135"/>
+      <c r="E106" s="135"/>
+      <c r="F106" s="135"/>
+      <c r="G106" s="135"/>
       <c r="M106" s="104"/>
     </row>
-    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="104"/>
-      <c r="C107" s="135" t="s">
+      <c r="M107" s="104"/>
+    </row>
+    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="104"/>
+      <c r="C108" s="135" t="s">
         <v>594</v>
       </c>
-      <c r="D107" s="135"/>
-      <c r="E107" s="135"/>
-      <c r="F107" s="135"/>
-      <c r="G107" s="135"/>
-      <c r="M107" s="104"/>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="104"/>
+      <c r="D108" s="135"/>
+      <c r="E108" s="135"/>
+      <c r="F108" s="135"/>
+      <c r="G108" s="135"/>
       <c r="M108" s="104"/>
     </row>
-    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="104"/>
-      <c r="C109" s="136" t="s">
-        <v>595</v>
-      </c>
-      <c r="D109" s="136"/>
-      <c r="E109" s="136"/>
-      <c r="F109" s="136"/>
-      <c r="G109" s="136"/>
-      <c r="H109" s="136"/>
       <c r="M109" s="104"/>
     </row>
     <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="104"/>
-      <c r="C110" s="111" t="s">
-        <v>596</v>
-      </c>
-      <c r="D110" s="137" t="s">
-        <v>597</v>
-      </c>
-      <c r="E110" s="137"/>
-      <c r="F110" s="137"/>
-      <c r="G110" s="137"/>
-      <c r="H110" s="137" t="s">
-        <v>598</v>
-      </c>
-      <c r="I110" s="137"/>
-      <c r="J110" s="137"/>
-      <c r="K110" s="137"/>
+      <c r="C110" s="136" t="s">
+        <v>595</v>
+      </c>
+      <c r="D110" s="136"/>
+      <c r="E110" s="136"/>
+      <c r="F110" s="136"/>
+      <c r="G110" s="136"/>
+      <c r="H110" s="136"/>
       <c r="M110" s="104"/>
     </row>
-    <row r="111" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="104"/>
       <c r="C111" s="111" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D111" s="137" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E111" s="137"/>
       <c r="F111" s="137"/>
       <c r="G111" s="137"/>
-      <c r="H111" s="138" t="s">
-        <v>601</v>
-      </c>
-      <c r="I111" s="138"/>
-      <c r="J111" s="138"/>
-      <c r="K111" s="138"/>
+      <c r="H111" s="137" t="s">
+        <v>598</v>
+      </c>
+      <c r="I111" s="137"/>
+      <c r="J111" s="137"/>
+      <c r="K111" s="137"/>
       <c r="M111" s="104"/>
     </row>
-    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="46.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="104"/>
       <c r="C112" s="111" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D112" s="137" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E112" s="137"/>
       <c r="F112" s="137"/>
       <c r="G112" s="137"/>
-      <c r="H112" s="137" t="s">
-        <v>604</v>
-      </c>
-      <c r="I112" s="137"/>
-      <c r="J112" s="137"/>
-      <c r="K112" s="137"/>
+      <c r="H112" s="138" t="s">
+        <v>601</v>
+      </c>
+      <c r="I112" s="138"/>
+      <c r="J112" s="138"/>
+      <c r="K112" s="138"/>
       <c r="M112" s="104"/>
     </row>
     <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="104"/>
       <c r="C113" s="111" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D113" s="137" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E113" s="137"/>
       <c r="F113" s="137"/>
       <c r="G113" s="137"/>
       <c r="H113" s="137" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="I113" s="137"/>
       <c r="J113" s="137"/>
@@ -17989,77 +18030,96 @@
     <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="104"/>
       <c r="C114" s="111" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D114" s="137" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E114" s="137"/>
       <c r="F114" s="137"/>
       <c r="G114" s="137"/>
       <c r="H114" s="137" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="I114" s="137"/>
       <c r="J114" s="137"/>
       <c r="K114" s="137"/>
       <c r="M114" s="104"/>
     </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="104"/>
-      <c r="C115" s="139" t="s">
-        <v>611</v>
-      </c>
-      <c r="D115" s="139"/>
-      <c r="E115" s="139"/>
-      <c r="F115" s="139"/>
+      <c r="C115" s="111" t="s">
+        <v>608</v>
+      </c>
+      <c r="D115" s="137" t="s">
+        <v>609</v>
+      </c>
+      <c r="E115" s="137"/>
+      <c r="F115" s="137"/>
+      <c r="G115" s="137"/>
+      <c r="H115" s="137" t="s">
+        <v>610</v>
+      </c>
+      <c r="I115" s="137"/>
+      <c r="J115" s="137"/>
+      <c r="K115" s="137"/>
       <c r="M115" s="104"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="104"/>
-      <c r="C116" s="54" t="s">
-        <v>612</v>
-      </c>
+      <c r="C116" s="139" t="s">
+        <v>611</v>
+      </c>
+      <c r="D116" s="139"/>
+      <c r="E116" s="139"/>
+      <c r="F116" s="139"/>
       <c r="M116" s="104"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="104"/>
       <c r="C117" s="54" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="M117" s="104"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="104"/>
-      <c r="C118" s="139" t="s">
-        <v>614</v>
-      </c>
-      <c r="D118" s="139"/>
-      <c r="E118" s="139"/>
-      <c r="F118" s="139"/>
+      <c r="C118" s="54" t="s">
+        <v>613</v>
+      </c>
       <c r="M118" s="104"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="104"/>
-      <c r="C119" s="54" t="s">
-        <v>615</v>
-      </c>
+      <c r="C119" s="139" t="s">
+        <v>614</v>
+      </c>
+      <c r="D119" s="139"/>
+      <c r="E119" s="139"/>
+      <c r="F119" s="139"/>
       <c r="M119" s="104"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="104"/>
-      <c r="B120" s="104"/>
-      <c r="C120" s="104"/>
-      <c r="D120" s="104"/>
-      <c r="E120" s="104"/>
-      <c r="F120" s="104"/>
-      <c r="G120" s="104"/>
-      <c r="H120" s="104"/>
-      <c r="I120" s="104"/>
-      <c r="J120" s="104"/>
-      <c r="K120" s="104"/>
-      <c r="L120" s="104"/>
+      <c r="C120" s="54" t="s">
+        <v>615</v>
+      </c>
       <c r="M120" s="104"/>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="104"/>
+      <c r="B121" s="104"/>
+      <c r="C121" s="104"/>
+      <c r="D121" s="104"/>
+      <c r="E121" s="104"/>
+      <c r="F121" s="104"/>
+      <c r="G121" s="104"/>
+      <c r="H121" s="104"/>
+      <c r="I121" s="104"/>
+      <c r="J121" s="104"/>
+      <c r="K121" s="104"/>
+      <c r="L121" s="104"/>
+      <c r="M121" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="92">
@@ -18137,14 +18197,12 @@
     <mergeCell ref="H84:H89"/>
     <mergeCell ref="H90:H92"/>
     <mergeCell ref="H93:H96"/>
-    <mergeCell ref="E97:E103"/>
+    <mergeCell ref="E97:E104"/>
     <mergeCell ref="H97:H100"/>
-    <mergeCell ref="H101:H103"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C107:G107"/>
-    <mergeCell ref="C109:H109"/>
-    <mergeCell ref="D110:G110"/>
-    <mergeCell ref="H110:K110"/>
+    <mergeCell ref="H101:H102"/>
+    <mergeCell ref="C106:G106"/>
+    <mergeCell ref="C108:G108"/>
+    <mergeCell ref="C110:H110"/>
     <mergeCell ref="D111:G111"/>
     <mergeCell ref="H111:K111"/>
     <mergeCell ref="D112:G112"/>
@@ -18153,8 +18211,10 @@
     <mergeCell ref="H113:K113"/>
     <mergeCell ref="D114:G114"/>
     <mergeCell ref="H114:K114"/>
-    <mergeCell ref="C115:F115"/>
-    <mergeCell ref="C118:F118"/>
+    <mergeCell ref="D115:G115"/>
+    <mergeCell ref="H115:K115"/>
+    <mergeCell ref="C116:F116"/>
+    <mergeCell ref="C119:F119"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
@@ -19529,7 +19589,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AK359"/>
+  <dimension ref="A1:AK364"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="2.64"/>
@@ -27434,7 +27494,9 @@
         <v>755</v>
       </c>
       <c r="K179" s="110"/>
-      <c r="L179" s="110"/>
+      <c r="L179" s="110" t="s">
+        <v>697</v>
+      </c>
       <c r="M179" s="58" t="s">
         <v>728</v>
       </c>
@@ -27486,7 +27548,9 @@
         <v>696</v>
       </c>
       <c r="K180" s="58"/>
-      <c r="L180" s="58"/>
+      <c r="L180" s="58" t="n">
+        <v>1</v>
+      </c>
       <c r="M180" s="94" t="s">
         <v>857</v>
       </c>
@@ -27528,7 +27592,7 @@
       <c r="H181" s="58"/>
       <c r="I181" s="58"/>
       <c r="J181" s="58" t="s">
-        <v>845</v>
+        <v>1289</v>
       </c>
       <c r="K181" s="58"/>
       <c r="L181" s="58"/>
@@ -27609,8 +27673,8 @@
         <v>715</v>
       </c>
       <c r="K183" s="58"/>
-      <c r="L183" s="149" t="s">
-        <v>707</v>
+      <c r="L183" s="149" t="n">
+        <v>0</v>
       </c>
       <c r="M183" s="95"/>
       <c r="N183" s="205"/>
@@ -29182,7 +29246,7 @@
       <c r="N218" s="110"/>
       <c r="O218" s="110"/>
       <c r="P218" s="58" t="s">
-        <v>886</v>
+        <v>1294</v>
       </c>
       <c r="Q218" s="58"/>
       <c r="R218" s="58"/>
@@ -31462,23 +31526,23 @@
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="104"/>
       <c r="B273" s="54" t="s">
-        <v>590</v>
+        <v>1291</v>
       </c>
       <c r="C273" s="104"/>
-      <c r="D273" s="158" t="s">
+      <c r="D273" s="110" t="s">
         <v>681</v>
       </c>
-      <c r="E273" s="158"/>
-      <c r="F273" s="158"/>
-      <c r="G273" s="158" t="s">
+      <c r="E273" s="110"/>
+      <c r="F273" s="110" t="s">
         <v>682</v>
       </c>
-      <c r="H273" s="158"/>
-      <c r="I273" s="158"/>
-      <c r="J273" s="58" t="s">
-        <v>744</v>
-      </c>
-      <c r="K273" s="58"/>
+      <c r="G273" s="110"/>
+      <c r="H273" s="110"/>
+      <c r="I273" s="110"/>
+      <c r="J273" s="110"/>
+      <c r="K273" s="58" t="s">
+        <v>861</v>
+      </c>
       <c r="L273" s="58"/>
       <c r="M273" s="110" t="s">
         <v>772</v>
@@ -31490,44 +31554,49 @@
       <c r="R273" s="58"/>
       <c r="S273" s="58"/>
       <c r="T273" s="104"/>
-      <c r="U273" s="169" t="s">
-        <v>719</v>
-      </c>
-      <c r="V273" s="169"/>
-      <c r="W273" s="169"/>
-      <c r="X273" s="169"/>
-      <c r="Y273" s="169"/>
-      <c r="Z273" s="169"/>
-      <c r="AA273" s="169"/>
-      <c r="AB273" s="169"/>
-      <c r="AC273" s="169"/>
-      <c r="AD273" s="169"/>
-      <c r="AE273" s="169"/>
-      <c r="AF273" s="169"/>
-      <c r="AG273" s="169"/>
-      <c r="AH273" s="169"/>
-      <c r="AI273" s="169"/>
-      <c r="AJ273" s="169"/>
+      <c r="U273" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="V273" s="110"/>
+      <c r="W273" s="110"/>
+      <c r="X273" s="110"/>
+      <c r="Y273" s="110"/>
+      <c r="Z273" s="110"/>
+      <c r="AA273" s="110"/>
+      <c r="AB273" s="110"/>
+      <c r="AC273" s="110"/>
+      <c r="AD273" s="110"/>
+      <c r="AE273" s="110"/>
+      <c r="AF273" s="110"/>
+      <c r="AG273" s="110"/>
+      <c r="AH273" s="110"/>
+      <c r="AI273" s="110"/>
+      <c r="AJ273" s="110"/>
       <c r="AK273" s="104"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="104"/>
+      <c r="B274" s="104"/>
       <c r="C274" s="104"/>
       <c r="D274" s="58" t="s">
-        <v>898</v>
+        <v>625</v>
       </c>
       <c r="E274" s="58"/>
-      <c r="F274" s="58"/>
-      <c r="G274" s="162" t="s">
-        <v>898</v>
-      </c>
-      <c r="H274" s="162"/>
+      <c r="F274" s="162" t="s">
+        <v>685</v>
+      </c>
+      <c r="G274" s="162"/>
+      <c r="H274" s="162" t="s">
+        <v>686</v>
+      </c>
       <c r="I274" s="162"/>
-      <c r="J274" s="189"/>
-      <c r="K274" s="190"/>
-      <c r="L274" s="191"/>
+      <c r="J274" s="162"/>
+      <c r="K274" s="58" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L274" s="58"/>
       <c r="M274" s="58" t="s">
-        <v>912</v>
+        <v>1293</v>
       </c>
       <c r="N274" s="58"/>
       <c r="O274" s="58"/>
@@ -31536,39 +31605,45 @@
       <c r="R274" s="58"/>
       <c r="S274" s="58"/>
       <c r="T274" s="104"/>
-      <c r="U274" s="169"/>
-      <c r="V274" s="169"/>
-      <c r="W274" s="169"/>
-      <c r="X274" s="169"/>
-      <c r="Y274" s="169"/>
-      <c r="Z274" s="169"/>
-      <c r="AA274" s="169"/>
-      <c r="AB274" s="169"/>
-      <c r="AC274" s="169"/>
-      <c r="AD274" s="169"/>
-      <c r="AE274" s="169"/>
-      <c r="AF274" s="169"/>
-      <c r="AG274" s="169"/>
-      <c r="AH274" s="169"/>
-      <c r="AI274" s="169"/>
-      <c r="AJ274" s="169"/>
+      <c r="U274" s="161" t="s">
+        <v>864</v>
+      </c>
+      <c r="V274" s="161"/>
+      <c r="W274" s="161"/>
+      <c r="X274" s="161"/>
+      <c r="Y274" s="161"/>
+      <c r="Z274" s="161"/>
+      <c r="AA274" s="161"/>
+      <c r="AB274" s="161"/>
+      <c r="AC274" s="161"/>
+      <c r="AD274" s="161"/>
+      <c r="AE274" s="161"/>
+      <c r="AF274" s="161"/>
+      <c r="AG274" s="161"/>
+      <c r="AH274" s="161"/>
+      <c r="AI274" s="161"/>
+      <c r="AJ274" s="161"/>
       <c r="AK274" s="104"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="104"/>
+      <c r="B275" s="104"/>
       <c r="C275" s="104"/>
       <c r="D275" s="58" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="E275" s="58"/>
-      <c r="F275" s="58"/>
-      <c r="G275" s="162" t="s">
-        <v>856</v>
-      </c>
-      <c r="H275" s="162"/>
+      <c r="F275" s="162" t="s">
+        <v>732</v>
+      </c>
+      <c r="G275" s="162"/>
+      <c r="H275" s="162" t="s">
+        <v>866</v>
+      </c>
       <c r="I275" s="162"/>
-      <c r="J275" s="216"/>
-      <c r="L275" s="132"/>
+      <c r="J275" s="162"/>
+      <c r="K275" s="58"/>
+      <c r="L275" s="58"/>
       <c r="M275" s="58"/>
       <c r="N275" s="58"/>
       <c r="O275" s="58"/>
@@ -31577,36 +31652,37 @@
       <c r="R275" s="58"/>
       <c r="S275" s="58"/>
       <c r="T275" s="104"/>
-      <c r="U275" s="169"/>
-      <c r="V275" s="169"/>
-      <c r="W275" s="169"/>
-      <c r="X275" s="169"/>
-      <c r="Y275" s="169"/>
-      <c r="Z275" s="169"/>
-      <c r="AA275" s="169"/>
-      <c r="AB275" s="169"/>
-      <c r="AC275" s="169"/>
-      <c r="AD275" s="169"/>
-      <c r="AE275" s="169"/>
-      <c r="AF275" s="169"/>
-      <c r="AG275" s="169"/>
-      <c r="AH275" s="169"/>
-      <c r="AI275" s="169"/>
-      <c r="AJ275" s="169"/>
+      <c r="U275" s="161"/>
+      <c r="V275" s="161"/>
+      <c r="W275" s="161"/>
+      <c r="X275" s="161"/>
+      <c r="Y275" s="161"/>
+      <c r="Z275" s="161"/>
+      <c r="AA275" s="161"/>
+      <c r="AB275" s="161"/>
+      <c r="AC275" s="161"/>
+      <c r="AD275" s="161"/>
+      <c r="AE275" s="161"/>
+      <c r="AF275" s="161"/>
+      <c r="AG275" s="161"/>
+      <c r="AH275" s="161"/>
+      <c r="AI275" s="161"/>
+      <c r="AJ275" s="161"/>
       <c r="AK275" s="104"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="104"/>
+      <c r="B276" s="104"/>
       <c r="C276" s="104"/>
       <c r="D276" s="58"/>
       <c r="E276" s="58"/>
-      <c r="F276" s="58"/>
+      <c r="F276" s="162"/>
       <c r="G276" s="162"/>
       <c r="H276" s="162"/>
       <c r="I276" s="162"/>
-      <c r="J276" s="196"/>
-      <c r="K276" s="197"/>
-      <c r="L276" s="198"/>
+      <c r="J276" s="162"/>
+      <c r="K276" s="58"/>
+      <c r="L276" s="58"/>
       <c r="M276" s="58"/>
       <c r="N276" s="58"/>
       <c r="O276" s="58"/>
@@ -31615,22 +31691,22 @@
       <c r="R276" s="58"/>
       <c r="S276" s="58"/>
       <c r="T276" s="104"/>
-      <c r="U276" s="169"/>
-      <c r="V276" s="169"/>
-      <c r="W276" s="169"/>
-      <c r="X276" s="169"/>
-      <c r="Y276" s="169"/>
-      <c r="Z276" s="169"/>
-      <c r="AA276" s="169"/>
-      <c r="AB276" s="169"/>
-      <c r="AC276" s="169"/>
-      <c r="AD276" s="169"/>
-      <c r="AE276" s="169"/>
-      <c r="AF276" s="169"/>
-      <c r="AG276" s="169"/>
-      <c r="AH276" s="169"/>
-      <c r="AI276" s="169"/>
-      <c r="AJ276" s="169"/>
+      <c r="U276" s="161"/>
+      <c r="V276" s="161"/>
+      <c r="W276" s="161"/>
+      <c r="X276" s="161"/>
+      <c r="Y276" s="161"/>
+      <c r="Z276" s="161"/>
+      <c r="AA276" s="161"/>
+      <c r="AB276" s="161"/>
+      <c r="AC276" s="161"/>
+      <c r="AD276" s="161"/>
+      <c r="AE276" s="161"/>
+      <c r="AF276" s="161"/>
+      <c r="AG276" s="161"/>
+      <c r="AH276" s="161"/>
+      <c r="AI276" s="161"/>
+      <c r="AJ276" s="161"/>
       <c r="AK276" s="104"/>
     </row>
     <row r="277" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31649,10 +31725,10 @@
       <c r="M277" s="104"/>
       <c r="N277" s="104"/>
       <c r="O277" s="104"/>
-      <c r="P277" s="104"/>
-      <c r="Q277" s="104"/>
-      <c r="R277" s="104"/>
-      <c r="S277" s="104"/>
+      <c r="P277" s="58"/>
+      <c r="Q277" s="58"/>
+      <c r="R277" s="58"/>
+      <c r="S277" s="58"/>
       <c r="T277" s="104"/>
       <c r="U277" s="104"/>
       <c r="V277" s="104"/>
@@ -31672,35 +31748,33 @@
       <c r="AJ277" s="104"/>
       <c r="AK277" s="104"/>
     </row>
-    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="104"/>
       <c r="B278" s="54" t="s">
-        <v>432</v>
+        <v>590</v>
       </c>
       <c r="C278" s="104"/>
-      <c r="D278" s="58" t="s">
+      <c r="D278" s="158" t="s">
+        <v>681</v>
+      </c>
+      <c r="E278" s="158"/>
+      <c r="F278" s="158"/>
+      <c r="G278" s="158" t="s">
+        <v>682</v>
+      </c>
+      <c r="H278" s="158"/>
+      <c r="I278" s="158"/>
+      <c r="J278" s="58" t="s">
         <v>744</v>
       </c>
-      <c r="E278" s="58"/>
-      <c r="F278" s="58"/>
-      <c r="G278" s="58" t="s">
-        <v>913</v>
-      </c>
-      <c r="H278" s="58"/>
-      <c r="I278" s="58"/>
-      <c r="J278" s="58"/>
       <c r="K278" s="58"/>
-      <c r="L278" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="M278" s="58"/>
-      <c r="N278" s="110" t="s">
+      <c r="L278" s="58"/>
+      <c r="M278" s="110" t="s">
         <v>772</v>
       </c>
+      <c r="N278" s="110"/>
       <c r="O278" s="110"/>
-      <c r="P278" s="58" t="s">
-        <v>914</v>
-      </c>
+      <c r="P278" s="58"/>
       <c r="Q278" s="58"/>
       <c r="R278" s="58"/>
       <c r="S278" s="58"/>
@@ -31725,28 +31799,27 @@
       <c r="AJ278" s="169"/>
       <c r="AK278" s="104"/>
     </row>
-    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="104"/>
-      <c r="B279" s="54" t="s">
-        <v>438</v>
-      </c>
       <c r="C279" s="104"/>
-      <c r="D279" s="189"/>
-      <c r="E279" s="190"/>
-      <c r="F279" s="190"/>
-      <c r="G279" s="190"/>
-      <c r="H279" s="190"/>
-      <c r="I279" s="190"/>
-      <c r="J279" s="190"/>
-      <c r="K279" s="191"/>
-      <c r="L279" s="186" t="s">
-        <v>915</v>
-      </c>
-      <c r="M279" s="186"/>
-      <c r="N279" s="129" t="s">
-        <v>916</v>
-      </c>
-      <c r="O279" s="129"/>
+      <c r="D279" s="58" t="s">
+        <v>898</v>
+      </c>
+      <c r="E279" s="58"/>
+      <c r="F279" s="58"/>
+      <c r="G279" s="162" t="s">
+        <v>898</v>
+      </c>
+      <c r="H279" s="162"/>
+      <c r="I279" s="162"/>
+      <c r="J279" s="189"/>
+      <c r="K279" s="190"/>
+      <c r="L279" s="191"/>
+      <c r="M279" s="58" t="s">
+        <v>912</v>
+      </c>
+      <c r="N279" s="58"/>
+      <c r="O279" s="58"/>
       <c r="P279" s="58"/>
       <c r="Q279" s="58"/>
       <c r="R279" s="58"/>
@@ -31773,20 +31846,21 @@
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="104"/>
       <c r="C280" s="104"/>
-      <c r="D280" s="196"/>
-      <c r="E280" s="197"/>
-      <c r="F280" s="197"/>
-      <c r="G280" s="197"/>
-      <c r="H280" s="197"/>
-      <c r="I280" s="197"/>
-      <c r="J280" s="197"/>
-      <c r="K280" s="198"/>
-      <c r="L280" s="220" t="s">
-        <v>917</v>
-      </c>
-      <c r="M280" s="220"/>
-      <c r="N280" s="129"/>
-      <c r="O280" s="129"/>
+      <c r="D280" s="58" t="s">
+        <v>856</v>
+      </c>
+      <c r="E280" s="58"/>
+      <c r="F280" s="58"/>
+      <c r="G280" s="162" t="s">
+        <v>856</v>
+      </c>
+      <c r="H280" s="162"/>
+      <c r="I280" s="162"/>
+      <c r="J280" s="216"/>
+      <c r="L280" s="132"/>
+      <c r="M280" s="58"/>
+      <c r="N280" s="58"/>
+      <c r="O280" s="58"/>
       <c r="P280" s="58"/>
       <c r="Q280" s="58"/>
       <c r="R280" s="58"/>
@@ -31810,126 +31884,119 @@
       <c r="AJ280" s="169"/>
       <c r="AK280" s="104"/>
     </row>
-    <row r="281" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="104"/>
-      <c r="B281" s="104"/>
       <c r="C281" s="104"/>
-      <c r="D281" s="104"/>
-      <c r="E281" s="104"/>
-      <c r="F281" s="104"/>
-      <c r="G281" s="104"/>
-      <c r="H281" s="104"/>
-      <c r="I281" s="104"/>
-      <c r="J281" s="177"/>
-      <c r="K281" s="104"/>
-      <c r="L281" s="104"/>
-      <c r="M281" s="104"/>
-      <c r="N281" s="129"/>
-      <c r="O281" s="129"/>
+      <c r="D281" s="58"/>
+      <c r="E281" s="58"/>
+      <c r="F281" s="58"/>
+      <c r="G281" s="162"/>
+      <c r="H281" s="162"/>
+      <c r="I281" s="162"/>
+      <c r="J281" s="196"/>
+      <c r="K281" s="197"/>
+      <c r="L281" s="198"/>
+      <c r="M281" s="58"/>
+      <c r="N281" s="58"/>
+      <c r="O281" s="58"/>
       <c r="P281" s="58"/>
       <c r="Q281" s="58"/>
       <c r="R281" s="58"/>
       <c r="S281" s="58"/>
       <c r="T281" s="104"/>
-      <c r="U281" s="104"/>
-      <c r="V281" s="104"/>
-      <c r="W281" s="104"/>
-      <c r="X281" s="104"/>
-      <c r="Y281" s="104"/>
-      <c r="Z281" s="104"/>
-      <c r="AA281" s="104"/>
-      <c r="AB281" s="104"/>
-      <c r="AC281" s="104"/>
-      <c r="AD281" s="104"/>
-      <c r="AE281" s="104"/>
-      <c r="AF281" s="104"/>
-      <c r="AG281" s="104"/>
-      <c r="AH281" s="104"/>
-      <c r="AI281" s="104"/>
-      <c r="AJ281" s="104"/>
+      <c r="U281" s="169"/>
+      <c r="V281" s="169"/>
+      <c r="W281" s="169"/>
+      <c r="X281" s="169"/>
+      <c r="Y281" s="169"/>
+      <c r="Z281" s="169"/>
+      <c r="AA281" s="169"/>
+      <c r="AB281" s="169"/>
+      <c r="AC281" s="169"/>
+      <c r="AD281" s="169"/>
+      <c r="AE281" s="169"/>
+      <c r="AF281" s="169"/>
+      <c r="AG281" s="169"/>
+      <c r="AH281" s="169"/>
+      <c r="AI281" s="169"/>
+      <c r="AJ281" s="169"/>
       <c r="AK281" s="104"/>
     </row>
-    <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="104"/>
-      <c r="B282" s="54" t="s">
-        <v>443</v>
-      </c>
+      <c r="B282" s="104"/>
       <c r="C282" s="104"/>
-      <c r="D282" s="158" t="s">
-        <v>681</v>
-      </c>
-      <c r="E282" s="158"/>
-      <c r="F282" s="158"/>
-      <c r="G282" s="58" t="s">
-        <v>830</v>
-      </c>
-      <c r="H282" s="58"/>
-      <c r="I282" s="158" t="s">
-        <v>682</v>
-      </c>
-      <c r="J282" s="158"/>
-      <c r="K282" s="158"/>
-      <c r="L282" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="M282" s="58"/>
-      <c r="N282" s="129"/>
-      <c r="O282" s="129"/>
-      <c r="P282" s="58"/>
-      <c r="Q282" s="58"/>
-      <c r="R282" s="58"/>
-      <c r="S282" s="58"/>
+      <c r="D282" s="104"/>
+      <c r="E282" s="104"/>
+      <c r="F282" s="104"/>
+      <c r="G282" s="104"/>
+      <c r="H282" s="104"/>
+      <c r="I282" s="104"/>
+      <c r="J282" s="104"/>
+      <c r="K282" s="104"/>
+      <c r="L282" s="104"/>
+      <c r="M282" s="104"/>
+      <c r="N282" s="104"/>
+      <c r="O282" s="104"/>
+      <c r="P282" s="104"/>
+      <c r="Q282" s="104"/>
+      <c r="R282" s="104"/>
+      <c r="S282" s="104"/>
       <c r="T282" s="104"/>
-      <c r="U282" s="169" t="s">
-        <v>719</v>
-      </c>
-      <c r="V282" s="169"/>
-      <c r="W282" s="169"/>
-      <c r="X282" s="169"/>
-      <c r="Y282" s="169"/>
-      <c r="Z282" s="169"/>
-      <c r="AA282" s="169"/>
-      <c r="AB282" s="169"/>
-      <c r="AC282" s="169"/>
-      <c r="AD282" s="169"/>
-      <c r="AE282" s="169"/>
-      <c r="AF282" s="169"/>
-      <c r="AG282" s="169"/>
-      <c r="AH282" s="169"/>
-      <c r="AI282" s="169"/>
-      <c r="AJ282" s="169"/>
+      <c r="U282" s="104"/>
+      <c r="V282" s="104"/>
+      <c r="W282" s="104"/>
+      <c r="X282" s="104"/>
+      <c r="Y282" s="104"/>
+      <c r="Z282" s="104"/>
+      <c r="AA282" s="104"/>
+      <c r="AB282" s="104"/>
+      <c r="AC282" s="104"/>
+      <c r="AD282" s="104"/>
+      <c r="AE282" s="104"/>
+      <c r="AF282" s="104"/>
+      <c r="AG282" s="104"/>
+      <c r="AH282" s="104"/>
+      <c r="AI282" s="104"/>
+      <c r="AJ282" s="104"/>
       <c r="AK282" s="104"/>
     </row>
-    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="104"/>
       <c r="B283" s="54" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="C283" s="104"/>
       <c r="D283" s="58" t="s">
-        <v>689</v>
+        <v>744</v>
       </c>
       <c r="E283" s="58"/>
       <c r="F283" s="58"/>
-      <c r="G283" s="189"/>
-      <c r="H283" s="191"/>
-      <c r="I283" s="162" t="s">
-        <v>689</v>
-      </c>
-      <c r="J283" s="162"/>
-      <c r="K283" s="162"/>
-      <c r="L283" s="186" t="s">
-        <v>918</v>
-      </c>
-      <c r="M283" s="186"/>
-      <c r="N283" s="129"/>
-      <c r="O283" s="129"/>
-      <c r="P283" s="58"/>
+      <c r="G283" s="58" t="s">
+        <v>913</v>
+      </c>
+      <c r="H283" s="58"/>
+      <c r="I283" s="58"/>
+      <c r="J283" s="58"/>
+      <c r="K283" s="58"/>
+      <c r="L283" s="58" t="s">
+        <v>728</v>
+      </c>
+      <c r="M283" s="58"/>
+      <c r="N283" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="O283" s="110"/>
+      <c r="P283" s="58" t="s">
+        <v>914</v>
+      </c>
       <c r="Q283" s="58"/>
       <c r="R283" s="58"/>
       <c r="S283" s="58"/>
       <c r="T283" s="104"/>
-      <c r="U283" s="169"/>
+      <c r="U283" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V283" s="169"/>
       <c r="W283" s="169"/>
       <c r="X283" s="169"/>
@@ -31947,22 +32014,27 @@
       <c r="AJ283" s="169"/>
       <c r="AK283" s="104"/>
     </row>
-    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="104"/>
+      <c r="B284" s="54" t="s">
+        <v>438</v>
+      </c>
       <c r="C284" s="104"/>
-      <c r="D284" s="58"/>
-      <c r="E284" s="58"/>
-      <c r="F284" s="58"/>
-      <c r="G284" s="196"/>
-      <c r="H284" s="198"/>
-      <c r="I284" s="162"/>
-      <c r="J284" s="162"/>
-      <c r="K284" s="162"/>
-      <c r="L284" s="220" t="s">
-        <v>919</v>
-      </c>
-      <c r="M284" s="220"/>
-      <c r="N284" s="129"/>
+      <c r="D284" s="189"/>
+      <c r="E284" s="190"/>
+      <c r="F284" s="190"/>
+      <c r="G284" s="190"/>
+      <c r="H284" s="190"/>
+      <c r="I284" s="190"/>
+      <c r="J284" s="190"/>
+      <c r="K284" s="191"/>
+      <c r="L284" s="186" t="s">
+        <v>915</v>
+      </c>
+      <c r="M284" s="186"/>
+      <c r="N284" s="129" t="s">
+        <v>916</v>
+      </c>
       <c r="O284" s="129"/>
       <c r="P284" s="58"/>
       <c r="Q284" s="58"/>
@@ -31987,136 +32059,119 @@
       <c r="AJ284" s="169"/>
       <c r="AK284" s="104"/>
     </row>
-    <row r="285" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="104"/>
-      <c r="B285" s="104"/>
       <c r="C285" s="104"/>
-      <c r="D285" s="104"/>
-      <c r="E285" s="104"/>
-      <c r="F285" s="104"/>
-      <c r="G285" s="104"/>
-      <c r="H285" s="104"/>
-      <c r="I285" s="104"/>
-      <c r="J285" s="177"/>
-      <c r="K285" s="104"/>
-      <c r="L285" s="104"/>
-      <c r="M285" s="104"/>
-      <c r="N285" s="104"/>
-      <c r="O285" s="104"/>
+      <c r="D285" s="196"/>
+      <c r="E285" s="197"/>
+      <c r="F285" s="197"/>
+      <c r="G285" s="197"/>
+      <c r="H285" s="197"/>
+      <c r="I285" s="197"/>
+      <c r="J285" s="197"/>
+      <c r="K285" s="198"/>
+      <c r="L285" s="220" t="s">
+        <v>917</v>
+      </c>
+      <c r="M285" s="220"/>
+      <c r="N285" s="129"/>
+      <c r="O285" s="129"/>
       <c r="P285" s="58"/>
       <c r="Q285" s="58"/>
       <c r="R285" s="58"/>
       <c r="S285" s="58"/>
       <c r="T285" s="104"/>
-      <c r="U285" s="104"/>
-      <c r="V285" s="104"/>
-      <c r="W285" s="104"/>
-      <c r="X285" s="104"/>
-      <c r="Y285" s="104"/>
-      <c r="Z285" s="104"/>
-      <c r="AA285" s="104"/>
-      <c r="AB285" s="104"/>
-      <c r="AC285" s="104"/>
-      <c r="AD285" s="104"/>
-      <c r="AE285" s="104"/>
-      <c r="AF285" s="104"/>
-      <c r="AG285" s="104"/>
-      <c r="AH285" s="104"/>
-      <c r="AI285" s="104"/>
-      <c r="AJ285" s="104"/>
+      <c r="U285" s="169"/>
+      <c r="V285" s="169"/>
+      <c r="W285" s="169"/>
+      <c r="X285" s="169"/>
+      <c r="Y285" s="169"/>
+      <c r="Z285" s="169"/>
+      <c r="AA285" s="169"/>
+      <c r="AB285" s="169"/>
+      <c r="AC285" s="169"/>
+      <c r="AD285" s="169"/>
+      <c r="AE285" s="169"/>
+      <c r="AF285" s="169"/>
+      <c r="AG285" s="169"/>
+      <c r="AH285" s="169"/>
+      <c r="AI285" s="169"/>
+      <c r="AJ285" s="169"/>
       <c r="AK285" s="104"/>
     </row>
-    <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="104"/>
-      <c r="B286" s="54" t="s">
-        <v>450</v>
-      </c>
+      <c r="B286" s="104"/>
       <c r="C286" s="104"/>
-      <c r="D286" s="158" t="s">
-        <v>755</v>
-      </c>
-      <c r="E286" s="158"/>
-      <c r="F286" s="158"/>
-      <c r="G286" s="158" t="s">
-        <v>900</v>
-      </c>
-      <c r="H286" s="158"/>
-      <c r="I286" s="158"/>
-      <c r="J286" s="149" t="s">
-        <v>920</v>
-      </c>
-      <c r="K286" s="58" t="s">
-        <v>731</v>
-      </c>
-      <c r="L286" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="M286" s="58"/>
-      <c r="N286" s="110" t="s">
-        <v>772</v>
-      </c>
-      <c r="O286" s="110"/>
+      <c r="D286" s="104"/>
+      <c r="E286" s="104"/>
+      <c r="F286" s="104"/>
+      <c r="G286" s="104"/>
+      <c r="H286" s="104"/>
+      <c r="I286" s="104"/>
+      <c r="J286" s="177"/>
+      <c r="K286" s="104"/>
+      <c r="L286" s="104"/>
+      <c r="M286" s="104"/>
+      <c r="N286" s="129"/>
+      <c r="O286" s="129"/>
       <c r="P286" s="58"/>
       <c r="Q286" s="58"/>
       <c r="R286" s="58"/>
       <c r="S286" s="58"/>
       <c r="T286" s="104"/>
-      <c r="U286" s="169" t="s">
-        <v>719</v>
-      </c>
-      <c r="V286" s="169"/>
-      <c r="W286" s="169"/>
-      <c r="X286" s="169"/>
-      <c r="Y286" s="169"/>
-      <c r="Z286" s="169"/>
-      <c r="AA286" s="169"/>
-      <c r="AB286" s="169"/>
-      <c r="AC286" s="169"/>
-      <c r="AD286" s="169"/>
-      <c r="AE286" s="169"/>
-      <c r="AF286" s="169"/>
-      <c r="AG286" s="169"/>
-      <c r="AH286" s="169"/>
-      <c r="AI286" s="169"/>
-      <c r="AJ286" s="169"/>
+      <c r="U286" s="104"/>
+      <c r="V286" s="104"/>
+      <c r="W286" s="104"/>
+      <c r="X286" s="104"/>
+      <c r="Y286" s="104"/>
+      <c r="Z286" s="104"/>
+      <c r="AA286" s="104"/>
+      <c r="AB286" s="104"/>
+      <c r="AC286" s="104"/>
+      <c r="AD286" s="104"/>
+      <c r="AE286" s="104"/>
+      <c r="AF286" s="104"/>
+      <c r="AG286" s="104"/>
+      <c r="AH286" s="104"/>
+      <c r="AI286" s="104"/>
+      <c r="AJ286" s="104"/>
       <c r="AK286" s="104"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="104"/>
       <c r="B287" s="54" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C287" s="104"/>
-      <c r="D287" s="58" t="s">
-        <v>689</v>
-      </c>
-      <c r="E287" s="58"/>
-      <c r="F287" s="58"/>
-      <c r="G287" s="162" t="s">
-        <v>689</v>
-      </c>
-      <c r="H287" s="162"/>
-      <c r="I287" s="162"/>
-      <c r="J287" s="94" t="s">
-        <v>921</v>
-      </c>
-      <c r="K287" s="94" t="s">
-        <v>922</v>
-      </c>
-      <c r="L287" s="186" t="s">
-        <v>923</v>
-      </c>
-      <c r="M287" s="186"/>
-      <c r="N287" s="58" t="s">
-        <v>924</v>
-      </c>
-      <c r="O287" s="58"/>
+      <c r="D287" s="158" t="s">
+        <v>681</v>
+      </c>
+      <c r="E287" s="158"/>
+      <c r="F287" s="158"/>
+      <c r="G287" s="58" t="s">
+        <v>830</v>
+      </c>
+      <c r="H287" s="58"/>
+      <c r="I287" s="158" t="s">
+        <v>682</v>
+      </c>
+      <c r="J287" s="158"/>
+      <c r="K287" s="158"/>
+      <c r="L287" s="58" t="s">
+        <v>728</v>
+      </c>
+      <c r="M287" s="58"/>
+      <c r="N287" s="129"/>
+      <c r="O287" s="129"/>
       <c r="P287" s="58"/>
       <c r="Q287" s="58"/>
       <c r="R287" s="58"/>
       <c r="S287" s="58"/>
       <c r="T287" s="104"/>
-      <c r="U287" s="169"/>
+      <c r="U287" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V287" s="169"/>
       <c r="W287" s="169"/>
       <c r="X287" s="169"/>
@@ -32137,27 +32192,27 @@
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="104"/>
       <c r="B288" s="54" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
       <c r="C288" s="104"/>
-      <c r="D288" s="58"/>
+      <c r="D288" s="58" t="s">
+        <v>689</v>
+      </c>
       <c r="E288" s="58"/>
       <c r="F288" s="58"/>
-      <c r="G288" s="162"/>
-      <c r="H288" s="162"/>
-      <c r="I288" s="162"/>
-      <c r="J288" s="95" t="s">
-        <v>829</v>
-      </c>
-      <c r="K288" s="95" t="s">
-        <v>925</v>
-      </c>
-      <c r="L288" s="225" t="s">
-        <v>926</v>
-      </c>
-      <c r="M288" s="225"/>
-      <c r="N288" s="58"/>
-      <c r="O288" s="58"/>
+      <c r="G288" s="189"/>
+      <c r="H288" s="191"/>
+      <c r="I288" s="162" t="s">
+        <v>689</v>
+      </c>
+      <c r="J288" s="162"/>
+      <c r="K288" s="162"/>
+      <c r="L288" s="186" t="s">
+        <v>918</v>
+      </c>
+      <c r="M288" s="186"/>
+      <c r="N288" s="129"/>
+      <c r="O288" s="129"/>
       <c r="P288" s="58"/>
       <c r="Q288" s="58"/>
       <c r="R288" s="58"/>
@@ -32183,24 +32238,21 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="104"/>
-      <c r="B289" s="54" t="s">
-        <v>463</v>
-      </c>
       <c r="C289" s="104"/>
       <c r="D289" s="58"/>
       <c r="E289" s="58"/>
       <c r="F289" s="58"/>
-      <c r="G289" s="162"/>
-      <c r="H289" s="162"/>
+      <c r="G289" s="196"/>
+      <c r="H289" s="198"/>
       <c r="I289" s="162"/>
-      <c r="J289" s="95"/>
-      <c r="K289" s="95"/>
-      <c r="L289" s="178" t="s">
-        <v>927</v>
-      </c>
-      <c r="M289" s="178"/>
-      <c r="N289" s="58"/>
-      <c r="O289" s="58"/>
+      <c r="J289" s="162"/>
+      <c r="K289" s="162"/>
+      <c r="L289" s="220" t="s">
+        <v>919</v>
+      </c>
+      <c r="M289" s="220"/>
+      <c r="N289" s="129"/>
+      <c r="O289" s="129"/>
       <c r="P289" s="58"/>
       <c r="Q289" s="58"/>
       <c r="R289" s="58"/>
@@ -32224,73 +32276,83 @@
       <c r="AJ289" s="169"/>
       <c r="AK289" s="104"/>
     </row>
-    <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="104"/>
-      <c r="B290" s="54" t="s">
-        <v>467</v>
-      </c>
+      <c r="B290" s="104"/>
       <c r="C290" s="104"/>
-      <c r="D290" s="58"/>
-      <c r="E290" s="58"/>
-      <c r="F290" s="58"/>
-      <c r="G290" s="162"/>
-      <c r="H290" s="162"/>
-      <c r="I290" s="162"/>
-      <c r="J290" s="95"/>
-      <c r="K290" s="95"/>
-      <c r="L290" s="178" t="s">
-        <v>928</v>
-      </c>
-      <c r="M290" s="178"/>
-      <c r="N290" s="58"/>
-      <c r="O290" s="58"/>
+      <c r="D290" s="104"/>
+      <c r="E290" s="104"/>
+      <c r="F290" s="104"/>
+      <c r="G290" s="104"/>
+      <c r="H290" s="104"/>
+      <c r="I290" s="104"/>
+      <c r="J290" s="177"/>
+      <c r="K290" s="104"/>
+      <c r="L290" s="104"/>
+      <c r="M290" s="104"/>
+      <c r="N290" s="104"/>
+      <c r="O290" s="104"/>
       <c r="P290" s="58"/>
       <c r="Q290" s="58"/>
       <c r="R290" s="58"/>
       <c r="S290" s="58"/>
       <c r="T290" s="104"/>
-      <c r="U290" s="169"/>
-      <c r="V290" s="169"/>
-      <c r="W290" s="169"/>
-      <c r="X290" s="169"/>
-      <c r="Y290" s="169"/>
-      <c r="Z290" s="169"/>
-      <c r="AA290" s="169"/>
-      <c r="AB290" s="169"/>
-      <c r="AC290" s="169"/>
-      <c r="AD290" s="169"/>
-      <c r="AE290" s="169"/>
-      <c r="AF290" s="169"/>
-      <c r="AG290" s="169"/>
-      <c r="AH290" s="169"/>
-      <c r="AI290" s="169"/>
-      <c r="AJ290" s="169"/>
+      <c r="U290" s="104"/>
+      <c r="V290" s="104"/>
+      <c r="W290" s="104"/>
+      <c r="X290" s="104"/>
+      <c r="Y290" s="104"/>
+      <c r="Z290" s="104"/>
+      <c r="AA290" s="104"/>
+      <c r="AB290" s="104"/>
+      <c r="AC290" s="104"/>
+      <c r="AD290" s="104"/>
+      <c r="AE290" s="104"/>
+      <c r="AF290" s="104"/>
+      <c r="AG290" s="104"/>
+      <c r="AH290" s="104"/>
+      <c r="AI290" s="104"/>
+      <c r="AJ290" s="104"/>
       <c r="AK290" s="104"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="104"/>
       <c r="B291" s="54" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="C291" s="104"/>
-      <c r="D291" s="58"/>
-      <c r="E291" s="58"/>
-      <c r="F291" s="58"/>
-      <c r="G291" s="162"/>
-      <c r="H291" s="162"/>
-      <c r="I291" s="162"/>
-      <c r="J291" s="92"/>
-      <c r="K291" s="92"/>
-      <c r="L291" s="220"/>
-      <c r="M291" s="220"/>
-      <c r="N291" s="58"/>
-      <c r="O291" s="58"/>
+      <c r="D291" s="158" t="s">
+        <v>755</v>
+      </c>
+      <c r="E291" s="158"/>
+      <c r="F291" s="158"/>
+      <c r="G291" s="158" t="s">
+        <v>900</v>
+      </c>
+      <c r="H291" s="158"/>
+      <c r="I291" s="158"/>
+      <c r="J291" s="149" t="s">
+        <v>920</v>
+      </c>
+      <c r="K291" s="58" t="s">
+        <v>731</v>
+      </c>
+      <c r="L291" s="58" t="s">
+        <v>728</v>
+      </c>
+      <c r="M291" s="58"/>
+      <c r="N291" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="O291" s="110"/>
       <c r="P291" s="58"/>
       <c r="Q291" s="58"/>
       <c r="R291" s="58"/>
       <c r="S291" s="58"/>
       <c r="T291" s="104"/>
-      <c r="U291" s="169"/>
+      <c r="U291" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V291" s="169"/>
       <c r="W291" s="169"/>
       <c r="X291" s="169"/>
@@ -32308,390 +32370,399 @@
       <c r="AJ291" s="169"/>
       <c r="AK291" s="104"/>
     </row>
-    <row r="292" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="104"/>
-      <c r="B292" s="104"/>
+      <c r="B292" s="54" t="s">
+        <v>455</v>
+      </c>
       <c r="C292" s="104"/>
-      <c r="D292" s="104"/>
-      <c r="E292" s="104"/>
-      <c r="F292" s="104"/>
-      <c r="G292" s="104"/>
-      <c r="H292" s="104"/>
-      <c r="I292" s="104"/>
-      <c r="J292" s="104"/>
-      <c r="K292" s="104"/>
-      <c r="L292" s="104"/>
-      <c r="M292" s="104"/>
-      <c r="N292" s="104"/>
-      <c r="O292" s="104"/>
+      <c r="D292" s="58" t="s">
+        <v>689</v>
+      </c>
+      <c r="E292" s="58"/>
+      <c r="F292" s="58"/>
+      <c r="G292" s="162" t="s">
+        <v>689</v>
+      </c>
+      <c r="H292" s="162"/>
+      <c r="I292" s="162"/>
+      <c r="J292" s="94" t="s">
+        <v>921</v>
+      </c>
+      <c r="K292" s="94" t="s">
+        <v>922</v>
+      </c>
+      <c r="L292" s="186" t="s">
+        <v>923</v>
+      </c>
+      <c r="M292" s="186"/>
+      <c r="N292" s="58" t="s">
+        <v>924</v>
+      </c>
+      <c r="O292" s="58"/>
       <c r="P292" s="58"/>
       <c r="Q292" s="58"/>
       <c r="R292" s="58"/>
       <c r="S292" s="58"/>
       <c r="T292" s="104"/>
-      <c r="U292" s="104"/>
-      <c r="V292" s="104"/>
-      <c r="W292" s="104"/>
-      <c r="X292" s="104"/>
-      <c r="Y292" s="104"/>
-      <c r="Z292" s="104"/>
-      <c r="AA292" s="104"/>
-      <c r="AB292" s="104"/>
-      <c r="AC292" s="104"/>
-      <c r="AD292" s="104"/>
-      <c r="AE292" s="104"/>
-      <c r="AF292" s="104"/>
-      <c r="AG292" s="104"/>
-      <c r="AH292" s="104"/>
-      <c r="AI292" s="104"/>
-      <c r="AJ292" s="104"/>
+      <c r="U292" s="169"/>
+      <c r="V292" s="169"/>
+      <c r="W292" s="169"/>
+      <c r="X292" s="169"/>
+      <c r="Y292" s="169"/>
+      <c r="Z292" s="169"/>
+      <c r="AA292" s="169"/>
+      <c r="AB292" s="169"/>
+      <c r="AC292" s="169"/>
+      <c r="AD292" s="169"/>
+      <c r="AE292" s="169"/>
+      <c r="AF292" s="169"/>
+      <c r="AG292" s="169"/>
+      <c r="AH292" s="169"/>
+      <c r="AI292" s="169"/>
+      <c r="AJ292" s="169"/>
       <c r="AK292" s="104"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="104"/>
       <c r="B293" s="54" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="C293" s="104"/>
-      <c r="D293" s="158" t="s">
-        <v>694</v>
-      </c>
-      <c r="E293" s="110" t="s">
-        <v>681</v>
-      </c>
-      <c r="F293" s="110"/>
-      <c r="G293" s="110"/>
-      <c r="H293" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="I293" s="110"/>
-      <c r="J293" s="110"/>
-      <c r="K293" s="110"/>
-      <c r="L293" s="110"/>
-      <c r="M293" s="110"/>
-      <c r="N293" s="110" t="s">
-        <v>772</v>
-      </c>
-      <c r="O293" s="110"/>
+      <c r="D293" s="58"/>
+      <c r="E293" s="58"/>
+      <c r="F293" s="58"/>
+      <c r="G293" s="162"/>
+      <c r="H293" s="162"/>
+      <c r="I293" s="162"/>
+      <c r="J293" s="95" t="s">
+        <v>829</v>
+      </c>
+      <c r="K293" s="95" t="s">
+        <v>925</v>
+      </c>
+      <c r="L293" s="225" t="s">
+        <v>926</v>
+      </c>
+      <c r="M293" s="225"/>
+      <c r="N293" s="58"/>
+      <c r="O293" s="58"/>
       <c r="P293" s="58"/>
       <c r="Q293" s="58"/>
       <c r="R293" s="58"/>
       <c r="S293" s="58"/>
       <c r="T293" s="104"/>
-      <c r="U293" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="V293" s="110"/>
-      <c r="W293" s="110"/>
-      <c r="X293" s="110"/>
-      <c r="Y293" s="110"/>
-      <c r="Z293" s="110"/>
-      <c r="AA293" s="110"/>
-      <c r="AB293" s="110"/>
-      <c r="AC293" s="110"/>
-      <c r="AD293" s="110"/>
-      <c r="AE293" s="110"/>
-      <c r="AF293" s="110"/>
-      <c r="AG293" s="110"/>
-      <c r="AH293" s="110"/>
-      <c r="AI293" s="110"/>
-      <c r="AJ293" s="110"/>
+      <c r="U293" s="169"/>
+      <c r="V293" s="169"/>
+      <c r="W293" s="169"/>
+      <c r="X293" s="169"/>
+      <c r="Y293" s="169"/>
+      <c r="Z293" s="169"/>
+      <c r="AA293" s="169"/>
+      <c r="AB293" s="169"/>
+      <c r="AC293" s="169"/>
+      <c r="AD293" s="169"/>
+      <c r="AE293" s="169"/>
+      <c r="AF293" s="169"/>
+      <c r="AG293" s="169"/>
+      <c r="AH293" s="169"/>
+      <c r="AI293" s="169"/>
+      <c r="AJ293" s="169"/>
       <c r="AK293" s="104"/>
     </row>
-    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="104"/>
       <c r="B294" s="54" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="C294" s="104"/>
-      <c r="D294" s="159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E294" s="58" t="s">
-        <v>625</v>
-      </c>
-      <c r="F294" s="58" t="s">
-        <v>625</v>
-      </c>
-      <c r="G294" s="58"/>
-      <c r="H294" s="162" t="s">
-        <v>685</v>
-      </c>
+      <c r="D294" s="58"/>
+      <c r="E294" s="58"/>
+      <c r="F294" s="58"/>
+      <c r="G294" s="162"/>
+      <c r="H294" s="162"/>
       <c r="I294" s="162"/>
-      <c r="J294" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K294" s="160"/>
-      <c r="L294" s="160"/>
-      <c r="M294" s="160"/>
-      <c r="N294" s="129" t="s">
-        <v>929</v>
-      </c>
-      <c r="O294" s="129"/>
+      <c r="J294" s="95"/>
+      <c r="K294" s="95"/>
+      <c r="L294" s="178" t="s">
+        <v>927</v>
+      </c>
+      <c r="M294" s="178"/>
+      <c r="N294" s="58"/>
+      <c r="O294" s="58"/>
       <c r="P294" s="58"/>
       <c r="Q294" s="58"/>
       <c r="R294" s="58"/>
       <c r="S294" s="58"/>
       <c r="T294" s="104"/>
-      <c r="U294" s="161" t="s">
-        <v>687</v>
-      </c>
-      <c r="V294" s="161"/>
-      <c r="W294" s="161"/>
-      <c r="X294" s="161"/>
-      <c r="Y294" s="161"/>
-      <c r="Z294" s="161"/>
-      <c r="AA294" s="161"/>
-      <c r="AB294" s="161"/>
-      <c r="AC294" s="161"/>
-      <c r="AD294" s="161"/>
-      <c r="AE294" s="161"/>
-      <c r="AF294" s="161"/>
-      <c r="AG294" s="161"/>
-      <c r="AH294" s="161"/>
-      <c r="AI294" s="161"/>
-      <c r="AJ294" s="161"/>
+      <c r="U294" s="169"/>
+      <c r="V294" s="169"/>
+      <c r="W294" s="169"/>
+      <c r="X294" s="169"/>
+      <c r="Y294" s="169"/>
+      <c r="Z294" s="169"/>
+      <c r="AA294" s="169"/>
+      <c r="AB294" s="169"/>
+      <c r="AC294" s="169"/>
+      <c r="AD294" s="169"/>
+      <c r="AE294" s="169"/>
+      <c r="AF294" s="169"/>
+      <c r="AG294" s="169"/>
+      <c r="AH294" s="169"/>
+      <c r="AI294" s="169"/>
+      <c r="AJ294" s="169"/>
       <c r="AK294" s="104"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="104"/>
+      <c r="B295" s="54" t="s">
+        <v>467</v>
+      </c>
       <c r="C295" s="104"/>
-      <c r="D295" s="159"/>
-      <c r="E295" s="159" t="n">
-        <v>0</v>
-      </c>
-      <c r="F295" s="58" t="s">
-        <v>930</v>
-      </c>
-      <c r="G295" s="58"/>
-      <c r="H295" s="162" t="s">
-        <v>732</v>
-      </c>
+      <c r="D295" s="58"/>
+      <c r="E295" s="58"/>
+      <c r="F295" s="58"/>
+      <c r="G295" s="162"/>
+      <c r="H295" s="162"/>
       <c r="I295" s="162"/>
-      <c r="J295" s="162" t="s">
-        <v>691</v>
-      </c>
-      <c r="K295" s="162"/>
-      <c r="L295" s="162"/>
-      <c r="M295" s="162"/>
-      <c r="N295" s="129"/>
-      <c r="O295" s="129"/>
+      <c r="J295" s="95"/>
+      <c r="K295" s="95"/>
+      <c r="L295" s="178" t="s">
+        <v>928</v>
+      </c>
+      <c r="M295" s="178"/>
+      <c r="N295" s="58"/>
+      <c r="O295" s="58"/>
       <c r="P295" s="58"/>
       <c r="Q295" s="58"/>
       <c r="R295" s="58"/>
       <c r="S295" s="58"/>
       <c r="T295" s="104"/>
-      <c r="U295" s="161"/>
-      <c r="V295" s="161"/>
-      <c r="W295" s="161"/>
-      <c r="X295" s="161"/>
-      <c r="Y295" s="161"/>
-      <c r="Z295" s="161"/>
-      <c r="AA295" s="161"/>
-      <c r="AB295" s="161"/>
-      <c r="AC295" s="161"/>
-      <c r="AD295" s="161"/>
-      <c r="AE295" s="161"/>
-      <c r="AF295" s="161"/>
-      <c r="AG295" s="161"/>
-      <c r="AH295" s="161"/>
-      <c r="AI295" s="161"/>
-      <c r="AJ295" s="161"/>
+      <c r="U295" s="169"/>
+      <c r="V295" s="169"/>
+      <c r="W295" s="169"/>
+      <c r="X295" s="169"/>
+      <c r="Y295" s="169"/>
+      <c r="Z295" s="169"/>
+      <c r="AA295" s="169"/>
+      <c r="AB295" s="169"/>
+      <c r="AC295" s="169"/>
+      <c r="AD295" s="169"/>
+      <c r="AE295" s="169"/>
+      <c r="AF295" s="169"/>
+      <c r="AG295" s="169"/>
+      <c r="AH295" s="169"/>
+      <c r="AI295" s="169"/>
+      <c r="AJ295" s="169"/>
       <c r="AK295" s="104"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="104"/>
+      <c r="B296" s="54" t="s">
+        <v>471</v>
+      </c>
       <c r="C296" s="104"/>
-      <c r="D296" s="159"/>
-      <c r="E296" s="159"/>
+      <c r="D296" s="58"/>
+      <c r="E296" s="58"/>
       <c r="F296" s="58"/>
-      <c r="G296" s="58"/>
+      <c r="G296" s="162"/>
       <c r="H296" s="162"/>
       <c r="I296" s="162"/>
-      <c r="J296" s="162"/>
-      <c r="K296" s="162"/>
-      <c r="L296" s="162"/>
-      <c r="M296" s="162"/>
-      <c r="N296" s="129"/>
-      <c r="O296" s="129"/>
+      <c r="J296" s="92"/>
+      <c r="K296" s="92"/>
+      <c r="L296" s="220"/>
+      <c r="M296" s="220"/>
+      <c r="N296" s="58"/>
+      <c r="O296" s="58"/>
       <c r="P296" s="58"/>
       <c r="Q296" s="58"/>
       <c r="R296" s="58"/>
       <c r="S296" s="58"/>
       <c r="T296" s="104"/>
-      <c r="U296" s="161"/>
-      <c r="V296" s="161"/>
-      <c r="W296" s="161"/>
-      <c r="X296" s="161"/>
-      <c r="Y296" s="161"/>
-      <c r="Z296" s="161"/>
-      <c r="AA296" s="161"/>
-      <c r="AB296" s="161"/>
-      <c r="AC296" s="161"/>
-      <c r="AD296" s="161"/>
-      <c r="AE296" s="161"/>
-      <c r="AF296" s="161"/>
-      <c r="AG296" s="161"/>
-      <c r="AH296" s="161"/>
-      <c r="AI296" s="161"/>
-      <c r="AJ296" s="161"/>
+      <c r="U296" s="169"/>
+      <c r="V296" s="169"/>
+      <c r="W296" s="169"/>
+      <c r="X296" s="169"/>
+      <c r="Y296" s="169"/>
+      <c r="Z296" s="169"/>
+      <c r="AA296" s="169"/>
+      <c r="AB296" s="169"/>
+      <c r="AC296" s="169"/>
+      <c r="AD296" s="169"/>
+      <c r="AE296" s="169"/>
+      <c r="AF296" s="169"/>
+      <c r="AG296" s="169"/>
+      <c r="AH296" s="169"/>
+      <c r="AI296" s="169"/>
+      <c r="AJ296" s="169"/>
       <c r="AK296" s="104"/>
     </row>
-    <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="104"/>
+      <c r="B297" s="104"/>
       <c r="C297" s="104"/>
-      <c r="D297" s="158" t="s">
-        <v>694</v>
-      </c>
-      <c r="E297" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="F297" s="110"/>
-      <c r="G297" s="110"/>
-      <c r="H297" s="110" t="s">
-        <v>681</v>
-      </c>
-      <c r="I297" s="110"/>
-      <c r="J297" s="110"/>
-      <c r="K297" s="110"/>
-      <c r="L297" s="110"/>
-      <c r="M297" s="110"/>
-      <c r="N297" s="129"/>
-      <c r="O297" s="129"/>
+      <c r="D297" s="104"/>
+      <c r="E297" s="104"/>
+      <c r="F297" s="104"/>
+      <c r="G297" s="104"/>
+      <c r="H297" s="104"/>
+      <c r="I297" s="104"/>
+      <c r="J297" s="104"/>
+      <c r="K297" s="104"/>
+      <c r="L297" s="104"/>
+      <c r="M297" s="104"/>
+      <c r="N297" s="104"/>
+      <c r="O297" s="104"/>
       <c r="P297" s="58"/>
       <c r="Q297" s="58"/>
       <c r="R297" s="58"/>
       <c r="S297" s="58"/>
       <c r="T297" s="104"/>
-      <c r="U297" s="110" t="s">
+      <c r="U297" s="104"/>
+      <c r="V297" s="104"/>
+      <c r="W297" s="104"/>
+      <c r="X297" s="104"/>
+      <c r="Y297" s="104"/>
+      <c r="Z297" s="104"/>
+      <c r="AA297" s="104"/>
+      <c r="AB297" s="104"/>
+      <c r="AC297" s="104"/>
+      <c r="AD297" s="104"/>
+      <c r="AE297" s="104"/>
+      <c r="AF297" s="104"/>
+      <c r="AG297" s="104"/>
+      <c r="AH297" s="104"/>
+      <c r="AI297" s="104"/>
+      <c r="AJ297" s="104"/>
+      <c r="AK297" s="104"/>
+    </row>
+    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A298" s="104"/>
+      <c r="B298" s="54" t="s">
+        <v>475</v>
+      </c>
+      <c r="C298" s="104"/>
+      <c r="D298" s="158" t="s">
+        <v>694</v>
+      </c>
+      <c r="E298" s="110" t="s">
         <v>681</v>
       </c>
-      <c r="V297" s="110"/>
-      <c r="W297" s="110"/>
-      <c r="X297" s="110"/>
-      <c r="Y297" s="110"/>
-      <c r="Z297" s="110"/>
-      <c r="AA297" s="110"/>
-      <c r="AB297" s="110"/>
-      <c r="AC297" s="110"/>
-      <c r="AD297" s="110"/>
-      <c r="AE297" s="110"/>
-      <c r="AF297" s="110"/>
-      <c r="AG297" s="110"/>
-      <c r="AH297" s="110"/>
-      <c r="AI297" s="110"/>
-      <c r="AJ297" s="110"/>
-      <c r="AK297" s="104"/>
-    </row>
-    <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="104"/>
-      <c r="C298" s="104"/>
-      <c r="D298" s="163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E298" s="162" t="s">
-        <v>625</v>
-      </c>
-      <c r="F298" s="162" t="s">
-        <v>625</v>
-      </c>
-      <c r="G298" s="162"/>
-      <c r="H298" s="58" t="s">
-        <v>685</v>
-      </c>
-      <c r="I298" s="58"/>
-      <c r="J298" s="149" t="s">
-        <v>686</v>
-      </c>
-      <c r="K298" s="149"/>
-      <c r="L298" s="149"/>
-      <c r="M298" s="149"/>
-      <c r="N298" s="129"/>
-      <c r="O298" s="129"/>
+      <c r="F298" s="110"/>
+      <c r="G298" s="110"/>
+      <c r="H298" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="I298" s="110"/>
+      <c r="J298" s="110"/>
+      <c r="K298" s="110"/>
+      <c r="L298" s="110"/>
+      <c r="M298" s="110"/>
+      <c r="N298" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="O298" s="110"/>
       <c r="P298" s="58"/>
       <c r="Q298" s="58"/>
       <c r="R298" s="58"/>
       <c r="S298" s="58"/>
       <c r="T298" s="104"/>
-      <c r="U298" s="129" t="s">
-        <v>687</v>
-      </c>
-      <c r="V298" s="129"/>
-      <c r="W298" s="129"/>
-      <c r="X298" s="129"/>
-      <c r="Y298" s="129"/>
-      <c r="Z298" s="129"/>
-      <c r="AA298" s="129"/>
-      <c r="AB298" s="129"/>
-      <c r="AC298" s="129"/>
-      <c r="AD298" s="129"/>
-      <c r="AE298" s="129"/>
-      <c r="AF298" s="129"/>
-      <c r="AG298" s="129"/>
-      <c r="AH298" s="129"/>
-      <c r="AI298" s="129"/>
-      <c r="AJ298" s="129"/>
+      <c r="U298" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="V298" s="110"/>
+      <c r="W298" s="110"/>
+      <c r="X298" s="110"/>
+      <c r="Y298" s="110"/>
+      <c r="Z298" s="110"/>
+      <c r="AA298" s="110"/>
+      <c r="AB298" s="110"/>
+      <c r="AC298" s="110"/>
+      <c r="AD298" s="110"/>
+      <c r="AE298" s="110"/>
+      <c r="AF298" s="110"/>
+      <c r="AG298" s="110"/>
+      <c r="AH298" s="110"/>
+      <c r="AI298" s="110"/>
+      <c r="AJ298" s="110"/>
       <c r="AK298" s="104"/>
     </row>
-    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="104"/>
+      <c r="B299" s="54" t="s">
+        <v>481</v>
+      </c>
       <c r="C299" s="104"/>
-      <c r="D299" s="163"/>
-      <c r="E299" s="163" t="n">
+      <c r="D299" s="159" t="n">
         <v>0</v>
       </c>
-      <c r="F299" s="184" t="s">
-        <v>930</v>
-      </c>
-      <c r="G299" s="184"/>
-      <c r="H299" s="58" t="s">
-        <v>732</v>
-      </c>
-      <c r="I299" s="58"/>
-      <c r="J299" s="58" t="s">
-        <v>691</v>
-      </c>
-      <c r="K299" s="58"/>
-      <c r="L299" s="58"/>
-      <c r="M299" s="58"/>
-      <c r="N299" s="129"/>
+      <c r="E299" s="58" t="s">
+        <v>625</v>
+      </c>
+      <c r="F299" s="58" t="s">
+        <v>625</v>
+      </c>
+      <c r="G299" s="58"/>
+      <c r="H299" s="162" t="s">
+        <v>685</v>
+      </c>
+      <c r="I299" s="162"/>
+      <c r="J299" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K299" s="160"/>
+      <c r="L299" s="160"/>
+      <c r="M299" s="160"/>
+      <c r="N299" s="129" t="s">
+        <v>929</v>
+      </c>
       <c r="O299" s="129"/>
       <c r="P299" s="58"/>
       <c r="Q299" s="58"/>
       <c r="R299" s="58"/>
       <c r="S299" s="58"/>
       <c r="T299" s="104"/>
-      <c r="U299" s="129"/>
-      <c r="V299" s="129"/>
-      <c r="W299" s="129"/>
-      <c r="X299" s="129"/>
-      <c r="Y299" s="129"/>
-      <c r="Z299" s="129"/>
-      <c r="AA299" s="129"/>
-      <c r="AB299" s="129"/>
-      <c r="AC299" s="129"/>
-      <c r="AD299" s="129"/>
-      <c r="AE299" s="129"/>
-      <c r="AF299" s="129"/>
-      <c r="AG299" s="129"/>
-      <c r="AH299" s="129"/>
-      <c r="AI299" s="129"/>
-      <c r="AJ299" s="129"/>
+      <c r="U299" s="161" t="s">
+        <v>687</v>
+      </c>
+      <c r="V299" s="161"/>
+      <c r="W299" s="161"/>
+      <c r="X299" s="161"/>
+      <c r="Y299" s="161"/>
+      <c r="Z299" s="161"/>
+      <c r="AA299" s="161"/>
+      <c r="AB299" s="161"/>
+      <c r="AC299" s="161"/>
+      <c r="AD299" s="161"/>
+      <c r="AE299" s="161"/>
+      <c r="AF299" s="161"/>
+      <c r="AG299" s="161"/>
+      <c r="AH299" s="161"/>
+      <c r="AI299" s="161"/>
+      <c r="AJ299" s="161"/>
       <c r="AK299" s="104"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="104"/>
       <c r="C300" s="104"/>
-      <c r="D300" s="163"/>
-      <c r="E300" s="163"/>
-      <c r="F300" s="184"/>
-      <c r="G300" s="184"/>
-      <c r="H300" s="58"/>
-      <c r="I300" s="58"/>
-      <c r="J300" s="58"/>
-      <c r="K300" s="58"/>
-      <c r="L300" s="58"/>
-      <c r="M300" s="58"/>
+      <c r="D300" s="159"/>
+      <c r="E300" s="159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F300" s="58" t="s">
+        <v>930</v>
+      </c>
+      <c r="G300" s="58"/>
+      <c r="H300" s="162" t="s">
+        <v>732</v>
+      </c>
+      <c r="I300" s="162"/>
+      <c r="J300" s="162" t="s">
+        <v>691</v>
+      </c>
+      <c r="K300" s="162"/>
+      <c r="L300" s="162"/>
+      <c r="M300" s="162"/>
       <c r="N300" s="129"/>
       <c r="O300" s="129"/>
       <c r="P300" s="58"/>
@@ -32699,43 +32770,37 @@
       <c r="R300" s="58"/>
       <c r="S300" s="58"/>
       <c r="T300" s="104"/>
-      <c r="U300" s="129"/>
-      <c r="V300" s="129"/>
-      <c r="W300" s="129"/>
-      <c r="X300" s="129"/>
-      <c r="Y300" s="129"/>
-      <c r="Z300" s="129"/>
-      <c r="AA300" s="129"/>
-      <c r="AB300" s="129"/>
-      <c r="AC300" s="129"/>
-      <c r="AD300" s="129"/>
-      <c r="AE300" s="129"/>
-      <c r="AF300" s="129"/>
-      <c r="AG300" s="129"/>
-      <c r="AH300" s="129"/>
-      <c r="AI300" s="129"/>
-      <c r="AJ300" s="129"/>
+      <c r="U300" s="161"/>
+      <c r="V300" s="161"/>
+      <c r="W300" s="161"/>
+      <c r="X300" s="161"/>
+      <c r="Y300" s="161"/>
+      <c r="Z300" s="161"/>
+      <c r="AA300" s="161"/>
+      <c r="AB300" s="161"/>
+      <c r="AC300" s="161"/>
+      <c r="AD300" s="161"/>
+      <c r="AE300" s="161"/>
+      <c r="AF300" s="161"/>
+      <c r="AG300" s="161"/>
+      <c r="AH300" s="161"/>
+      <c r="AI300" s="161"/>
+      <c r="AJ300" s="161"/>
       <c r="AK300" s="104"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="104"/>
       <c r="C301" s="104"/>
-      <c r="D301" s="162" t="s">
-        <v>696</v>
-      </c>
-      <c r="E301" s="162" t="s">
-        <v>697</v>
-      </c>
-      <c r="F301" s="162" t="s">
-        <v>696</v>
-      </c>
-      <c r="G301" s="162"/>
-      <c r="H301" s="58"/>
-      <c r="I301" s="58"/>
-      <c r="J301" s="58"/>
-      <c r="K301" s="58"/>
-      <c r="L301" s="58"/>
-      <c r="M301" s="58"/>
+      <c r="D301" s="159"/>
+      <c r="E301" s="159"/>
+      <c r="F301" s="58"/>
+      <c r="G301" s="58"/>
+      <c r="H301" s="162"/>
+      <c r="I301" s="162"/>
+      <c r="J301" s="162"/>
+      <c r="K301" s="162"/>
+      <c r="L301" s="162"/>
+      <c r="M301" s="162"/>
       <c r="N301" s="129"/>
       <c r="O301" s="129"/>
       <c r="P301" s="58"/>
@@ -32743,43 +32808,43 @@
       <c r="R301" s="58"/>
       <c r="S301" s="58"/>
       <c r="T301" s="104"/>
-      <c r="U301" s="129"/>
-      <c r="V301" s="129"/>
-      <c r="W301" s="129"/>
-      <c r="X301" s="129"/>
-      <c r="Y301" s="129"/>
-      <c r="Z301" s="129"/>
-      <c r="AA301" s="129"/>
-      <c r="AB301" s="129"/>
-      <c r="AC301" s="129"/>
-      <c r="AD301" s="129"/>
-      <c r="AE301" s="129"/>
-      <c r="AF301" s="129"/>
-      <c r="AG301" s="129"/>
-      <c r="AH301" s="129"/>
-      <c r="AI301" s="129"/>
-      <c r="AJ301" s="129"/>
+      <c r="U301" s="161"/>
+      <c r="V301" s="161"/>
+      <c r="W301" s="161"/>
+      <c r="X301" s="161"/>
+      <c r="Y301" s="161"/>
+      <c r="Z301" s="161"/>
+      <c r="AA301" s="161"/>
+      <c r="AB301" s="161"/>
+      <c r="AC301" s="161"/>
+      <c r="AD301" s="161"/>
+      <c r="AE301" s="161"/>
+      <c r="AF301" s="161"/>
+      <c r="AG301" s="161"/>
+      <c r="AH301" s="161"/>
+      <c r="AI301" s="161"/>
+      <c r="AJ301" s="161"/>
       <c r="AK301" s="104"/>
     </row>
-    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="104"/>
       <c r="C302" s="104"/>
-      <c r="D302" s="166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" s="161" t="s">
-        <v>733</v>
-      </c>
-      <c r="F302" s="226" t="s">
-        <v>931</v>
-      </c>
-      <c r="G302" s="226"/>
-      <c r="H302" s="58"/>
-      <c r="I302" s="58"/>
-      <c r="J302" s="58"/>
-      <c r="K302" s="58"/>
-      <c r="L302" s="58"/>
-      <c r="M302" s="58"/>
+      <c r="D302" s="158" t="s">
+        <v>694</v>
+      </c>
+      <c r="E302" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="F302" s="110"/>
+      <c r="G302" s="110"/>
+      <c r="H302" s="110" t="s">
+        <v>681</v>
+      </c>
+      <c r="I302" s="110"/>
+      <c r="J302" s="110"/>
+      <c r="K302" s="110"/>
+      <c r="L302" s="110"/>
+      <c r="M302" s="110"/>
       <c r="N302" s="129"/>
       <c r="O302" s="129"/>
       <c r="P302" s="58"/>
@@ -32787,41 +32852,49 @@
       <c r="R302" s="58"/>
       <c r="S302" s="58"/>
       <c r="T302" s="104"/>
-      <c r="U302" s="129"/>
-      <c r="V302" s="129"/>
-      <c r="W302" s="129"/>
-      <c r="X302" s="129"/>
-      <c r="Y302" s="129"/>
-      <c r="Z302" s="129"/>
-      <c r="AA302" s="129"/>
-      <c r="AB302" s="129"/>
-      <c r="AC302" s="129"/>
-      <c r="AD302" s="129"/>
-      <c r="AE302" s="129"/>
-      <c r="AF302" s="129"/>
-      <c r="AG302" s="129"/>
-      <c r="AH302" s="129"/>
-      <c r="AI302" s="129"/>
-      <c r="AJ302" s="129"/>
+      <c r="U302" s="110" t="s">
+        <v>681</v>
+      </c>
+      <c r="V302" s="110"/>
+      <c r="W302" s="110"/>
+      <c r="X302" s="110"/>
+      <c r="Y302" s="110"/>
+      <c r="Z302" s="110"/>
+      <c r="AA302" s="110"/>
+      <c r="AB302" s="110"/>
+      <c r="AC302" s="110"/>
+      <c r="AD302" s="110"/>
+      <c r="AE302" s="110"/>
+      <c r="AF302" s="110"/>
+      <c r="AG302" s="110"/>
+      <c r="AH302" s="110"/>
+      <c r="AI302" s="110"/>
+      <c r="AJ302" s="110"/>
       <c r="AK302" s="104"/>
     </row>
-    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="104"/>
       <c r="C303" s="104"/>
-      <c r="D303" s="168" t="n">
+      <c r="D303" s="163" t="n">
         <v>1</v>
       </c>
-      <c r="E303" s="161"/>
-      <c r="F303" s="185" t="s">
-        <v>932</v>
-      </c>
-      <c r="G303" s="185"/>
-      <c r="H303" s="58"/>
+      <c r="E303" s="162" t="s">
+        <v>625</v>
+      </c>
+      <c r="F303" s="162" t="s">
+        <v>625</v>
+      </c>
+      <c r="G303" s="162"/>
+      <c r="H303" s="58" t="s">
+        <v>685</v>
+      </c>
       <c r="I303" s="58"/>
-      <c r="J303" s="58"/>
-      <c r="K303" s="58"/>
-      <c r="L303" s="58"/>
-      <c r="M303" s="58"/>
+      <c r="J303" s="149" t="s">
+        <v>686</v>
+      </c>
+      <c r="K303" s="149"/>
+      <c r="L303" s="149"/>
+      <c r="M303" s="149"/>
       <c r="N303" s="129"/>
       <c r="O303" s="129"/>
       <c r="P303" s="58"/>
@@ -32829,7 +32902,9 @@
       <c r="R303" s="58"/>
       <c r="S303" s="58"/>
       <c r="T303" s="104"/>
-      <c r="U303" s="129"/>
+      <c r="U303" s="129" t="s">
+        <v>687</v>
+      </c>
       <c r="V303" s="129"/>
       <c r="W303" s="129"/>
       <c r="X303" s="129"/>
@@ -32850,22 +32925,24 @@
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="104"/>
       <c r="C304" s="104"/>
-      <c r="D304" s="158" t="s">
-        <v>694</v>
-      </c>
-      <c r="E304" s="110" t="s">
-        <v>681</v>
-      </c>
-      <c r="F304" s="110"/>
-      <c r="G304" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="H304" s="110"/>
-      <c r="I304" s="110"/>
-      <c r="J304" s="110"/>
-      <c r="K304" s="110"/>
-      <c r="L304" s="110"/>
-      <c r="M304" s="110"/>
+      <c r="D304" s="163"/>
+      <c r="E304" s="163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F304" s="184" t="s">
+        <v>930</v>
+      </c>
+      <c r="G304" s="184"/>
+      <c r="H304" s="58" t="s">
+        <v>732</v>
+      </c>
+      <c r="I304" s="58"/>
+      <c r="J304" s="58" t="s">
+        <v>691</v>
+      </c>
+      <c r="K304" s="58"/>
+      <c r="L304" s="58"/>
+      <c r="M304" s="58"/>
       <c r="N304" s="129"/>
       <c r="O304" s="129"/>
       <c r="P304" s="58"/>
@@ -32873,49 +32950,37 @@
       <c r="R304" s="58"/>
       <c r="S304" s="58"/>
       <c r="T304" s="104"/>
-      <c r="U304" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="V304" s="110"/>
-      <c r="W304" s="110"/>
-      <c r="X304" s="110"/>
-      <c r="Y304" s="110"/>
-      <c r="Z304" s="110"/>
-      <c r="AA304" s="110"/>
-      <c r="AB304" s="110"/>
-      <c r="AC304" s="110"/>
-      <c r="AD304" s="110"/>
-      <c r="AE304" s="110"/>
-      <c r="AF304" s="110"/>
-      <c r="AG304" s="110"/>
-      <c r="AH304" s="110"/>
-      <c r="AI304" s="110"/>
-      <c r="AJ304" s="110"/>
+      <c r="U304" s="129"/>
+      <c r="V304" s="129"/>
+      <c r="W304" s="129"/>
+      <c r="X304" s="129"/>
+      <c r="Y304" s="129"/>
+      <c r="Z304" s="129"/>
+      <c r="AA304" s="129"/>
+      <c r="AB304" s="129"/>
+      <c r="AC304" s="129"/>
+      <c r="AD304" s="129"/>
+      <c r="AE304" s="129"/>
+      <c r="AF304" s="129"/>
+      <c r="AG304" s="129"/>
+      <c r="AH304" s="129"/>
+      <c r="AI304" s="129"/>
+      <c r="AJ304" s="129"/>
       <c r="AK304" s="104"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="104"/>
       <c r="C305" s="104"/>
-      <c r="D305" s="159" t="n">
-        <v>0</v>
-      </c>
-      <c r="E305" s="58" t="s">
-        <v>625</v>
-      </c>
-      <c r="F305" s="58"/>
-      <c r="G305" s="182" t="s">
-        <v>734</v>
-      </c>
-      <c r="H305" s="160" t="s">
-        <v>702</v>
-      </c>
-      <c r="I305" s="160"/>
-      <c r="J305" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K305" s="160"/>
-      <c r="L305" s="160"/>
-      <c r="M305" s="160"/>
+      <c r="D305" s="163"/>
+      <c r="E305" s="163"/>
+      <c r="F305" s="184"/>
+      <c r="G305" s="184"/>
+      <c r="H305" s="58"/>
+      <c r="I305" s="58"/>
+      <c r="J305" s="58"/>
+      <c r="K305" s="58"/>
+      <c r="L305" s="58"/>
+      <c r="M305" s="58"/>
       <c r="N305" s="129"/>
       <c r="O305" s="129"/>
       <c r="P305" s="58"/>
@@ -32923,47 +32988,43 @@
       <c r="R305" s="58"/>
       <c r="S305" s="58"/>
       <c r="T305" s="104"/>
-      <c r="U305" s="169" t="s">
-        <v>703</v>
-      </c>
-      <c r="V305" s="169"/>
-      <c r="W305" s="169"/>
-      <c r="X305" s="169"/>
-      <c r="Y305" s="169"/>
-      <c r="Z305" s="169"/>
-      <c r="AA305" s="169"/>
-      <c r="AB305" s="169"/>
-      <c r="AC305" s="169"/>
-      <c r="AD305" s="169"/>
-      <c r="AE305" s="169"/>
-      <c r="AF305" s="169"/>
-      <c r="AG305" s="169"/>
-      <c r="AH305" s="169"/>
-      <c r="AI305" s="169"/>
-      <c r="AJ305" s="169"/>
+      <c r="U305" s="129"/>
+      <c r="V305" s="129"/>
+      <c r="W305" s="129"/>
+      <c r="X305" s="129"/>
+      <c r="Y305" s="129"/>
+      <c r="Z305" s="129"/>
+      <c r="AA305" s="129"/>
+      <c r="AB305" s="129"/>
+      <c r="AC305" s="129"/>
+      <c r="AD305" s="129"/>
+      <c r="AE305" s="129"/>
+      <c r="AF305" s="129"/>
+      <c r="AG305" s="129"/>
+      <c r="AH305" s="129"/>
+      <c r="AI305" s="129"/>
+      <c r="AJ305" s="129"/>
       <c r="AK305" s="104"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="104"/>
       <c r="C306" s="104"/>
-      <c r="D306" s="159"/>
-      <c r="E306" s="58" t="s">
-        <v>865</v>
-      </c>
-      <c r="F306" s="58"/>
-      <c r="G306" s="162" t="s">
-        <v>735</v>
-      </c>
-      <c r="H306" s="162" t="s">
-        <v>705</v>
-      </c>
-      <c r="I306" s="162"/>
-      <c r="J306" s="162" t="s">
-        <v>706</v>
-      </c>
-      <c r="K306" s="162"/>
-      <c r="L306" s="162"/>
-      <c r="M306" s="162"/>
+      <c r="D306" s="162" t="s">
+        <v>696</v>
+      </c>
+      <c r="E306" s="162" t="s">
+        <v>697</v>
+      </c>
+      <c r="F306" s="162" t="s">
+        <v>696</v>
+      </c>
+      <c r="G306" s="162"/>
+      <c r="H306" s="58"/>
+      <c r="I306" s="58"/>
+      <c r="J306" s="58"/>
+      <c r="K306" s="58"/>
+      <c r="L306" s="58"/>
+      <c r="M306" s="58"/>
       <c r="N306" s="129"/>
       <c r="O306" s="129"/>
       <c r="P306" s="58"/>
@@ -32971,37 +33032,43 @@
       <c r="R306" s="58"/>
       <c r="S306" s="58"/>
       <c r="T306" s="104"/>
-      <c r="U306" s="169"/>
-      <c r="V306" s="169"/>
-      <c r="W306" s="169"/>
-      <c r="X306" s="169"/>
-      <c r="Y306" s="169"/>
-      <c r="Z306" s="169"/>
-      <c r="AA306" s="169"/>
-      <c r="AB306" s="169"/>
-      <c r="AC306" s="169"/>
-      <c r="AD306" s="169"/>
-      <c r="AE306" s="169"/>
-      <c r="AF306" s="169"/>
-      <c r="AG306" s="169"/>
-      <c r="AH306" s="169"/>
-      <c r="AI306" s="169"/>
-      <c r="AJ306" s="169"/>
+      <c r="U306" s="129"/>
+      <c r="V306" s="129"/>
+      <c r="W306" s="129"/>
+      <c r="X306" s="129"/>
+      <c r="Y306" s="129"/>
+      <c r="Z306" s="129"/>
+      <c r="AA306" s="129"/>
+      <c r="AB306" s="129"/>
+      <c r="AC306" s="129"/>
+      <c r="AD306" s="129"/>
+      <c r="AE306" s="129"/>
+      <c r="AF306" s="129"/>
+      <c r="AG306" s="129"/>
+      <c r="AH306" s="129"/>
+      <c r="AI306" s="129"/>
+      <c r="AJ306" s="129"/>
       <c r="AK306" s="104"/>
     </row>
-    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="104"/>
       <c r="C307" s="104"/>
-      <c r="D307" s="159"/>
-      <c r="E307" s="58"/>
-      <c r="F307" s="58"/>
-      <c r="G307" s="162"/>
-      <c r="H307" s="162"/>
-      <c r="I307" s="162"/>
-      <c r="J307" s="162"/>
-      <c r="K307" s="162"/>
-      <c r="L307" s="162"/>
-      <c r="M307" s="162"/>
+      <c r="D307" s="166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E307" s="161" t="s">
+        <v>733</v>
+      </c>
+      <c r="F307" s="226" t="s">
+        <v>931</v>
+      </c>
+      <c r="G307" s="226"/>
+      <c r="H307" s="58"/>
+      <c r="I307" s="58"/>
+      <c r="J307" s="58"/>
+      <c r="K307" s="58"/>
+      <c r="L307" s="58"/>
+      <c r="M307" s="58"/>
       <c r="N307" s="129"/>
       <c r="O307" s="129"/>
       <c r="P307" s="58"/>
@@ -33009,43 +33076,41 @@
       <c r="R307" s="58"/>
       <c r="S307" s="58"/>
       <c r="T307" s="104"/>
-      <c r="U307" s="169"/>
-      <c r="V307" s="169"/>
-      <c r="W307" s="169"/>
-      <c r="X307" s="169"/>
-      <c r="Y307" s="169"/>
-      <c r="Z307" s="169"/>
-      <c r="AA307" s="169"/>
-      <c r="AB307" s="169"/>
-      <c r="AC307" s="169"/>
-      <c r="AD307" s="169"/>
-      <c r="AE307" s="169"/>
-      <c r="AF307" s="169"/>
-      <c r="AG307" s="169"/>
-      <c r="AH307" s="169"/>
-      <c r="AI307" s="169"/>
-      <c r="AJ307" s="169"/>
+      <c r="U307" s="129"/>
+      <c r="V307" s="129"/>
+      <c r="W307" s="129"/>
+      <c r="X307" s="129"/>
+      <c r="Y307" s="129"/>
+      <c r="Z307" s="129"/>
+      <c r="AA307" s="129"/>
+      <c r="AB307" s="129"/>
+      <c r="AC307" s="129"/>
+      <c r="AD307" s="129"/>
+      <c r="AE307" s="129"/>
+      <c r="AF307" s="129"/>
+      <c r="AG307" s="129"/>
+      <c r="AH307" s="129"/>
+      <c r="AI307" s="129"/>
+      <c r="AJ307" s="129"/>
       <c r="AK307" s="104"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="104"/>
       <c r="C308" s="104"/>
-      <c r="D308" s="158" t="s">
-        <v>694</v>
-      </c>
-      <c r="E308" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="F308" s="110"/>
-      <c r="G308" s="110" t="s">
-        <v>681</v>
-      </c>
-      <c r="H308" s="110"/>
-      <c r="I308" s="110"/>
-      <c r="J308" s="110"/>
-      <c r="K308" s="110"/>
-      <c r="L308" s="110"/>
-      <c r="M308" s="110"/>
+      <c r="D308" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E308" s="161"/>
+      <c r="F308" s="185" t="s">
+        <v>932</v>
+      </c>
+      <c r="G308" s="185"/>
+      <c r="H308" s="58"/>
+      <c r="I308" s="58"/>
+      <c r="J308" s="58"/>
+      <c r="K308" s="58"/>
+      <c r="L308" s="58"/>
+      <c r="M308" s="58"/>
       <c r="N308" s="129"/>
       <c r="O308" s="129"/>
       <c r="P308" s="58"/>
@@ -33053,49 +33118,43 @@
       <c r="R308" s="58"/>
       <c r="S308" s="58"/>
       <c r="T308" s="104"/>
-      <c r="U308" s="110" t="s">
-        <v>681</v>
-      </c>
-      <c r="V308" s="110"/>
-      <c r="W308" s="110"/>
-      <c r="X308" s="110"/>
-      <c r="Y308" s="110"/>
-      <c r="Z308" s="110"/>
-      <c r="AA308" s="110"/>
-      <c r="AB308" s="110"/>
-      <c r="AC308" s="110"/>
-      <c r="AD308" s="110"/>
-      <c r="AE308" s="110"/>
-      <c r="AF308" s="110"/>
-      <c r="AG308" s="110"/>
-      <c r="AH308" s="110"/>
-      <c r="AI308" s="110"/>
-      <c r="AJ308" s="110"/>
+      <c r="U308" s="129"/>
+      <c r="V308" s="129"/>
+      <c r="W308" s="129"/>
+      <c r="X308" s="129"/>
+      <c r="Y308" s="129"/>
+      <c r="Z308" s="129"/>
+      <c r="AA308" s="129"/>
+      <c r="AB308" s="129"/>
+      <c r="AC308" s="129"/>
+      <c r="AD308" s="129"/>
+      <c r="AE308" s="129"/>
+      <c r="AF308" s="129"/>
+      <c r="AG308" s="129"/>
+      <c r="AH308" s="129"/>
+      <c r="AI308" s="129"/>
+      <c r="AJ308" s="129"/>
       <c r="AK308" s="104"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="104"/>
       <c r="C309" s="104"/>
-      <c r="D309" s="159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E309" s="58" t="s">
-        <v>625</v>
-      </c>
-      <c r="F309" s="58"/>
-      <c r="G309" s="182" t="s">
-        <v>734</v>
-      </c>
-      <c r="H309" s="160" t="s">
-        <v>702</v>
-      </c>
-      <c r="I309" s="160"/>
-      <c r="J309" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K309" s="160"/>
-      <c r="L309" s="160"/>
-      <c r="M309" s="160"/>
+      <c r="D309" s="158" t="s">
+        <v>694</v>
+      </c>
+      <c r="E309" s="110" t="s">
+        <v>681</v>
+      </c>
+      <c r="F309" s="110"/>
+      <c r="G309" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="H309" s="110"/>
+      <c r="I309" s="110"/>
+      <c r="J309" s="110"/>
+      <c r="K309" s="110"/>
+      <c r="L309" s="110"/>
+      <c r="M309" s="110"/>
       <c r="N309" s="129"/>
       <c r="O309" s="129"/>
       <c r="P309" s="58"/>
@@ -33103,47 +33162,49 @@
       <c r="R309" s="58"/>
       <c r="S309" s="58"/>
       <c r="T309" s="104"/>
-      <c r="U309" s="169" t="s">
-        <v>703</v>
-      </c>
-      <c r="V309" s="169"/>
-      <c r="W309" s="169"/>
-      <c r="X309" s="169"/>
-      <c r="Y309" s="169"/>
-      <c r="Z309" s="169"/>
-      <c r="AA309" s="169"/>
-      <c r="AB309" s="169"/>
-      <c r="AC309" s="169"/>
-      <c r="AD309" s="169"/>
-      <c r="AE309" s="169"/>
-      <c r="AF309" s="169"/>
-      <c r="AG309" s="169"/>
-      <c r="AH309" s="169"/>
-      <c r="AI309" s="169"/>
-      <c r="AJ309" s="169"/>
+      <c r="U309" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="V309" s="110"/>
+      <c r="W309" s="110"/>
+      <c r="X309" s="110"/>
+      <c r="Y309" s="110"/>
+      <c r="Z309" s="110"/>
+      <c r="AA309" s="110"/>
+      <c r="AB309" s="110"/>
+      <c r="AC309" s="110"/>
+      <c r="AD309" s="110"/>
+      <c r="AE309" s="110"/>
+      <c r="AF309" s="110"/>
+      <c r="AG309" s="110"/>
+      <c r="AH309" s="110"/>
+      <c r="AI309" s="110"/>
+      <c r="AJ309" s="110"/>
       <c r="AK309" s="104"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="104"/>
       <c r="C310" s="104"/>
-      <c r="D310" s="159"/>
+      <c r="D310" s="159" t="n">
+        <v>0</v>
+      </c>
       <c r="E310" s="58" t="s">
-        <v>865</v>
+        <v>625</v>
       </c>
       <c r="F310" s="58"/>
-      <c r="G310" s="162" t="s">
-        <v>735</v>
-      </c>
-      <c r="H310" s="162" t="s">
-        <v>705</v>
-      </c>
-      <c r="I310" s="162"/>
-      <c r="J310" s="162" t="s">
-        <v>706</v>
-      </c>
-      <c r="K310" s="162"/>
-      <c r="L310" s="162"/>
-      <c r="M310" s="162"/>
+      <c r="G310" s="182" t="s">
+        <v>734</v>
+      </c>
+      <c r="H310" s="160" t="s">
+        <v>702</v>
+      </c>
+      <c r="I310" s="160"/>
+      <c r="J310" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K310" s="160"/>
+      <c r="L310" s="160"/>
+      <c r="M310" s="160"/>
       <c r="N310" s="129"/>
       <c r="O310" s="129"/>
       <c r="P310" s="58"/>
@@ -33151,7 +33212,9 @@
       <c r="R310" s="58"/>
       <c r="S310" s="58"/>
       <c r="T310" s="104"/>
-      <c r="U310" s="169"/>
+      <c r="U310" s="169" t="s">
+        <v>703</v>
+      </c>
       <c r="V310" s="169"/>
       <c r="W310" s="169"/>
       <c r="X310" s="169"/>
@@ -33173,12 +33236,20 @@
       <c r="A311" s="104"/>
       <c r="C311" s="104"/>
       <c r="D311" s="159"/>
-      <c r="E311" s="58"/>
+      <c r="E311" s="58" t="s">
+        <v>865</v>
+      </c>
       <c r="F311" s="58"/>
-      <c r="G311" s="162"/>
-      <c r="H311" s="162"/>
+      <c r="G311" s="162" t="s">
+        <v>735</v>
+      </c>
+      <c r="H311" s="162" t="s">
+        <v>705</v>
+      </c>
       <c r="I311" s="162"/>
-      <c r="J311" s="162"/>
+      <c r="J311" s="162" t="s">
+        <v>706</v>
+      </c>
       <c r="K311" s="162"/>
       <c r="L311" s="162"/>
       <c r="M311" s="162"/>
@@ -33210,20 +33281,16 @@
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="104"/>
       <c r="C312" s="104"/>
-      <c r="D312" s="158" t="s">
-        <v>681</v>
-      </c>
-      <c r="E312" s="158"/>
-      <c r="F312" s="158"/>
-      <c r="G312" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="H312" s="110"/>
-      <c r="I312" s="110"/>
-      <c r="J312" s="110"/>
-      <c r="K312" s="110"/>
-      <c r="L312" s="110"/>
-      <c r="M312" s="110"/>
+      <c r="D312" s="159"/>
+      <c r="E312" s="58"/>
+      <c r="F312" s="58"/>
+      <c r="G312" s="162"/>
+      <c r="H312" s="162"/>
+      <c r="I312" s="162"/>
+      <c r="J312" s="162"/>
+      <c r="K312" s="162"/>
+      <c r="L312" s="162"/>
+      <c r="M312" s="162"/>
       <c r="N312" s="129"/>
       <c r="O312" s="129"/>
       <c r="P312" s="58"/>
@@ -33231,45 +33298,43 @@
       <c r="R312" s="58"/>
       <c r="S312" s="58"/>
       <c r="T312" s="104"/>
-      <c r="U312" s="110" t="s">
-        <v>682</v>
-      </c>
-      <c r="V312" s="110"/>
-      <c r="W312" s="110"/>
-      <c r="X312" s="110"/>
-      <c r="Y312" s="110"/>
-      <c r="Z312" s="110"/>
-      <c r="AA312" s="110"/>
-      <c r="AB312" s="110"/>
-      <c r="AC312" s="110"/>
-      <c r="AD312" s="110"/>
-      <c r="AE312" s="110"/>
-      <c r="AF312" s="110"/>
-      <c r="AG312" s="110"/>
-      <c r="AH312" s="110"/>
-      <c r="AI312" s="110"/>
-      <c r="AJ312" s="110"/>
+      <c r="U312" s="169"/>
+      <c r="V312" s="169"/>
+      <c r="W312" s="169"/>
+      <c r="X312" s="169"/>
+      <c r="Y312" s="169"/>
+      <c r="Z312" s="169"/>
+      <c r="AA312" s="169"/>
+      <c r="AB312" s="169"/>
+      <c r="AC312" s="169"/>
+      <c r="AD312" s="169"/>
+      <c r="AE312" s="169"/>
+      <c r="AF312" s="169"/>
+      <c r="AG312" s="169"/>
+      <c r="AH312" s="169"/>
+      <c r="AI312" s="169"/>
+      <c r="AJ312" s="169"/>
       <c r="AK312" s="104"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="104"/>
       <c r="C313" s="104"/>
-      <c r="D313" s="58" t="s">
-        <v>689</v>
-      </c>
-      <c r="E313" s="58"/>
-      <c r="F313" s="58"/>
-      <c r="G313" s="162" t="s">
-        <v>625</v>
-      </c>
-      <c r="H313" s="162"/>
-      <c r="I313" s="162"/>
-      <c r="J313" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K313" s="160"/>
-      <c r="L313" s="160"/>
-      <c r="M313" s="160"/>
+      <c r="D313" s="158" t="s">
+        <v>694</v>
+      </c>
+      <c r="E313" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="F313" s="110"/>
+      <c r="G313" s="110" t="s">
+        <v>681</v>
+      </c>
+      <c r="H313" s="110"/>
+      <c r="I313" s="110"/>
+      <c r="J313" s="110"/>
+      <c r="K313" s="110"/>
+      <c r="L313" s="110"/>
+      <c r="M313" s="110"/>
       <c r="N313" s="129"/>
       <c r="O313" s="129"/>
       <c r="P313" s="58"/>
@@ -33277,43 +33342,49 @@
       <c r="R313" s="58"/>
       <c r="S313" s="58"/>
       <c r="T313" s="104"/>
-      <c r="U313" s="169" t="s">
-        <v>703</v>
-      </c>
-      <c r="V313" s="169"/>
-      <c r="W313" s="169"/>
-      <c r="X313" s="169"/>
-      <c r="Y313" s="169"/>
-      <c r="Z313" s="169"/>
-      <c r="AA313" s="169"/>
-      <c r="AB313" s="169"/>
-      <c r="AC313" s="169"/>
-      <c r="AD313" s="169"/>
-      <c r="AE313" s="169"/>
-      <c r="AF313" s="169"/>
-      <c r="AG313" s="169"/>
-      <c r="AH313" s="169"/>
-      <c r="AI313" s="169"/>
-      <c r="AJ313" s="169"/>
+      <c r="U313" s="110" t="s">
+        <v>681</v>
+      </c>
+      <c r="V313" s="110"/>
+      <c r="W313" s="110"/>
+      <c r="X313" s="110"/>
+      <c r="Y313" s="110"/>
+      <c r="Z313" s="110"/>
+      <c r="AA313" s="110"/>
+      <c r="AB313" s="110"/>
+      <c r="AC313" s="110"/>
+      <c r="AD313" s="110"/>
+      <c r="AE313" s="110"/>
+      <c r="AF313" s="110"/>
+      <c r="AG313" s="110"/>
+      <c r="AH313" s="110"/>
+      <c r="AI313" s="110"/>
+      <c r="AJ313" s="110"/>
       <c r="AK313" s="104"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="104"/>
       <c r="C314" s="104"/>
-      <c r="D314" s="58"/>
-      <c r="E314" s="58"/>
+      <c r="D314" s="159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E314" s="58" t="s">
+        <v>625</v>
+      </c>
       <c r="F314" s="58"/>
-      <c r="G314" s="162" t="s">
-        <v>711</v>
-      </c>
-      <c r="H314" s="162"/>
-      <c r="I314" s="162"/>
-      <c r="J314" s="162" t="s">
-        <v>712</v>
-      </c>
-      <c r="K314" s="162"/>
-      <c r="L314" s="162"/>
-      <c r="M314" s="162"/>
+      <c r="G314" s="182" t="s">
+        <v>734</v>
+      </c>
+      <c r="H314" s="160" t="s">
+        <v>702</v>
+      </c>
+      <c r="I314" s="160"/>
+      <c r="J314" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K314" s="160"/>
+      <c r="L314" s="160"/>
+      <c r="M314" s="160"/>
       <c r="N314" s="129"/>
       <c r="O314" s="129"/>
       <c r="P314" s="58"/>
@@ -33321,7 +33392,9 @@
       <c r="R314" s="58"/>
       <c r="S314" s="58"/>
       <c r="T314" s="104"/>
-      <c r="U314" s="169"/>
+      <c r="U314" s="169" t="s">
+        <v>703</v>
+      </c>
       <c r="V314" s="169"/>
       <c r="W314" s="169"/>
       <c r="X314" s="169"/>
@@ -33342,13 +33415,21 @@
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="104"/>
       <c r="C315" s="104"/>
-      <c r="D315" s="58"/>
-      <c r="E315" s="58"/>
+      <c r="D315" s="159"/>
+      <c r="E315" s="58" t="s">
+        <v>865</v>
+      </c>
       <c r="F315" s="58"/>
-      <c r="G315" s="162"/>
-      <c r="H315" s="162"/>
+      <c r="G315" s="162" t="s">
+        <v>735</v>
+      </c>
+      <c r="H315" s="162" t="s">
+        <v>705</v>
+      </c>
       <c r="I315" s="162"/>
-      <c r="J315" s="162"/>
+      <c r="J315" s="162" t="s">
+        <v>706</v>
+      </c>
       <c r="K315" s="162"/>
       <c r="L315" s="162"/>
       <c r="M315" s="162"/>
@@ -33380,22 +33461,16 @@
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="104"/>
       <c r="C316" s="104"/>
-      <c r="D316" s="58"/>
+      <c r="D316" s="159"/>
       <c r="E316" s="58"/>
       <c r="F316" s="58"/>
-      <c r="G316" s="58" t="s">
-        <v>830</v>
-      </c>
-      <c r="H316" s="58"/>
-      <c r="I316" s="162" t="s">
-        <v>715</v>
-      </c>
-      <c r="J316" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K316" s="160"/>
-      <c r="L316" s="160"/>
-      <c r="M316" s="160"/>
+      <c r="G316" s="162"/>
+      <c r="H316" s="162"/>
+      <c r="I316" s="162"/>
+      <c r="J316" s="162"/>
+      <c r="K316" s="162"/>
+      <c r="L316" s="162"/>
+      <c r="M316" s="162"/>
       <c r="N316" s="129"/>
       <c r="O316" s="129"/>
       <c r="P316" s="58"/>
@@ -33403,41 +33478,41 @@
       <c r="R316" s="58"/>
       <c r="S316" s="58"/>
       <c r="T316" s="104"/>
-      <c r="U316" s="162" t="s">
-        <v>716</v>
-      </c>
-      <c r="V316" s="162"/>
-      <c r="W316" s="162"/>
-      <c r="X316" s="162"/>
-      <c r="Y316" s="162"/>
-      <c r="Z316" s="162"/>
-      <c r="AA316" s="162"/>
-      <c r="AB316" s="162"/>
-      <c r="AC316" s="162"/>
-      <c r="AD316" s="162"/>
-      <c r="AE316" s="162"/>
-      <c r="AF316" s="162"/>
-      <c r="AG316" s="162"/>
-      <c r="AH316" s="162"/>
-      <c r="AI316" s="162"/>
-      <c r="AJ316" s="162"/>
+      <c r="U316" s="169"/>
+      <c r="V316" s="169"/>
+      <c r="W316" s="169"/>
+      <c r="X316" s="169"/>
+      <c r="Y316" s="169"/>
+      <c r="Z316" s="169"/>
+      <c r="AA316" s="169"/>
+      <c r="AB316" s="169"/>
+      <c r="AC316" s="169"/>
+      <c r="AD316" s="169"/>
+      <c r="AE316" s="169"/>
+      <c r="AF316" s="169"/>
+      <c r="AG316" s="169"/>
+      <c r="AH316" s="169"/>
+      <c r="AI316" s="169"/>
+      <c r="AJ316" s="169"/>
       <c r="AK316" s="104"/>
     </row>
-    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="104"/>
       <c r="C317" s="104"/>
-      <c r="D317" s="58"/>
-      <c r="E317" s="58"/>
-      <c r="F317" s="58"/>
-      <c r="I317" s="161" t="s">
-        <v>933</v>
-      </c>
-      <c r="J317" s="162" t="s">
-        <v>718</v>
-      </c>
-      <c r="K317" s="162"/>
-      <c r="L317" s="162"/>
-      <c r="M317" s="162"/>
+      <c r="D317" s="158" t="s">
+        <v>681</v>
+      </c>
+      <c r="E317" s="158"/>
+      <c r="F317" s="158"/>
+      <c r="G317" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="H317" s="110"/>
+      <c r="I317" s="110"/>
+      <c r="J317" s="110"/>
+      <c r="K317" s="110"/>
+      <c r="L317" s="110"/>
+      <c r="M317" s="110"/>
       <c r="N317" s="129"/>
       <c r="O317" s="129"/>
       <c r="P317" s="58"/>
@@ -33445,39 +33520,45 @@
       <c r="R317" s="58"/>
       <c r="S317" s="58"/>
       <c r="T317" s="104"/>
-      <c r="U317" s="169" t="s">
-        <v>719</v>
-      </c>
-      <c r="V317" s="169"/>
-      <c r="W317" s="169"/>
-      <c r="X317" s="169"/>
-      <c r="Y317" s="169"/>
-      <c r="Z317" s="169"/>
-      <c r="AA317" s="169"/>
-      <c r="AB317" s="169"/>
-      <c r="AC317" s="162" t="s">
-        <v>720</v>
-      </c>
-      <c r="AD317" s="162"/>
-      <c r="AE317" s="162"/>
-      <c r="AF317" s="162"/>
-      <c r="AG317" s="162"/>
-      <c r="AH317" s="162"/>
-      <c r="AI317" s="162"/>
-      <c r="AJ317" s="162"/>
+      <c r="U317" s="110" t="s">
+        <v>682</v>
+      </c>
+      <c r="V317" s="110"/>
+      <c r="W317" s="110"/>
+      <c r="X317" s="110"/>
+      <c r="Y317" s="110"/>
+      <c r="Z317" s="110"/>
+      <c r="AA317" s="110"/>
+      <c r="AB317" s="110"/>
+      <c r="AC317" s="110"/>
+      <c r="AD317" s="110"/>
+      <c r="AE317" s="110"/>
+      <c r="AF317" s="110"/>
+      <c r="AG317" s="110"/>
+      <c r="AH317" s="110"/>
+      <c r="AI317" s="110"/>
+      <c r="AJ317" s="110"/>
       <c r="AK317" s="104"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="104"/>
       <c r="C318" s="104"/>
-      <c r="D318" s="58"/>
+      <c r="D318" s="58" t="s">
+        <v>689</v>
+      </c>
       <c r="E318" s="58"/>
       <c r="F318" s="58"/>
-      <c r="I318" s="161"/>
-      <c r="J318" s="162"/>
-      <c r="K318" s="162"/>
-      <c r="L318" s="162"/>
-      <c r="M318" s="162"/>
+      <c r="G318" s="162" t="s">
+        <v>625</v>
+      </c>
+      <c r="H318" s="162"/>
+      <c r="I318" s="162"/>
+      <c r="J318" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K318" s="160"/>
+      <c r="L318" s="160"/>
+      <c r="M318" s="160"/>
       <c r="N318" s="129"/>
       <c r="O318" s="129"/>
       <c r="P318" s="58"/>
@@ -33485,26 +33566,24 @@
       <c r="R318" s="58"/>
       <c r="S318" s="58"/>
       <c r="T318" s="104"/>
-      <c r="U318" s="162" t="s">
-        <v>934</v>
-      </c>
-      <c r="V318" s="162"/>
-      <c r="W318" s="162"/>
-      <c r="X318" s="162"/>
-      <c r="Y318" s="162"/>
-      <c r="Z318" s="162"/>
-      <c r="AA318" s="162"/>
-      <c r="AB318" s="162"/>
-      <c r="AC318" s="162" t="s">
-        <v>935</v>
-      </c>
-      <c r="AD318" s="162"/>
-      <c r="AE318" s="162"/>
-      <c r="AF318" s="162"/>
-      <c r="AG318" s="162"/>
-      <c r="AH318" s="162"/>
-      <c r="AI318" s="162"/>
-      <c r="AJ318" s="162"/>
+      <c r="U318" s="169" t="s">
+        <v>703</v>
+      </c>
+      <c r="V318" s="169"/>
+      <c r="W318" s="169"/>
+      <c r="X318" s="169"/>
+      <c r="Y318" s="169"/>
+      <c r="Z318" s="169"/>
+      <c r="AA318" s="169"/>
+      <c r="AB318" s="169"/>
+      <c r="AC318" s="169"/>
+      <c r="AD318" s="169"/>
+      <c r="AE318" s="169"/>
+      <c r="AF318" s="169"/>
+      <c r="AG318" s="169"/>
+      <c r="AH318" s="169"/>
+      <c r="AI318" s="169"/>
+      <c r="AJ318" s="169"/>
       <c r="AK318" s="104"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33513,8 +33592,14 @@
       <c r="D319" s="58"/>
       <c r="E319" s="58"/>
       <c r="F319" s="58"/>
-      <c r="I319" s="161"/>
-      <c r="J319" s="162"/>
+      <c r="G319" s="162" t="s">
+        <v>711</v>
+      </c>
+      <c r="H319" s="162"/>
+      <c r="I319" s="162"/>
+      <c r="J319" s="162" t="s">
+        <v>712</v>
+      </c>
       <c r="K319" s="162"/>
       <c r="L319" s="162"/>
       <c r="M319" s="162"/>
@@ -33525,22 +33610,22 @@
       <c r="R319" s="58"/>
       <c r="S319" s="58"/>
       <c r="T319" s="104"/>
-      <c r="U319" s="162"/>
-      <c r="V319" s="162"/>
-      <c r="W319" s="162"/>
-      <c r="X319" s="162"/>
-      <c r="Y319" s="162"/>
-      <c r="Z319" s="162"/>
-      <c r="AA319" s="162"/>
-      <c r="AB319" s="162"/>
-      <c r="AC319" s="162"/>
-      <c r="AD319" s="162"/>
-      <c r="AE319" s="162"/>
-      <c r="AF319" s="162"/>
-      <c r="AG319" s="162"/>
-      <c r="AH319" s="162"/>
-      <c r="AI319" s="162"/>
-      <c r="AJ319" s="162"/>
+      <c r="U319" s="169"/>
+      <c r="V319" s="169"/>
+      <c r="W319" s="169"/>
+      <c r="X319" s="169"/>
+      <c r="Y319" s="169"/>
+      <c r="Z319" s="169"/>
+      <c r="AA319" s="169"/>
+      <c r="AB319" s="169"/>
+      <c r="AC319" s="169"/>
+      <c r="AD319" s="169"/>
+      <c r="AE319" s="169"/>
+      <c r="AF319" s="169"/>
+      <c r="AG319" s="169"/>
+      <c r="AH319" s="169"/>
+      <c r="AI319" s="169"/>
+      <c r="AJ319" s="169"/>
       <c r="AK319" s="104"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33549,17 +33634,13 @@
       <c r="D320" s="58"/>
       <c r="E320" s="58"/>
       <c r="F320" s="58"/>
-      <c r="G320" s="162" t="s">
-        <v>696</v>
-      </c>
+      <c r="G320" s="162"/>
       <c r="H320" s="162"/>
       <c r="I320" s="162"/>
-      <c r="J320" s="160" t="s">
-        <v>686</v>
-      </c>
-      <c r="K320" s="160"/>
-      <c r="L320" s="160"/>
-      <c r="M320" s="160"/>
+      <c r="J320" s="162"/>
+      <c r="K320" s="162"/>
+      <c r="L320" s="162"/>
+      <c r="M320" s="162"/>
       <c r="N320" s="129"/>
       <c r="O320" s="129"/>
       <c r="P320" s="58"/>
@@ -33567,9 +33648,7 @@
       <c r="R320" s="58"/>
       <c r="S320" s="58"/>
       <c r="T320" s="104"/>
-      <c r="U320" s="169" t="s">
-        <v>723</v>
-      </c>
+      <c r="U320" s="169"/>
       <c r="V320" s="169"/>
       <c r="W320" s="169"/>
       <c r="X320" s="169"/>
@@ -33593,19 +33672,19 @@
       <c r="D321" s="58"/>
       <c r="E321" s="58"/>
       <c r="F321" s="58"/>
-      <c r="G321" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="H321" s="184" t="s">
-        <v>931</v>
-      </c>
-      <c r="I321" s="184"/>
-      <c r="J321" s="162" t="s">
-        <v>725</v>
-      </c>
-      <c r="K321" s="162"/>
-      <c r="L321" s="162"/>
-      <c r="M321" s="162"/>
+      <c r="G321" s="58" t="s">
+        <v>830</v>
+      </c>
+      <c r="H321" s="58"/>
+      <c r="I321" s="162" t="s">
+        <v>715</v>
+      </c>
+      <c r="J321" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K321" s="160"/>
+      <c r="L321" s="160"/>
+      <c r="M321" s="160"/>
       <c r="N321" s="129"/>
       <c r="O321" s="129"/>
       <c r="P321" s="58"/>
@@ -33613,38 +33692,38 @@
       <c r="R321" s="58"/>
       <c r="S321" s="58"/>
       <c r="T321" s="104"/>
-      <c r="U321" s="169"/>
-      <c r="V321" s="169"/>
-      <c r="W321" s="169"/>
-      <c r="X321" s="169"/>
-      <c r="Y321" s="169"/>
-      <c r="Z321" s="169"/>
-      <c r="AA321" s="169"/>
-      <c r="AB321" s="169"/>
-      <c r="AC321" s="169"/>
-      <c r="AD321" s="169"/>
-      <c r="AE321" s="169"/>
-      <c r="AF321" s="169"/>
-      <c r="AG321" s="169"/>
-      <c r="AH321" s="169"/>
-      <c r="AI321" s="169"/>
-      <c r="AJ321" s="169"/>
+      <c r="U321" s="162" t="s">
+        <v>716</v>
+      </c>
+      <c r="V321" s="162"/>
+      <c r="W321" s="162"/>
+      <c r="X321" s="162"/>
+      <c r="Y321" s="162"/>
+      <c r="Z321" s="162"/>
+      <c r="AA321" s="162"/>
+      <c r="AB321" s="162"/>
+      <c r="AC321" s="162"/>
+      <c r="AD321" s="162"/>
+      <c r="AE321" s="162"/>
+      <c r="AF321" s="162"/>
+      <c r="AG321" s="162"/>
+      <c r="AH321" s="162"/>
+      <c r="AI321" s="162"/>
+      <c r="AJ321" s="162"/>
       <c r="AK321" s="104"/>
     </row>
-    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="104"/>
       <c r="C322" s="104"/>
       <c r="D322" s="58"/>
       <c r="E322" s="58"/>
       <c r="F322" s="58"/>
-      <c r="G322" s="175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H322" s="185" t="s">
-        <v>932</v>
-      </c>
-      <c r="I322" s="185"/>
-      <c r="J322" s="162"/>
+      <c r="I322" s="161" t="s">
+        <v>933</v>
+      </c>
+      <c r="J322" s="162" t="s">
+        <v>718</v>
+      </c>
       <c r="K322" s="162"/>
       <c r="L322" s="162"/>
       <c r="M322" s="162"/>
@@ -33655,7 +33734,9 @@
       <c r="R322" s="58"/>
       <c r="S322" s="58"/>
       <c r="T322" s="104"/>
-      <c r="U322" s="169"/>
+      <c r="U322" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V322" s="169"/>
       <c r="W322" s="169"/>
       <c r="X322" s="169"/>
@@ -33663,148 +33744,121 @@
       <c r="Z322" s="169"/>
       <c r="AA322" s="169"/>
       <c r="AB322" s="169"/>
-      <c r="AC322" s="169"/>
-      <c r="AD322" s="169"/>
-      <c r="AE322" s="169"/>
-      <c r="AF322" s="169"/>
-      <c r="AG322" s="169"/>
-      <c r="AH322" s="169"/>
-      <c r="AI322" s="169"/>
-      <c r="AJ322" s="169"/>
+      <c r="AC322" s="162" t="s">
+        <v>720</v>
+      </c>
+      <c r="AD322" s="162"/>
+      <c r="AE322" s="162"/>
+      <c r="AF322" s="162"/>
+      <c r="AG322" s="162"/>
+      <c r="AH322" s="162"/>
+      <c r="AI322" s="162"/>
+      <c r="AJ322" s="162"/>
       <c r="AK322" s="104"/>
     </row>
-    <row r="323" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="104"/>
-      <c r="B323" s="104"/>
       <c r="C323" s="104"/>
-      <c r="D323" s="104"/>
-      <c r="E323" s="104"/>
-      <c r="F323" s="104"/>
-      <c r="G323" s="104"/>
-      <c r="H323" s="104"/>
-      <c r="I323" s="104"/>
-      <c r="J323" s="104"/>
-      <c r="K323" s="104"/>
-      <c r="L323" s="177"/>
-      <c r="M323" s="104"/>
-      <c r="N323" s="104"/>
-      <c r="O323" s="104"/>
-      <c r="P323" s="104"/>
-      <c r="Q323" s="104"/>
-      <c r="R323" s="104"/>
-      <c r="S323" s="104"/>
+      <c r="D323" s="58"/>
+      <c r="E323" s="58"/>
+      <c r="F323" s="58"/>
+      <c r="I323" s="161"/>
+      <c r="J323" s="162"/>
+      <c r="K323" s="162"/>
+      <c r="L323" s="162"/>
+      <c r="M323" s="162"/>
+      <c r="N323" s="129"/>
+      <c r="O323" s="129"/>
+      <c r="P323" s="58"/>
+      <c r="Q323" s="58"/>
+      <c r="R323" s="58"/>
+      <c r="S323" s="58"/>
       <c r="T323" s="104"/>
-      <c r="U323" s="104"/>
-      <c r="V323" s="104"/>
-      <c r="W323" s="104"/>
-      <c r="X323" s="104"/>
-      <c r="Y323" s="104"/>
-      <c r="Z323" s="104"/>
-      <c r="AA323" s="104"/>
-      <c r="AB323" s="104"/>
-      <c r="AC323" s="104"/>
-      <c r="AD323" s="104"/>
-      <c r="AE323" s="104"/>
-      <c r="AF323" s="104"/>
-      <c r="AG323" s="104"/>
-      <c r="AH323" s="104"/>
-      <c r="AI323" s="104"/>
-      <c r="AJ323" s="104"/>
+      <c r="U323" s="162" t="s">
+        <v>934</v>
+      </c>
+      <c r="V323" s="162"/>
+      <c r="W323" s="162"/>
+      <c r="X323" s="162"/>
+      <c r="Y323" s="162"/>
+      <c r="Z323" s="162"/>
+      <c r="AA323" s="162"/>
+      <c r="AB323" s="162"/>
+      <c r="AC323" s="162" t="s">
+        <v>935</v>
+      </c>
+      <c r="AD323" s="162"/>
+      <c r="AE323" s="162"/>
+      <c r="AF323" s="162"/>
+      <c r="AG323" s="162"/>
+      <c r="AH323" s="162"/>
+      <c r="AI323" s="162"/>
+      <c r="AJ323" s="162"/>
       <c r="AK323" s="104"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="104"/>
-      <c r="B324" s="54" t="s">
-        <v>487</v>
-      </c>
       <c r="C324" s="104"/>
-      <c r="D324" s="149" t="s">
-        <v>936</v>
-      </c>
-      <c r="E324" s="149" t="s">
-        <v>937</v>
-      </c>
-      <c r="F324" s="58" t="s">
-        <v>938</v>
-      </c>
-      <c r="G324" s="58"/>
-      <c r="H324" s="110" t="s">
-        <v>755</v>
-      </c>
-      <c r="I324" s="110"/>
-      <c r="J324" s="110"/>
-      <c r="K324" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="L324" s="58"/>
-      <c r="M324" s="58"/>
-      <c r="N324" s="58"/>
-      <c r="O324" s="110" t="s">
-        <v>772</v>
-      </c>
-      <c r="P324" s="58" t="s">
-        <v>939</v>
-      </c>
+      <c r="D324" s="58"/>
+      <c r="E324" s="58"/>
+      <c r="F324" s="58"/>
+      <c r="I324" s="161"/>
+      <c r="J324" s="162"/>
+      <c r="K324" s="162"/>
+      <c r="L324" s="162"/>
+      <c r="M324" s="162"/>
+      <c r="N324" s="129"/>
+      <c r="O324" s="129"/>
+      <c r="P324" s="58"/>
       <c r="Q324" s="58"/>
       <c r="R324" s="58"/>
       <c r="S324" s="58"/>
       <c r="T324" s="104"/>
-      <c r="U324" s="169" t="s">
-        <v>719</v>
-      </c>
-      <c r="V324" s="169"/>
-      <c r="W324" s="169"/>
-      <c r="X324" s="169"/>
-      <c r="Y324" s="169"/>
-      <c r="Z324" s="169"/>
-      <c r="AA324" s="169"/>
-      <c r="AB324" s="169"/>
-      <c r="AC324" s="169"/>
-      <c r="AD324" s="169"/>
-      <c r="AE324" s="169"/>
-      <c r="AF324" s="169"/>
-      <c r="AG324" s="169"/>
-      <c r="AH324" s="169"/>
-      <c r="AI324" s="169"/>
-      <c r="AJ324" s="169"/>
+      <c r="U324" s="162"/>
+      <c r="V324" s="162"/>
+      <c r="W324" s="162"/>
+      <c r="X324" s="162"/>
+      <c r="Y324" s="162"/>
+      <c r="Z324" s="162"/>
+      <c r="AA324" s="162"/>
+      <c r="AB324" s="162"/>
+      <c r="AC324" s="162"/>
+      <c r="AD324" s="162"/>
+      <c r="AE324" s="162"/>
+      <c r="AF324" s="162"/>
+      <c r="AG324" s="162"/>
+      <c r="AH324" s="162"/>
+      <c r="AI324" s="162"/>
+      <c r="AJ324" s="162"/>
       <c r="AK324" s="104"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="104"/>
-      <c r="B325" s="54" t="s">
-        <v>492</v>
-      </c>
       <c r="C325" s="104"/>
-      <c r="D325" s="94" t="s">
-        <v>921</v>
-      </c>
-      <c r="E325" s="227" t="s">
-        <v>940</v>
-      </c>
-      <c r="F325" s="228" t="s">
-        <v>941</v>
-      </c>
-      <c r="G325" s="228"/>
-      <c r="H325" s="58" t="s">
-        <v>942</v>
-      </c>
-      <c r="I325" s="58"/>
-      <c r="J325" s="58"/>
-      <c r="K325" s="229" t="s">
-        <v>943</v>
-      </c>
-      <c r="L325" s="229"/>
-      <c r="M325" s="229"/>
-      <c r="N325" s="229"/>
-      <c r="O325" s="58" t="s">
-        <v>944</v>
-      </c>
+      <c r="D325" s="58"/>
+      <c r="E325" s="58"/>
+      <c r="F325" s="58"/>
+      <c r="G325" s="162" t="s">
+        <v>696</v>
+      </c>
+      <c r="H325" s="162"/>
+      <c r="I325" s="162"/>
+      <c r="J325" s="160" t="s">
+        <v>686</v>
+      </c>
+      <c r="K325" s="160"/>
+      <c r="L325" s="160"/>
+      <c r="M325" s="160"/>
+      <c r="N325" s="129"/>
+      <c r="O325" s="129"/>
       <c r="P325" s="58"/>
       <c r="Q325" s="58"/>
       <c r="R325" s="58"/>
       <c r="S325" s="58"/>
       <c r="T325" s="104"/>
-      <c r="U325" s="169"/>
+      <c r="U325" s="169" t="s">
+        <v>723</v>
+      </c>
       <c r="V325" s="169"/>
       <c r="W325" s="169"/>
       <c r="X325" s="169"/>
@@ -33824,30 +33878,25 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="104"/>
-      <c r="B326" s="54" t="s">
-        <v>497</v>
-      </c>
       <c r="C326" s="104"/>
-      <c r="D326" s="95" t="s">
-        <v>829</v>
-      </c>
-      <c r="E326" s="230" t="s">
-        <v>945</v>
-      </c>
-      <c r="F326" s="231" t="s">
-        <v>946</v>
-      </c>
-      <c r="G326" s="231"/>
-      <c r="H326" s="58"/>
-      <c r="I326" s="58"/>
-      <c r="J326" s="58"/>
-      <c r="K326" s="232" t="s">
-        <v>947</v>
-      </c>
-      <c r="L326" s="232"/>
-      <c r="M326" s="232"/>
-      <c r="N326" s="232"/>
-      <c r="O326" s="58"/>
+      <c r="D326" s="58"/>
+      <c r="E326" s="58"/>
+      <c r="F326" s="58"/>
+      <c r="G326" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" s="184" t="s">
+        <v>931</v>
+      </c>
+      <c r="I326" s="184"/>
+      <c r="J326" s="162" t="s">
+        <v>725</v>
+      </c>
+      <c r="K326" s="162"/>
+      <c r="L326" s="162"/>
+      <c r="M326" s="162"/>
+      <c r="N326" s="129"/>
+      <c r="O326" s="129"/>
       <c r="P326" s="58"/>
       <c r="Q326" s="58"/>
       <c r="R326" s="58"/>
@@ -33873,26 +33922,23 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="104"/>
-      <c r="B327" s="54" t="s">
-        <v>501</v>
-      </c>
       <c r="C327" s="104"/>
-      <c r="D327" s="95"/>
-      <c r="E327" s="95"/>
-      <c r="F327" s="231" t="s">
-        <v>948</v>
-      </c>
-      <c r="G327" s="231"/>
-      <c r="H327" s="58"/>
-      <c r="I327" s="58"/>
-      <c r="J327" s="58"/>
-      <c r="K327" s="232" t="s">
-        <v>949</v>
-      </c>
-      <c r="L327" s="232"/>
-      <c r="M327" s="232"/>
-      <c r="N327" s="232"/>
-      <c r="O327" s="58"/>
+      <c r="D327" s="58"/>
+      <c r="E327" s="58"/>
+      <c r="F327" s="58"/>
+      <c r="G327" s="175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H327" s="185" t="s">
+        <v>932</v>
+      </c>
+      <c r="I327" s="185"/>
+      <c r="J327" s="162"/>
+      <c r="K327" s="162"/>
+      <c r="L327" s="162"/>
+      <c r="M327" s="162"/>
+      <c r="N327" s="129"/>
+      <c r="O327" s="129"/>
       <c r="P327" s="58"/>
       <c r="Q327" s="58"/>
       <c r="R327" s="58"/>
@@ -33916,77 +33962,85 @@
       <c r="AJ327" s="169"/>
       <c r="AK327" s="104"/>
     </row>
-    <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="104"/>
-      <c r="B328" s="54" t="s">
-        <v>504</v>
-      </c>
+      <c r="B328" s="104"/>
       <c r="C328" s="104"/>
-      <c r="D328" s="95"/>
-      <c r="E328" s="95"/>
-      <c r="F328" s="231" t="s">
-        <v>950</v>
-      </c>
-      <c r="G328" s="231"/>
-      <c r="H328" s="58"/>
-      <c r="I328" s="58"/>
-      <c r="J328" s="58"/>
-      <c r="K328" s="232" t="s">
-        <v>951</v>
-      </c>
-      <c r="L328" s="232"/>
-      <c r="M328" s="232"/>
-      <c r="N328" s="232"/>
-      <c r="O328" s="58"/>
-      <c r="P328" s="58"/>
-      <c r="Q328" s="58"/>
-      <c r="R328" s="58"/>
-      <c r="S328" s="58"/>
+      <c r="D328" s="104"/>
+      <c r="E328" s="104"/>
+      <c r="F328" s="104"/>
+      <c r="G328" s="104"/>
+      <c r="H328" s="104"/>
+      <c r="I328" s="104"/>
+      <c r="J328" s="104"/>
+      <c r="K328" s="104"/>
+      <c r="L328" s="177"/>
+      <c r="M328" s="104"/>
+      <c r="N328" s="104"/>
+      <c r="O328" s="104"/>
+      <c r="P328" s="104"/>
+      <c r="Q328" s="104"/>
+      <c r="R328" s="104"/>
+      <c r="S328" s="104"/>
       <c r="T328" s="104"/>
-      <c r="U328" s="169"/>
-      <c r="V328" s="169"/>
-      <c r="W328" s="169"/>
-      <c r="X328" s="169"/>
-      <c r="Y328" s="169"/>
-      <c r="Z328" s="169"/>
-      <c r="AA328" s="169"/>
-      <c r="AB328" s="169"/>
-      <c r="AC328" s="169"/>
-      <c r="AD328" s="169"/>
-      <c r="AE328" s="169"/>
-      <c r="AF328" s="169"/>
-      <c r="AG328" s="169"/>
-      <c r="AH328" s="169"/>
-      <c r="AI328" s="169"/>
-      <c r="AJ328" s="169"/>
+      <c r="U328" s="104"/>
+      <c r="V328" s="104"/>
+      <c r="W328" s="104"/>
+      <c r="X328" s="104"/>
+      <c r="Y328" s="104"/>
+      <c r="Z328" s="104"/>
+      <c r="AA328" s="104"/>
+      <c r="AB328" s="104"/>
+      <c r="AC328" s="104"/>
+      <c r="AD328" s="104"/>
+      <c r="AE328" s="104"/>
+      <c r="AF328" s="104"/>
+      <c r="AG328" s="104"/>
+      <c r="AH328" s="104"/>
+      <c r="AI328" s="104"/>
+      <c r="AJ328" s="104"/>
       <c r="AK328" s="104"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="104"/>
       <c r="B329" s="54" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="C329" s="104"/>
-      <c r="D329" s="95"/>
-      <c r="E329" s="95"/>
-      <c r="F329" s="233"/>
-      <c r="G329" s="233"/>
-      <c r="H329" s="58"/>
-      <c r="I329" s="58"/>
-      <c r="J329" s="58"/>
-      <c r="K329" s="232" t="s">
-        <v>952</v>
-      </c>
-      <c r="L329" s="232"/>
-      <c r="M329" s="232"/>
-      <c r="N329" s="232"/>
-      <c r="O329" s="58"/>
-      <c r="P329" s="58"/>
+      <c r="D329" s="149" t="s">
+        <v>936</v>
+      </c>
+      <c r="E329" s="149" t="s">
+        <v>937</v>
+      </c>
+      <c r="F329" s="58" t="s">
+        <v>938</v>
+      </c>
+      <c r="G329" s="58"/>
+      <c r="H329" s="110" t="s">
+        <v>755</v>
+      </c>
+      <c r="I329" s="110"/>
+      <c r="J329" s="110"/>
+      <c r="K329" s="58" t="s">
+        <v>728</v>
+      </c>
+      <c r="L329" s="58"/>
+      <c r="M329" s="58"/>
+      <c r="N329" s="58"/>
+      <c r="O329" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="P329" s="58" t="s">
+        <v>939</v>
+      </c>
       <c r="Q329" s="58"/>
       <c r="R329" s="58"/>
       <c r="S329" s="58"/>
       <c r="T329" s="104"/>
-      <c r="U329" s="169"/>
+      <c r="U329" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V329" s="169"/>
       <c r="W329" s="169"/>
       <c r="X329" s="169"/>
@@ -34007,23 +34061,33 @@
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="104"/>
       <c r="B330" s="54" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="C330" s="104"/>
-      <c r="D330" s="95"/>
-      <c r="E330" s="95"/>
-      <c r="F330" s="233"/>
-      <c r="G330" s="233"/>
-      <c r="H330" s="58"/>
+      <c r="D330" s="94" t="s">
+        <v>921</v>
+      </c>
+      <c r="E330" s="227" t="s">
+        <v>940</v>
+      </c>
+      <c r="F330" s="228" t="s">
+        <v>941</v>
+      </c>
+      <c r="G330" s="228"/>
+      <c r="H330" s="58" t="s">
+        <v>942</v>
+      </c>
       <c r="I330" s="58"/>
       <c r="J330" s="58"/>
-      <c r="K330" s="232" t="s">
-        <v>953</v>
-      </c>
-      <c r="L330" s="232"/>
-      <c r="M330" s="232"/>
-      <c r="N330" s="232"/>
-      <c r="O330" s="58"/>
+      <c r="K330" s="229" t="s">
+        <v>943</v>
+      </c>
+      <c r="L330" s="229"/>
+      <c r="M330" s="229"/>
+      <c r="N330" s="229"/>
+      <c r="O330" s="58" t="s">
+        <v>944</v>
+      </c>
       <c r="P330" s="58"/>
       <c r="Q330" s="58"/>
       <c r="R330" s="58"/>
@@ -34050,18 +34114,24 @@
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="104"/>
       <c r="B331" s="54" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="C331" s="104"/>
-      <c r="D331" s="95"/>
-      <c r="E331" s="95"/>
-      <c r="F331" s="233"/>
-      <c r="G331" s="233"/>
+      <c r="D331" s="95" t="s">
+        <v>829</v>
+      </c>
+      <c r="E331" s="230" t="s">
+        <v>945</v>
+      </c>
+      <c r="F331" s="231" t="s">
+        <v>946</v>
+      </c>
+      <c r="G331" s="231"/>
       <c r="H331" s="58"/>
       <c r="I331" s="58"/>
       <c r="J331" s="58"/>
       <c r="K331" s="232" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="L331" s="232"/>
       <c r="M331" s="232"/>
@@ -34092,16 +34162,21 @@
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="104"/>
+      <c r="B332" s="54" t="s">
+        <v>501</v>
+      </c>
       <c r="C332" s="104"/>
       <c r="D332" s="95"/>
       <c r="E332" s="95"/>
-      <c r="F332" s="233"/>
-      <c r="G332" s="233"/>
+      <c r="F332" s="231" t="s">
+        <v>948</v>
+      </c>
+      <c r="G332" s="231"/>
       <c r="H332" s="58"/>
       <c r="I332" s="58"/>
       <c r="J332" s="58"/>
       <c r="K332" s="232" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="L332" s="232"/>
       <c r="M332" s="232"/>
@@ -34132,16 +34207,21 @@
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="104"/>
+      <c r="B333" s="54" t="s">
+        <v>504</v>
+      </c>
       <c r="C333" s="104"/>
       <c r="D333" s="95"/>
       <c r="E333" s="95"/>
-      <c r="F333" s="233"/>
-      <c r="G333" s="233"/>
+      <c r="F333" s="231" t="s">
+        <v>950</v>
+      </c>
+      <c r="G333" s="231"/>
       <c r="H333" s="58"/>
       <c r="I333" s="58"/>
       <c r="J333" s="58"/>
       <c r="K333" s="232" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="L333" s="232"/>
       <c r="M333" s="232"/>
@@ -34172,6 +34252,9 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="104"/>
+      <c r="B334" s="54" t="s">
+        <v>507</v>
+      </c>
       <c r="C334" s="104"/>
       <c r="D334" s="95"/>
       <c r="E334" s="95"/>
@@ -34181,7 +34264,7 @@
       <c r="I334" s="58"/>
       <c r="J334" s="58"/>
       <c r="K334" s="232" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="L334" s="232"/>
       <c r="M334" s="232"/>
@@ -34212,6 +34295,9 @@
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="104"/>
+      <c r="B335" s="54" t="s">
+        <v>510</v>
+      </c>
       <c r="C335" s="104"/>
       <c r="D335" s="95"/>
       <c r="E335" s="95"/>
@@ -34221,7 +34307,7 @@
       <c r="I335" s="58"/>
       <c r="J335" s="58"/>
       <c r="K335" s="232" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="L335" s="232"/>
       <c r="M335" s="232"/>
@@ -34252,6 +34338,9 @@
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="104"/>
+      <c r="B336" s="54" t="s">
+        <v>514</v>
+      </c>
       <c r="C336" s="104"/>
       <c r="D336" s="95"/>
       <c r="E336" s="95"/>
@@ -34261,7 +34350,7 @@
       <c r="I336" s="58"/>
       <c r="J336" s="58"/>
       <c r="K336" s="232" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="L336" s="232"/>
       <c r="M336" s="232"/>
@@ -34301,7 +34390,7 @@
       <c r="I337" s="58"/>
       <c r="J337" s="58"/>
       <c r="K337" s="232" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="L337" s="232"/>
       <c r="M337" s="232"/>
@@ -34341,7 +34430,7 @@
       <c r="I338" s="58"/>
       <c r="J338" s="58"/>
       <c r="K338" s="232" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="L338" s="232"/>
       <c r="M338" s="232"/>
@@ -34381,7 +34470,7 @@
       <c r="I339" s="58"/>
       <c r="J339" s="58"/>
       <c r="K339" s="232" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="L339" s="232"/>
       <c r="M339" s="232"/>
@@ -34413,19 +34502,19 @@
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="104"/>
       <c r="C340" s="104"/>
-      <c r="D340" s="92"/>
-      <c r="E340" s="92"/>
-      <c r="F340" s="234"/>
-      <c r="G340" s="234"/>
+      <c r="D340" s="95"/>
+      <c r="E340" s="95"/>
+      <c r="F340" s="233"/>
+      <c r="G340" s="233"/>
       <c r="H340" s="58"/>
       <c r="I340" s="58"/>
       <c r="J340" s="58"/>
-      <c r="K340" s="235" t="s">
-        <v>963</v>
-      </c>
-      <c r="L340" s="235"/>
-      <c r="M340" s="235"/>
-      <c r="N340" s="235"/>
+      <c r="K340" s="232" t="s">
+        <v>958</v>
+      </c>
+      <c r="L340" s="232"/>
+      <c r="M340" s="232"/>
+      <c r="N340" s="232"/>
       <c r="O340" s="58"/>
       <c r="P340" s="58"/>
       <c r="Q340" s="58"/>
@@ -34450,85 +34539,69 @@
       <c r="AJ340" s="169"/>
       <c r="AK340" s="104"/>
     </row>
-    <row r="341" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="104"/>
-      <c r="B341" s="104"/>
       <c r="C341" s="104"/>
-      <c r="D341" s="104"/>
-      <c r="E341" s="104"/>
-      <c r="F341" s="104"/>
-      <c r="G341" s="104"/>
-      <c r="H341" s="104"/>
-      <c r="I341" s="104"/>
-      <c r="J341" s="104"/>
-      <c r="K341" s="104"/>
-      <c r="L341" s="104"/>
-      <c r="M341" s="104"/>
-      <c r="N341" s="104"/>
-      <c r="O341" s="104"/>
+      <c r="D341" s="95"/>
+      <c r="E341" s="95"/>
+      <c r="F341" s="233"/>
+      <c r="G341" s="233"/>
+      <c r="H341" s="58"/>
+      <c r="I341" s="58"/>
+      <c r="J341" s="58"/>
+      <c r="K341" s="232" t="s">
+        <v>959</v>
+      </c>
+      <c r="L341" s="232"/>
+      <c r="M341" s="232"/>
+      <c r="N341" s="232"/>
+      <c r="O341" s="58"/>
       <c r="P341" s="58"/>
       <c r="Q341" s="58"/>
       <c r="R341" s="58"/>
       <c r="S341" s="58"/>
       <c r="T341" s="104"/>
-      <c r="U341" s="104"/>
-      <c r="V341" s="104"/>
-      <c r="W341" s="104"/>
-      <c r="X341" s="104"/>
-      <c r="Y341" s="104"/>
-      <c r="Z341" s="104"/>
-      <c r="AA341" s="104"/>
-      <c r="AB341" s="104"/>
-      <c r="AC341" s="104"/>
-      <c r="AD341" s="104"/>
-      <c r="AE341" s="104"/>
-      <c r="AF341" s="104"/>
-      <c r="AG341" s="104"/>
-      <c r="AH341" s="104"/>
-      <c r="AI341" s="104"/>
-      <c r="AJ341" s="104"/>
+      <c r="U341" s="169"/>
+      <c r="V341" s="169"/>
+      <c r="W341" s="169"/>
+      <c r="X341" s="169"/>
+      <c r="Y341" s="169"/>
+      <c r="Z341" s="169"/>
+      <c r="AA341" s="169"/>
+      <c r="AB341" s="169"/>
+      <c r="AC341" s="169"/>
+      <c r="AD341" s="169"/>
+      <c r="AE341" s="169"/>
+      <c r="AF341" s="169"/>
+      <c r="AG341" s="169"/>
+      <c r="AH341" s="169"/>
+      <c r="AI341" s="169"/>
+      <c r="AJ341" s="169"/>
       <c r="AK341" s="104"/>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="104"/>
-      <c r="B342" s="54" t="s">
-        <v>529</v>
-      </c>
       <c r="C342" s="104"/>
-      <c r="D342" s="149" t="s">
-        <v>936</v>
-      </c>
-      <c r="E342" s="149" t="s">
-        <v>937</v>
-      </c>
-      <c r="F342" s="58" t="s">
-        <v>938</v>
-      </c>
-      <c r="G342" s="58"/>
-      <c r="H342" s="149" t="s">
-        <v>964</v>
-      </c>
-      <c r="I342" s="58" t="s">
-        <v>965</v>
-      </c>
+      <c r="D342" s="95"/>
+      <c r="E342" s="95"/>
+      <c r="F342" s="233"/>
+      <c r="G342" s="233"/>
+      <c r="H342" s="58"/>
+      <c r="I342" s="58"/>
       <c r="J342" s="58"/>
-      <c r="K342" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="L342" s="58"/>
-      <c r="M342" s="58"/>
-      <c r="N342" s="58"/>
-      <c r="O342" s="110" t="s">
-        <v>772</v>
-      </c>
+      <c r="K342" s="232" t="s">
+        <v>960</v>
+      </c>
+      <c r="L342" s="232"/>
+      <c r="M342" s="232"/>
+      <c r="N342" s="232"/>
+      <c r="O342" s="58"/>
       <c r="P342" s="58"/>
       <c r="Q342" s="58"/>
       <c r="R342" s="58"/>
       <c r="S342" s="58"/>
       <c r="T342" s="104"/>
-      <c r="U342" s="169" t="s">
-        <v>719</v>
-      </c>
+      <c r="U342" s="169"/>
       <c r="V342" s="169"/>
       <c r="W342" s="169"/>
       <c r="X342" s="169"/>
@@ -34548,36 +34621,21 @@
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="104"/>
-      <c r="B343" s="54" t="s">
-        <v>533</v>
-      </c>
       <c r="C343" s="104"/>
-      <c r="D343" s="94" t="s">
-        <v>921</v>
-      </c>
-      <c r="E343" s="236" t="s">
-        <v>940</v>
-      </c>
-      <c r="F343" s="228" t="s">
-        <v>941</v>
-      </c>
-      <c r="G343" s="228"/>
-      <c r="H343" s="94" t="s">
-        <v>921</v>
-      </c>
-      <c r="I343" s="186" t="s">
-        <v>966</v>
-      </c>
-      <c r="J343" s="186"/>
-      <c r="K343" s="229" t="s">
-        <v>943</v>
-      </c>
-      <c r="L343" s="229"/>
-      <c r="M343" s="229"/>
-      <c r="N343" s="229"/>
-      <c r="O343" s="58" t="s">
-        <v>967</v>
-      </c>
+      <c r="D343" s="95"/>
+      <c r="E343" s="95"/>
+      <c r="F343" s="233"/>
+      <c r="G343" s="233"/>
+      <c r="H343" s="58"/>
+      <c r="I343" s="58"/>
+      <c r="J343" s="58"/>
+      <c r="K343" s="232" t="s">
+        <v>961</v>
+      </c>
+      <c r="L343" s="232"/>
+      <c r="M343" s="232"/>
+      <c r="N343" s="232"/>
+      <c r="O343" s="58"/>
       <c r="P343" s="58"/>
       <c r="Q343" s="58"/>
       <c r="R343" s="58"/>
@@ -34603,29 +34661,16 @@
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="104"/>
-      <c r="B344" s="54" t="s">
-        <v>537</v>
-      </c>
       <c r="C344" s="104"/>
-      <c r="D344" s="95" t="s">
-        <v>829</v>
-      </c>
-      <c r="E344" s="237" t="s">
-        <v>945</v>
-      </c>
-      <c r="F344" s="231" t="s">
-        <v>946</v>
-      </c>
-      <c r="G344" s="231"/>
-      <c r="H344" s="95" t="s">
-        <v>829</v>
-      </c>
-      <c r="I344" s="95" t="s">
-        <v>968</v>
-      </c>
-      <c r="J344" s="95"/>
+      <c r="D344" s="95"/>
+      <c r="E344" s="95"/>
+      <c r="F344" s="233"/>
+      <c r="G344" s="233"/>
+      <c r="H344" s="58"/>
+      <c r="I344" s="58"/>
+      <c r="J344" s="58"/>
       <c r="K344" s="232" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="L344" s="232"/>
       <c r="M344" s="232"/>
@@ -34656,26 +34701,20 @@
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="104"/>
-      <c r="B345" s="54" t="s">
-        <v>541</v>
-      </c>
       <c r="C345" s="104"/>
-      <c r="D345" s="95"/>
-      <c r="F345" s="231" t="s">
-        <v>948</v>
-      </c>
-      <c r="G345" s="231"/>
-      <c r="H345" s="95"/>
-      <c r="I345" s="95" t="s">
-        <v>970</v>
-      </c>
-      <c r="J345" s="95"/>
-      <c r="K345" s="232" t="s">
-        <v>949</v>
-      </c>
-      <c r="L345" s="232"/>
-      <c r="M345" s="232"/>
-      <c r="N345" s="232"/>
+      <c r="D345" s="92"/>
+      <c r="E345" s="92"/>
+      <c r="F345" s="234"/>
+      <c r="G345" s="234"/>
+      <c r="H345" s="58"/>
+      <c r="I345" s="58"/>
+      <c r="J345" s="58"/>
+      <c r="K345" s="235" t="s">
+        <v>963</v>
+      </c>
+      <c r="L345" s="235"/>
+      <c r="M345" s="235"/>
+      <c r="N345" s="235"/>
       <c r="O345" s="58"/>
       <c r="P345" s="58"/>
       <c r="Q345" s="58"/>
@@ -34700,77 +34739,85 @@
       <c r="AJ345" s="169"/>
       <c r="AK345" s="104"/>
     </row>
-    <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="7.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="104"/>
-      <c r="B346" s="54" t="s">
-        <v>544</v>
-      </c>
+      <c r="B346" s="104"/>
       <c r="C346" s="104"/>
-      <c r="D346" s="95"/>
-      <c r="F346" s="231" t="s">
-        <v>950</v>
-      </c>
-      <c r="G346" s="231"/>
-      <c r="H346" s="95"/>
-      <c r="I346" s="95" t="s">
-        <v>971</v>
-      </c>
-      <c r="J346" s="95"/>
-      <c r="K346" s="232" t="s">
-        <v>951</v>
-      </c>
-      <c r="L346" s="232"/>
-      <c r="M346" s="232"/>
-      <c r="N346" s="232"/>
-      <c r="O346" s="58"/>
+      <c r="D346" s="104"/>
+      <c r="E346" s="104"/>
+      <c r="F346" s="104"/>
+      <c r="G346" s="104"/>
+      <c r="H346" s="104"/>
+      <c r="I346" s="104"/>
+      <c r="J346" s="104"/>
+      <c r="K346" s="104"/>
+      <c r="L346" s="104"/>
+      <c r="M346" s="104"/>
+      <c r="N346" s="104"/>
+      <c r="O346" s="104"/>
       <c r="P346" s="58"/>
       <c r="Q346" s="58"/>
       <c r="R346" s="58"/>
       <c r="S346" s="58"/>
       <c r="T346" s="104"/>
-      <c r="U346" s="169"/>
-      <c r="V346" s="169"/>
-      <c r="W346" s="169"/>
-      <c r="X346" s="169"/>
-      <c r="Y346" s="169"/>
-      <c r="Z346" s="169"/>
-      <c r="AA346" s="169"/>
-      <c r="AB346" s="169"/>
-      <c r="AC346" s="169"/>
-      <c r="AD346" s="169"/>
-      <c r="AE346" s="169"/>
-      <c r="AF346" s="169"/>
-      <c r="AG346" s="169"/>
-      <c r="AH346" s="169"/>
-      <c r="AI346" s="169"/>
-      <c r="AJ346" s="169"/>
+      <c r="U346" s="104"/>
+      <c r="V346" s="104"/>
+      <c r="W346" s="104"/>
+      <c r="X346" s="104"/>
+      <c r="Y346" s="104"/>
+      <c r="Z346" s="104"/>
+      <c r="AA346" s="104"/>
+      <c r="AB346" s="104"/>
+      <c r="AC346" s="104"/>
+      <c r="AD346" s="104"/>
+      <c r="AE346" s="104"/>
+      <c r="AF346" s="104"/>
+      <c r="AG346" s="104"/>
+      <c r="AH346" s="104"/>
+      <c r="AI346" s="104"/>
+      <c r="AJ346" s="104"/>
       <c r="AK346" s="104"/>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="104"/>
       <c r="B347" s="54" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C347" s="104"/>
-      <c r="D347" s="95"/>
-      <c r="F347" s="233"/>
-      <c r="G347" s="233"/>
-      <c r="H347" s="132"/>
-      <c r="I347" s="95"/>
-      <c r="J347" s="95"/>
-      <c r="K347" s="232" t="s">
-        <v>952</v>
-      </c>
-      <c r="L347" s="232"/>
-      <c r="M347" s="232"/>
-      <c r="N347" s="232"/>
-      <c r="O347" s="58"/>
+      <c r="D347" s="149" t="s">
+        <v>936</v>
+      </c>
+      <c r="E347" s="149" t="s">
+        <v>937</v>
+      </c>
+      <c r="F347" s="58" t="s">
+        <v>938</v>
+      </c>
+      <c r="G347" s="58"/>
+      <c r="H347" s="149" t="s">
+        <v>964</v>
+      </c>
+      <c r="I347" s="58" t="s">
+        <v>965</v>
+      </c>
+      <c r="J347" s="58"/>
+      <c r="K347" s="58" t="s">
+        <v>728</v>
+      </c>
+      <c r="L347" s="58"/>
+      <c r="M347" s="58"/>
+      <c r="N347" s="58"/>
+      <c r="O347" s="110" t="s">
+        <v>772</v>
+      </c>
       <c r="P347" s="58"/>
       <c r="Q347" s="58"/>
       <c r="R347" s="58"/>
       <c r="S347" s="58"/>
       <c r="T347" s="104"/>
-      <c r="U347" s="169"/>
+      <c r="U347" s="169" t="s">
+        <v>719</v>
+      </c>
       <c r="V347" s="169"/>
       <c r="W347" s="169"/>
       <c r="X347" s="169"/>
@@ -34791,22 +34838,35 @@
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="104"/>
       <c r="B348" s="54" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="C348" s="104"/>
-      <c r="D348" s="95"/>
-      <c r="F348" s="233"/>
-      <c r="G348" s="233"/>
-      <c r="H348" s="132"/>
-      <c r="I348" s="95"/>
-      <c r="J348" s="95"/>
-      <c r="K348" s="232" t="s">
-        <v>953</v>
-      </c>
-      <c r="L348" s="232"/>
-      <c r="M348" s="232"/>
-      <c r="N348" s="232"/>
-      <c r="O348" s="58"/>
+      <c r="D348" s="94" t="s">
+        <v>921</v>
+      </c>
+      <c r="E348" s="236" t="s">
+        <v>940</v>
+      </c>
+      <c r="F348" s="228" t="s">
+        <v>941</v>
+      </c>
+      <c r="G348" s="228"/>
+      <c r="H348" s="94" t="s">
+        <v>921</v>
+      </c>
+      <c r="I348" s="186" t="s">
+        <v>966</v>
+      </c>
+      <c r="J348" s="186"/>
+      <c r="K348" s="229" t="s">
+        <v>943</v>
+      </c>
+      <c r="L348" s="229"/>
+      <c r="M348" s="229"/>
+      <c r="N348" s="229"/>
+      <c r="O348" s="58" t="s">
+        <v>967</v>
+      </c>
       <c r="P348" s="58"/>
       <c r="Q348" s="58"/>
       <c r="R348" s="58"/>
@@ -34833,17 +34893,28 @@
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="104"/>
       <c r="B349" s="54" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="C349" s="104"/>
-      <c r="D349" s="95"/>
-      <c r="F349" s="233"/>
-      <c r="G349" s="233"/>
-      <c r="H349" s="132"/>
-      <c r="I349" s="95"/>
+      <c r="D349" s="95" t="s">
+        <v>829</v>
+      </c>
+      <c r="E349" s="237" t="s">
+        <v>945</v>
+      </c>
+      <c r="F349" s="231" t="s">
+        <v>946</v>
+      </c>
+      <c r="G349" s="231"/>
+      <c r="H349" s="95" t="s">
+        <v>829</v>
+      </c>
+      <c r="I349" s="95" t="s">
+        <v>968</v>
+      </c>
       <c r="J349" s="95"/>
       <c r="K349" s="232" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
       <c r="L349" s="232"/>
       <c r="M349" s="232"/>
@@ -34875,17 +34946,21 @@
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="104"/>
       <c r="B350" s="54" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="C350" s="104"/>
       <c r="D350" s="95"/>
-      <c r="F350" s="233"/>
-      <c r="G350" s="233"/>
-      <c r="H350" s="132"/>
-      <c r="I350" s="95"/>
+      <c r="F350" s="231" t="s">
+        <v>948</v>
+      </c>
+      <c r="G350" s="231"/>
+      <c r="H350" s="95"/>
+      <c r="I350" s="95" t="s">
+        <v>970</v>
+      </c>
       <c r="J350" s="95"/>
       <c r="K350" s="232" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="L350" s="232"/>
       <c r="M350" s="232"/>
@@ -34916,15 +34991,22 @@
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="104"/>
+      <c r="B351" s="54" t="s">
+        <v>544</v>
+      </c>
       <c r="C351" s="104"/>
       <c r="D351" s="95"/>
-      <c r="F351" s="233"/>
-      <c r="G351" s="233"/>
-      <c r="H351" s="132"/>
-      <c r="I351" s="95"/>
+      <c r="F351" s="231" t="s">
+        <v>950</v>
+      </c>
+      <c r="G351" s="231"/>
+      <c r="H351" s="95"/>
+      <c r="I351" s="95" t="s">
+        <v>971</v>
+      </c>
       <c r="J351" s="95"/>
       <c r="K351" s="232" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="L351" s="232"/>
       <c r="M351" s="232"/>
@@ -34955,6 +35037,9 @@
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="104"/>
+      <c r="B352" s="54" t="s">
+        <v>547</v>
+      </c>
       <c r="C352" s="104"/>
       <c r="D352" s="95"/>
       <c r="F352" s="233"/>
@@ -34963,7 +35048,7 @@
       <c r="I352" s="95"/>
       <c r="J352" s="95"/>
       <c r="K352" s="232" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="L352" s="232"/>
       <c r="M352" s="232"/>
@@ -34994,6 +35079,9 @@
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="104"/>
+      <c r="B353" s="54" t="s">
+        <v>550</v>
+      </c>
       <c r="C353" s="104"/>
       <c r="D353" s="95"/>
       <c r="F353" s="233"/>
@@ -35002,7 +35090,7 @@
       <c r="I353" s="95"/>
       <c r="J353" s="95"/>
       <c r="K353" s="232" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="L353" s="232"/>
       <c r="M353" s="232"/>
@@ -35033,6 +35121,9 @@
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="104"/>
+      <c r="B354" s="54" t="s">
+        <v>553</v>
+      </c>
       <c r="C354" s="104"/>
       <c r="D354" s="95"/>
       <c r="F354" s="233"/>
@@ -35041,7 +35132,7 @@
       <c r="I354" s="95"/>
       <c r="J354" s="95"/>
       <c r="K354" s="232" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="L354" s="232"/>
       <c r="M354" s="232"/>
@@ -35072,6 +35163,9 @@
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="104"/>
+      <c r="B355" s="54" t="s">
+        <v>556</v>
+      </c>
       <c r="C355" s="104"/>
       <c r="D355" s="95"/>
       <c r="F355" s="233"/>
@@ -35080,7 +35174,7 @@
       <c r="I355" s="95"/>
       <c r="J355" s="95"/>
       <c r="K355" s="232" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="L355" s="232"/>
       <c r="M355" s="232"/>
@@ -35119,7 +35213,7 @@
       <c r="I356" s="95"/>
       <c r="J356" s="95"/>
       <c r="K356" s="232" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="L356" s="232"/>
       <c r="M356" s="232"/>
@@ -35158,7 +35252,7 @@
       <c r="I357" s="95"/>
       <c r="J357" s="95"/>
       <c r="K357" s="232" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="L357" s="232"/>
       <c r="M357" s="232"/>
@@ -35190,19 +35284,18 @@
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="104"/>
       <c r="C358" s="104"/>
-      <c r="D358" s="92"/>
-      <c r="E358" s="197"/>
-      <c r="F358" s="234"/>
-      <c r="G358" s="234"/>
-      <c r="H358" s="198"/>
-      <c r="I358" s="223"/>
-      <c r="J358" s="223"/>
-      <c r="K358" s="235" t="s">
-        <v>963</v>
-      </c>
-      <c r="L358" s="235"/>
-      <c r="M358" s="235"/>
-      <c r="N358" s="235"/>
+      <c r="D358" s="95"/>
+      <c r="F358" s="233"/>
+      <c r="G358" s="233"/>
+      <c r="H358" s="132"/>
+      <c r="I358" s="95"/>
+      <c r="J358" s="95"/>
+      <c r="K358" s="232" t="s">
+        <v>958</v>
+      </c>
+      <c r="L358" s="232"/>
+      <c r="M358" s="232"/>
+      <c r="N358" s="232"/>
       <c r="O358" s="58"/>
       <c r="P358" s="58"/>
       <c r="Q358" s="58"/>
@@ -35229,45 +35322,241 @@
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="104"/>
-      <c r="B359" s="104"/>
       <c r="C359" s="104"/>
-      <c r="D359" s="104"/>
-      <c r="E359" s="104"/>
-      <c r="F359" s="104"/>
-      <c r="G359" s="104"/>
-      <c r="H359" s="104"/>
-      <c r="I359" s="104"/>
-      <c r="J359" s="104"/>
-      <c r="K359" s="104"/>
-      <c r="L359" s="104"/>
-      <c r="M359" s="104"/>
-      <c r="N359" s="104"/>
-      <c r="O359" s="104"/>
-      <c r="P359" s="104"/>
-      <c r="Q359" s="104"/>
-      <c r="R359" s="104"/>
-      <c r="S359" s="104"/>
+      <c r="D359" s="95"/>
+      <c r="F359" s="233"/>
+      <c r="G359" s="233"/>
+      <c r="H359" s="132"/>
+      <c r="I359" s="95"/>
+      <c r="J359" s="95"/>
+      <c r="K359" s="232" t="s">
+        <v>959</v>
+      </c>
+      <c r="L359" s="232"/>
+      <c r="M359" s="232"/>
+      <c r="N359" s="232"/>
+      <c r="O359" s="58"/>
+      <c r="P359" s="58"/>
+      <c r="Q359" s="58"/>
+      <c r="R359" s="58"/>
+      <c r="S359" s="58"/>
       <c r="T359" s="104"/>
-      <c r="U359" s="104"/>
-      <c r="V359" s="104"/>
-      <c r="W359" s="104"/>
-      <c r="X359" s="104"/>
-      <c r="Y359" s="104"/>
-      <c r="Z359" s="104"/>
-      <c r="AA359" s="104"/>
-      <c r="AB359" s="104"/>
-      <c r="AC359" s="104"/>
-      <c r="AD359" s="104"/>
-      <c r="AE359" s="104"/>
-      <c r="AF359" s="104"/>
-      <c r="AG359" s="104"/>
-      <c r="AH359" s="104"/>
-      <c r="AI359" s="104"/>
-      <c r="AJ359" s="104"/>
+      <c r="U359" s="169"/>
+      <c r="V359" s="169"/>
+      <c r="W359" s="169"/>
+      <c r="X359" s="169"/>
+      <c r="Y359" s="169"/>
+      <c r="Z359" s="169"/>
+      <c r="AA359" s="169"/>
+      <c r="AB359" s="169"/>
+      <c r="AC359" s="169"/>
+      <c r="AD359" s="169"/>
+      <c r="AE359" s="169"/>
+      <c r="AF359" s="169"/>
+      <c r="AG359" s="169"/>
+      <c r="AH359" s="169"/>
+      <c r="AI359" s="169"/>
+      <c r="AJ359" s="169"/>
       <c r="AK359" s="104"/>
     </row>
+    <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A360" s="104"/>
+      <c r="C360" s="104"/>
+      <c r="D360" s="95"/>
+      <c r="F360" s="233"/>
+      <c r="G360" s="233"/>
+      <c r="H360" s="132"/>
+      <c r="I360" s="95"/>
+      <c r="J360" s="95"/>
+      <c r="K360" s="232" t="s">
+        <v>960</v>
+      </c>
+      <c r="L360" s="232"/>
+      <c r="M360" s="232"/>
+      <c r="N360" s="232"/>
+      <c r="O360" s="58"/>
+      <c r="P360" s="58"/>
+      <c r="Q360" s="58"/>
+      <c r="R360" s="58"/>
+      <c r="S360" s="58"/>
+      <c r="T360" s="104"/>
+      <c r="U360" s="169"/>
+      <c r="V360" s="169"/>
+      <c r="W360" s="169"/>
+      <c r="X360" s="169"/>
+      <c r="Y360" s="169"/>
+      <c r="Z360" s="169"/>
+      <c r="AA360" s="169"/>
+      <c r="AB360" s="169"/>
+      <c r="AC360" s="169"/>
+      <c r="AD360" s="169"/>
+      <c r="AE360" s="169"/>
+      <c r="AF360" s="169"/>
+      <c r="AG360" s="169"/>
+      <c r="AH360" s="169"/>
+      <c r="AI360" s="169"/>
+      <c r="AJ360" s="169"/>
+      <c r="AK360" s="104"/>
+    </row>
+    <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A361" s="104"/>
+      <c r="C361" s="104"/>
+      <c r="D361" s="95"/>
+      <c r="F361" s="233"/>
+      <c r="G361" s="233"/>
+      <c r="H361" s="132"/>
+      <c r="I361" s="95"/>
+      <c r="J361" s="95"/>
+      <c r="K361" s="232" t="s">
+        <v>961</v>
+      </c>
+      <c r="L361" s="232"/>
+      <c r="M361" s="232"/>
+      <c r="N361" s="232"/>
+      <c r="O361" s="58"/>
+      <c r="P361" s="58"/>
+      <c r="Q361" s="58"/>
+      <c r="R361" s="58"/>
+      <c r="S361" s="58"/>
+      <c r="T361" s="104"/>
+      <c r="U361" s="169"/>
+      <c r="V361" s="169"/>
+      <c r="W361" s="169"/>
+      <c r="X361" s="169"/>
+      <c r="Y361" s="169"/>
+      <c r="Z361" s="169"/>
+      <c r="AA361" s="169"/>
+      <c r="AB361" s="169"/>
+      <c r="AC361" s="169"/>
+      <c r="AD361" s="169"/>
+      <c r="AE361" s="169"/>
+      <c r="AF361" s="169"/>
+      <c r="AG361" s="169"/>
+      <c r="AH361" s="169"/>
+      <c r="AI361" s="169"/>
+      <c r="AJ361" s="169"/>
+      <c r="AK361" s="104"/>
+    </row>
+    <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A362" s="104"/>
+      <c r="C362" s="104"/>
+      <c r="D362" s="95"/>
+      <c r="F362" s="233"/>
+      <c r="G362" s="233"/>
+      <c r="H362" s="132"/>
+      <c r="I362" s="95"/>
+      <c r="J362" s="95"/>
+      <c r="K362" s="232" t="s">
+        <v>962</v>
+      </c>
+      <c r="L362" s="232"/>
+      <c r="M362" s="232"/>
+      <c r="N362" s="232"/>
+      <c r="O362" s="58"/>
+      <c r="P362" s="58"/>
+      <c r="Q362" s="58"/>
+      <c r="R362" s="58"/>
+      <c r="S362" s="58"/>
+      <c r="T362" s="104"/>
+      <c r="U362" s="169"/>
+      <c r="V362" s="169"/>
+      <c r="W362" s="169"/>
+      <c r="X362" s="169"/>
+      <c r="Y362" s="169"/>
+      <c r="Z362" s="169"/>
+      <c r="AA362" s="169"/>
+      <c r="AB362" s="169"/>
+      <c r="AC362" s="169"/>
+      <c r="AD362" s="169"/>
+      <c r="AE362" s="169"/>
+      <c r="AF362" s="169"/>
+      <c r="AG362" s="169"/>
+      <c r="AH362" s="169"/>
+      <c r="AI362" s="169"/>
+      <c r="AJ362" s="169"/>
+      <c r="AK362" s="104"/>
+    </row>
+    <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A363" s="104"/>
+      <c r="C363" s="104"/>
+      <c r="D363" s="92"/>
+      <c r="E363" s="197"/>
+      <c r="F363" s="234"/>
+      <c r="G363" s="234"/>
+      <c r="H363" s="198"/>
+      <c r="I363" s="223"/>
+      <c r="J363" s="223"/>
+      <c r="K363" s="235" t="s">
+        <v>963</v>
+      </c>
+      <c r="L363" s="235"/>
+      <c r="M363" s="235"/>
+      <c r="N363" s="235"/>
+      <c r="O363" s="58"/>
+      <c r="P363" s="58"/>
+      <c r="Q363" s="58"/>
+      <c r="R363" s="58"/>
+      <c r="S363" s="58"/>
+      <c r="T363" s="104"/>
+      <c r="U363" s="169"/>
+      <c r="V363" s="169"/>
+      <c r="W363" s="169"/>
+      <c r="X363" s="169"/>
+      <c r="Y363" s="169"/>
+      <c r="Z363" s="169"/>
+      <c r="AA363" s="169"/>
+      <c r="AB363" s="169"/>
+      <c r="AC363" s="169"/>
+      <c r="AD363" s="169"/>
+      <c r="AE363" s="169"/>
+      <c r="AF363" s="169"/>
+      <c r="AG363" s="169"/>
+      <c r="AH363" s="169"/>
+      <c r="AI363" s="169"/>
+      <c r="AJ363" s="169"/>
+      <c r="AK363" s="104"/>
+    </row>
+    <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A364" s="104"/>
+      <c r="B364" s="104"/>
+      <c r="C364" s="104"/>
+      <c r="D364" s="104"/>
+      <c r="E364" s="104"/>
+      <c r="F364" s="104"/>
+      <c r="G364" s="104"/>
+      <c r="H364" s="104"/>
+      <c r="I364" s="104"/>
+      <c r="J364" s="104"/>
+      <c r="K364" s="104"/>
+      <c r="L364" s="104"/>
+      <c r="M364" s="104"/>
+      <c r="N364" s="104"/>
+      <c r="O364" s="104"/>
+      <c r="P364" s="104"/>
+      <c r="Q364" s="104"/>
+      <c r="R364" s="104"/>
+      <c r="S364" s="104"/>
+      <c r="T364" s="104"/>
+      <c r="U364" s="104"/>
+      <c r="V364" s="104"/>
+      <c r="W364" s="104"/>
+      <c r="X364" s="104"/>
+      <c r="Y364" s="104"/>
+      <c r="Z364" s="104"/>
+      <c r="AA364" s="104"/>
+      <c r="AB364" s="104"/>
+      <c r="AC364" s="104"/>
+      <c r="AD364" s="104"/>
+      <c r="AE364" s="104"/>
+      <c r="AF364" s="104"/>
+      <c r="AG364" s="104"/>
+      <c r="AH364" s="104"/>
+      <c r="AI364" s="104"/>
+      <c r="AJ364" s="104"/>
+      <c r="AK364" s="104"/>
+    </row>
   </sheetData>
-  <mergeCells count="801">
+  <mergeCells count="815">
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="B2:I6"/>
     <mergeCell ref="J2:L4"/>
@@ -35671,15 +35960,15 @@
     <mergeCell ref="M176:M177"/>
     <mergeCell ref="D179:F179"/>
     <mergeCell ref="G179:I179"/>
-    <mergeCell ref="J179:L179"/>
+    <mergeCell ref="J179:K179"/>
     <mergeCell ref="N179:O179"/>
     <mergeCell ref="U179:AJ179"/>
     <mergeCell ref="D180:F185"/>
     <mergeCell ref="G180:I185"/>
-    <mergeCell ref="J180:L180"/>
+    <mergeCell ref="J180:K180"/>
     <mergeCell ref="N180:O185"/>
     <mergeCell ref="U180:AJ182"/>
-    <mergeCell ref="J181:L182"/>
+    <mergeCell ref="J181:K182"/>
     <mergeCell ref="J183:K183"/>
     <mergeCell ref="U183:AB183"/>
     <mergeCell ref="AC183:AJ183"/>
@@ -35752,7 +36041,7 @@
     <mergeCell ref="D218:I218"/>
     <mergeCell ref="J218:L218"/>
     <mergeCell ref="M218:O218"/>
-    <mergeCell ref="P218:S276"/>
+    <mergeCell ref="P218:S281"/>
     <mergeCell ref="U218:AJ224"/>
     <mergeCell ref="D219:I224"/>
     <mergeCell ref="J219:K219"/>
@@ -35858,144 +36147,134 @@
     <mergeCell ref="U268:AJ271"/>
     <mergeCell ref="J269:L269"/>
     <mergeCell ref="J270:L271"/>
-    <mergeCell ref="D273:F273"/>
-    <mergeCell ref="G273:I273"/>
-    <mergeCell ref="J273:L273"/>
-    <mergeCell ref="M273:O273"/>
-    <mergeCell ref="U273:AJ276"/>
-    <mergeCell ref="D274:F274"/>
-    <mergeCell ref="G274:I274"/>
-    <mergeCell ref="M274:O276"/>
-    <mergeCell ref="D275:F276"/>
-    <mergeCell ref="G275:I276"/>
     <mergeCell ref="D278:F278"/>
-    <mergeCell ref="G278:K278"/>
-    <mergeCell ref="L278:M278"/>
-    <mergeCell ref="N278:O278"/>
-    <mergeCell ref="P278:S322"/>
-    <mergeCell ref="U278:AJ280"/>
-    <mergeCell ref="L279:M279"/>
-    <mergeCell ref="N279:O284"/>
-    <mergeCell ref="L280:M280"/>
-    <mergeCell ref="D282:F282"/>
-    <mergeCell ref="G282:H282"/>
-    <mergeCell ref="I282:K282"/>
-    <mergeCell ref="L282:M282"/>
-    <mergeCell ref="U282:AJ284"/>
-    <mergeCell ref="D283:F284"/>
-    <mergeCell ref="I283:K284"/>
+    <mergeCell ref="G278:I278"/>
+    <mergeCell ref="J278:L278"/>
+    <mergeCell ref="M278:O278"/>
+    <mergeCell ref="U278:AJ281"/>
+    <mergeCell ref="D279:F279"/>
+    <mergeCell ref="G279:I279"/>
+    <mergeCell ref="M279:O281"/>
+    <mergeCell ref="D280:F281"/>
+    <mergeCell ref="G280:I281"/>
+    <mergeCell ref="D283:F283"/>
+    <mergeCell ref="G283:K283"/>
     <mergeCell ref="L283:M283"/>
+    <mergeCell ref="N283:O283"/>
+    <mergeCell ref="P283:S327"/>
+    <mergeCell ref="U283:AJ285"/>
     <mergeCell ref="L284:M284"/>
-    <mergeCell ref="D286:F286"/>
-    <mergeCell ref="G286:I286"/>
-    <mergeCell ref="L286:M286"/>
-    <mergeCell ref="N286:O286"/>
-    <mergeCell ref="U286:AJ291"/>
-    <mergeCell ref="D287:F291"/>
-    <mergeCell ref="G287:I291"/>
+    <mergeCell ref="N284:O289"/>
+    <mergeCell ref="L285:M285"/>
+    <mergeCell ref="D287:F287"/>
+    <mergeCell ref="G287:H287"/>
+    <mergeCell ref="I287:K287"/>
     <mergeCell ref="L287:M287"/>
-    <mergeCell ref="N287:O291"/>
+    <mergeCell ref="U287:AJ289"/>
+    <mergeCell ref="D288:F289"/>
+    <mergeCell ref="I288:K289"/>
     <mergeCell ref="L288:M288"/>
     <mergeCell ref="L289:M289"/>
-    <mergeCell ref="L290:M290"/>
+    <mergeCell ref="D291:F291"/>
+    <mergeCell ref="G291:I291"/>
     <mergeCell ref="L291:M291"/>
-    <mergeCell ref="E293:G293"/>
-    <mergeCell ref="H293:M293"/>
-    <mergeCell ref="N293:O293"/>
-    <mergeCell ref="U293:AJ293"/>
-    <mergeCell ref="D294:D296"/>
-    <mergeCell ref="F294:G294"/>
-    <mergeCell ref="H294:I294"/>
-    <mergeCell ref="J294:M294"/>
-    <mergeCell ref="N294:O322"/>
-    <mergeCell ref="U294:AJ296"/>
-    <mergeCell ref="E295:E296"/>
-    <mergeCell ref="F295:G296"/>
-    <mergeCell ref="H295:I296"/>
-    <mergeCell ref="J295:M296"/>
-    <mergeCell ref="E297:G297"/>
-    <mergeCell ref="H297:M297"/>
-    <mergeCell ref="U297:AJ297"/>
-    <mergeCell ref="D298:D300"/>
-    <mergeCell ref="F298:G298"/>
-    <mergeCell ref="H298:I298"/>
-    <mergeCell ref="J298:M298"/>
-    <mergeCell ref="U298:AJ303"/>
-    <mergeCell ref="E299:E300"/>
-    <mergeCell ref="F299:G300"/>
-    <mergeCell ref="H299:I303"/>
-    <mergeCell ref="J299:M303"/>
-    <mergeCell ref="F301:G301"/>
-    <mergeCell ref="E302:E303"/>
-    <mergeCell ref="F302:G302"/>
+    <mergeCell ref="N291:O291"/>
+    <mergeCell ref="U291:AJ296"/>
+    <mergeCell ref="D292:F296"/>
+    <mergeCell ref="G292:I296"/>
+    <mergeCell ref="L292:M292"/>
+    <mergeCell ref="N292:O296"/>
+    <mergeCell ref="L293:M293"/>
+    <mergeCell ref="L294:M294"/>
+    <mergeCell ref="L295:M295"/>
+    <mergeCell ref="L296:M296"/>
+    <mergeCell ref="E298:G298"/>
+    <mergeCell ref="H298:M298"/>
+    <mergeCell ref="N298:O298"/>
+    <mergeCell ref="U298:AJ298"/>
+    <mergeCell ref="D299:D301"/>
+    <mergeCell ref="F299:G299"/>
+    <mergeCell ref="H299:I299"/>
+    <mergeCell ref="J299:M299"/>
+    <mergeCell ref="N299:O327"/>
+    <mergeCell ref="U299:AJ301"/>
+    <mergeCell ref="E300:E301"/>
+    <mergeCell ref="F300:G301"/>
+    <mergeCell ref="H300:I301"/>
+    <mergeCell ref="J300:M301"/>
+    <mergeCell ref="E302:G302"/>
+    <mergeCell ref="H302:M302"/>
+    <mergeCell ref="U302:AJ302"/>
+    <mergeCell ref="D303:D305"/>
     <mergeCell ref="F303:G303"/>
-    <mergeCell ref="E304:F304"/>
-    <mergeCell ref="G304:M304"/>
-    <mergeCell ref="U304:AJ304"/>
-    <mergeCell ref="D305:D307"/>
-    <mergeCell ref="E305:F305"/>
-    <mergeCell ref="H305:I305"/>
-    <mergeCell ref="J305:M305"/>
-    <mergeCell ref="U305:AJ307"/>
-    <mergeCell ref="E306:F307"/>
-    <mergeCell ref="G306:G307"/>
-    <mergeCell ref="H306:I307"/>
-    <mergeCell ref="J306:M307"/>
-    <mergeCell ref="E308:F308"/>
-    <mergeCell ref="G308:M308"/>
-    <mergeCell ref="U308:AJ308"/>
-    <mergeCell ref="D309:D311"/>
+    <mergeCell ref="H303:I303"/>
+    <mergeCell ref="J303:M303"/>
+    <mergeCell ref="U303:AJ308"/>
+    <mergeCell ref="E304:E305"/>
+    <mergeCell ref="F304:G305"/>
+    <mergeCell ref="H304:I308"/>
+    <mergeCell ref="J304:M308"/>
+    <mergeCell ref="F306:G306"/>
+    <mergeCell ref="E307:E308"/>
+    <mergeCell ref="F307:G307"/>
+    <mergeCell ref="F308:G308"/>
     <mergeCell ref="E309:F309"/>
-    <mergeCell ref="H309:I309"/>
-    <mergeCell ref="J309:M309"/>
-    <mergeCell ref="U309:AJ311"/>
-    <mergeCell ref="E310:F311"/>
-    <mergeCell ref="G310:G311"/>
-    <mergeCell ref="H310:I311"/>
-    <mergeCell ref="J310:M311"/>
-    <mergeCell ref="D312:F312"/>
-    <mergeCell ref="G312:M312"/>
-    <mergeCell ref="U312:AJ312"/>
-    <mergeCell ref="D313:F322"/>
-    <mergeCell ref="G313:I313"/>
-    <mergeCell ref="J313:M313"/>
-    <mergeCell ref="U313:AJ315"/>
-    <mergeCell ref="G314:I315"/>
-    <mergeCell ref="J314:M315"/>
-    <mergeCell ref="G316:H316"/>
-    <mergeCell ref="J316:M316"/>
-    <mergeCell ref="U316:AJ316"/>
-    <mergeCell ref="I317:I319"/>
-    <mergeCell ref="J317:M319"/>
-    <mergeCell ref="U317:AB317"/>
-    <mergeCell ref="AC317:AJ317"/>
-    <mergeCell ref="U318:AB319"/>
-    <mergeCell ref="AC318:AJ319"/>
-    <mergeCell ref="G320:I320"/>
-    <mergeCell ref="J320:M320"/>
-    <mergeCell ref="U320:AJ322"/>
-    <mergeCell ref="H321:I321"/>
-    <mergeCell ref="J321:M322"/>
-    <mergeCell ref="H322:I322"/>
-    <mergeCell ref="F324:G324"/>
-    <mergeCell ref="H324:J324"/>
-    <mergeCell ref="K324:N324"/>
-    <mergeCell ref="P324:S358"/>
-    <mergeCell ref="U324:AJ340"/>
-    <mergeCell ref="F325:G325"/>
-    <mergeCell ref="H325:J340"/>
-    <mergeCell ref="K325:N325"/>
-    <mergeCell ref="O325:O340"/>
-    <mergeCell ref="F326:G326"/>
-    <mergeCell ref="K326:N326"/>
-    <mergeCell ref="F327:G327"/>
-    <mergeCell ref="K327:N327"/>
-    <mergeCell ref="F328:G328"/>
-    <mergeCell ref="K328:N328"/>
+    <mergeCell ref="G309:M309"/>
+    <mergeCell ref="U309:AJ309"/>
+    <mergeCell ref="D310:D312"/>
+    <mergeCell ref="E310:F310"/>
+    <mergeCell ref="H310:I310"/>
+    <mergeCell ref="J310:M310"/>
+    <mergeCell ref="U310:AJ312"/>
+    <mergeCell ref="E311:F312"/>
+    <mergeCell ref="G311:G312"/>
+    <mergeCell ref="H311:I312"/>
+    <mergeCell ref="J311:M312"/>
+    <mergeCell ref="E313:F313"/>
+    <mergeCell ref="G313:M313"/>
+    <mergeCell ref="U313:AJ313"/>
+    <mergeCell ref="D314:D316"/>
+    <mergeCell ref="E314:F314"/>
+    <mergeCell ref="H314:I314"/>
+    <mergeCell ref="J314:M314"/>
+    <mergeCell ref="U314:AJ316"/>
+    <mergeCell ref="E315:F316"/>
+    <mergeCell ref="G315:G316"/>
+    <mergeCell ref="H315:I316"/>
+    <mergeCell ref="J315:M316"/>
+    <mergeCell ref="D317:F317"/>
+    <mergeCell ref="G317:M317"/>
+    <mergeCell ref="U317:AJ317"/>
+    <mergeCell ref="D318:F327"/>
+    <mergeCell ref="G318:I318"/>
+    <mergeCell ref="J318:M318"/>
+    <mergeCell ref="U318:AJ320"/>
+    <mergeCell ref="G319:I320"/>
+    <mergeCell ref="J319:M320"/>
+    <mergeCell ref="G321:H321"/>
+    <mergeCell ref="J321:M321"/>
+    <mergeCell ref="U321:AJ321"/>
+    <mergeCell ref="I322:I324"/>
+    <mergeCell ref="J322:M324"/>
+    <mergeCell ref="U322:AB322"/>
+    <mergeCell ref="AC322:AJ322"/>
+    <mergeCell ref="U323:AB324"/>
+    <mergeCell ref="AC323:AJ324"/>
+    <mergeCell ref="G325:I325"/>
+    <mergeCell ref="J325:M325"/>
+    <mergeCell ref="U325:AJ327"/>
+    <mergeCell ref="H326:I326"/>
+    <mergeCell ref="J326:M327"/>
+    <mergeCell ref="H327:I327"/>
     <mergeCell ref="F329:G329"/>
+    <mergeCell ref="H329:J329"/>
     <mergeCell ref="K329:N329"/>
+    <mergeCell ref="P329:S363"/>
+    <mergeCell ref="U329:AJ345"/>
     <mergeCell ref="F330:G330"/>
+    <mergeCell ref="H330:J345"/>
     <mergeCell ref="K330:N330"/>
+    <mergeCell ref="O330:O345"/>
     <mergeCell ref="F331:G331"/>
     <mergeCell ref="K331:N331"/>
     <mergeCell ref="F332:G332"/>
@@ -36016,29 +36295,24 @@
     <mergeCell ref="K339:N339"/>
     <mergeCell ref="F340:G340"/>
     <mergeCell ref="K340:N340"/>
+    <mergeCell ref="F341:G341"/>
+    <mergeCell ref="K341:N341"/>
     <mergeCell ref="F342:G342"/>
-    <mergeCell ref="I342:J342"/>
     <mergeCell ref="K342:N342"/>
-    <mergeCell ref="U342:AJ358"/>
     <mergeCell ref="F343:G343"/>
-    <mergeCell ref="I343:J343"/>
     <mergeCell ref="K343:N343"/>
-    <mergeCell ref="O343:O358"/>
     <mergeCell ref="F344:G344"/>
-    <mergeCell ref="I344:J344"/>
     <mergeCell ref="K344:N344"/>
     <mergeCell ref="F345:G345"/>
-    <mergeCell ref="I345:J345"/>
     <mergeCell ref="K345:N345"/>
-    <mergeCell ref="F346:G346"/>
-    <mergeCell ref="I346:J346"/>
-    <mergeCell ref="K346:N346"/>
     <mergeCell ref="F347:G347"/>
     <mergeCell ref="I347:J347"/>
     <mergeCell ref="K347:N347"/>
+    <mergeCell ref="U347:AJ363"/>
     <mergeCell ref="F348:G348"/>
     <mergeCell ref="I348:J348"/>
     <mergeCell ref="K348:N348"/>
+    <mergeCell ref="O348:O363"/>
     <mergeCell ref="F349:G349"/>
     <mergeCell ref="I349:J349"/>
     <mergeCell ref="K349:N349"/>
@@ -36069,6 +36343,35 @@
     <mergeCell ref="F358:G358"/>
     <mergeCell ref="I358:J358"/>
     <mergeCell ref="K358:N358"/>
+    <mergeCell ref="F359:G359"/>
+    <mergeCell ref="I359:J359"/>
+    <mergeCell ref="K359:N359"/>
+    <mergeCell ref="F360:G360"/>
+    <mergeCell ref="I360:J360"/>
+    <mergeCell ref="K360:N360"/>
+    <mergeCell ref="F361:G361"/>
+    <mergeCell ref="I361:J361"/>
+    <mergeCell ref="K361:N361"/>
+    <mergeCell ref="F362:G362"/>
+    <mergeCell ref="I362:J362"/>
+    <mergeCell ref="K362:N362"/>
+    <mergeCell ref="F363:G363"/>
+    <mergeCell ref="I363:J363"/>
+    <mergeCell ref="K363:N363"/>
+    <mergeCell ref="D273:E273"/>
+    <mergeCell ref="F273:J273"/>
+    <mergeCell ref="K273:L273"/>
+    <mergeCell ref="M273:O273"/>
+    <mergeCell ref="U273:AJ273"/>
+    <mergeCell ref="D274:E274"/>
+    <mergeCell ref="F274:G274"/>
+    <mergeCell ref="H274:J274"/>
+    <mergeCell ref="K274:L276"/>
+    <mergeCell ref="M274:O276"/>
+    <mergeCell ref="U274:AJ276"/>
+    <mergeCell ref="D275:E276"/>
+    <mergeCell ref="F275:G276"/>
+    <mergeCell ref="H275:J276"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">O2:o:s → R</t>
   </si>
   <si>
-    <t xml:space="preserve">Copy a value of a given width in memory into a register sign extended.  A value wider than the register is truncated.  n and z are set from the value copied.  The zero extending copy (and the copy into memory) is code 12 extend 3; there is no room for this one there.</t>
+    <t xml:space="preserve">Copy a value of a given width (8, 16 or 32 bits) in memory into a register sign extended.  A value wider than the register is truncated.  n and z are set from the value copied.  There is no sign extending copy into memory; use the zero extending cpyx.</t>
   </si>
   <si>
     <t xml:space="preserve">Status to status</t>
@@ -4738,7 +4738,7 @@
     <t xml:space="preserve">Hardware Register Index</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardware, State, Copy Extend (sign extend)</t>
+    <t xml:space="preserve">Hardware, State, Copy Extend</t>
   </si>
   <si>
     <t xml:space="preserve">0 – 63</t>

--- a/W65C64/65C64 Instruction Architecture.xlsx
+++ b/W65C64/65C64 Instruction Architecture.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2655" uniqueCount="1297">
   <si>
     <t xml:space="preserve">Pin number</t>
   </si>
@@ -6057,6 +6057,9 @@
   </si>
   <si>
     <t xml:space="preserve">r2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None, V, X or Y</t>
   </si>
 </sst>
 </file>
@@ -21475,7 +21478,7 @@
       <c r="G44" s="164"/>
       <c r="H44" s="164"/>
       <c r="I44" s="161" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="J44" s="161"/>
       <c r="K44" s="161" t="s">
@@ -21657,7 +21660,7 @@
       <c r="G48" s="169"/>
       <c r="H48" s="169"/>
       <c r="I48" s="178" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="J48" s="178"/>
       <c r="K48" s="58" t="s">
@@ -27913,7 +27916,7 @@
       </c>
       <c r="F189" s="58"/>
       <c r="G189" s="161" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="H189" s="161"/>
       <c r="I189" s="161" t="s">
@@ -28085,7 +28088,7 @@
       </c>
       <c r="F193" s="161"/>
       <c r="G193" s="58" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="H193" s="58"/>
       <c r="I193" s="58" t="s">
@@ -31609,7 +31612,7 @@
       </c>
       <c r="E275" s="58"/>
       <c r="F275" s="161" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="G275" s="161"/>
       <c r="H275" s="161" t="s">
@@ -32728,7 +32731,7 @@
       </c>
       <c r="G300" s="58"/>
       <c r="H300" s="161" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="I300" s="161"/>
       <c r="J300" s="161" t="s">
@@ -32908,7 +32911,7 @@
       </c>
       <c r="G304" s="183"/>
       <c r="H304" s="58" t="s">
-        <v>735</v>
+        <v>1296</v>
       </c>
       <c r="I304" s="58"/>
       <c r="J304" s="58" t="s">
